--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB6211B-7BB8-F147-9BFC-B305C1A3640C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE045A27-5AAD-A448-AAB9-525566B7978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14420" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="4060" yWindow="3180" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="836">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3257,9 +3257,6 @@
     <t>fig/XLK-311-Restaurant/AiCity-910-築地樂樂町-02.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-新福島.jpg</t>
-  </si>
-  <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-河馬水產-02.jpeg</t>
   </si>
   <si>
@@ -3486,6 +3483,49 @@
   <si>
     <t>&lt;p&gt;
   網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://tw.news.yahoo.com/%E9%BE%9C%E5%B1%B1%E5%8C%97%E6%96%B9%E9%BA%B5%E9%A3%9F%E9%A4%90%E9%A4%A8%E5%89%B5%E6%84%8F%E5%B0%8F%E5%90%83-%E9%99%9D%E8%A5%BF%E7%89%B9%E8%89%B2%E8%82%89%E5%A4%BE%E9%A5%83-053033386.html"&gt;Yahoo!新聞&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>041</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22:02 火鍋。樂活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-新福島.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-樂活.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/2202LOHAS/posts/2197829400359251</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段2號2樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2609-2229</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 - 15:00, 17:00 - 22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="http://tw.openrice.com/info/event/partner-2202lohas/index.html"&gt;定位&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://www.upmedia.mg/news_info.php?SerialNo=87122"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3919,7 +3959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5473,7 +5513,7 @@
         <v>604</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>758</v>
+        <v>828</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>605</v>
@@ -5491,1129 +5531,1129 @@
         <v>668</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="64">
+    <row r="42" spans="1:12" ht="80">
       <c r="A42" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="K42" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="64">
+      <c r="A43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K42" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="80">
-      <c r="A43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K43" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="80">
       <c r="A44" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K44" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="80">
       <c r="A45" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="K45" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="80">
+      <c r="A46" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F46" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H45" s="6" t="s">
+      <c r="G46" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="K45" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="48">
-      <c r="A46" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="K46" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="48">
       <c r="A47" s="1" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="K47" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="64">
       <c r="A48" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K48" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="48">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="64">
       <c r="A49" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="K49" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="48">
       <c r="A50" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>448</v>
+        <v>270</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K50" s="10">
         <v>4.3</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="48">
       <c r="A51" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K51" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="48">
       <c r="A52" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K52" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="96">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="48">
       <c r="A53" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>449</v>
+        <v>235</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K53" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="80">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="96">
       <c r="A54" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K54" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K55" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="64">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>808</v>
+        <v>230</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>809</v>
+        <v>280</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>815</v>
+        <v>450</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>816</v>
+        <v>283</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>817</v>
+        <v>284</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>812</v>
+        <v>281</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>811</v>
+        <v>771</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>810</v>
+        <v>282</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>814</v>
+        <v>549</v>
       </c>
       <c r="K56" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>813</v>
+        <v>682</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="64">
       <c r="A57" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="K57" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="64">
+      <c r="A58" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="K57" s="10">
-        <v>4</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="80">
-      <c r="A58" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K58" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="64">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="80">
       <c r="A59" s="1" t="s">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K59" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="112">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="64">
       <c r="A60" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K60" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="80">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="112">
       <c r="A61" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>50</v>
+        <v>494</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K61" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="64">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="80">
       <c r="A62" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K62" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="80">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="64">
       <c r="A63" s="1" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="K63" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="112">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="80">
       <c r="A64" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K64" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="48">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="112">
       <c r="A65" s="1" t="s">
-        <v>461</v>
+        <v>296</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="K65" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="144">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>476</v>
+        <v>62</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>477</v>
+        <v>780</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="K66" s="10">
         <v>4.2</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="64">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="144">
       <c r="A67" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>33</v>
+        <v>475</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>34</v>
+        <v>781</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K67" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="96">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="64">
       <c r="A68" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>467</v>
+        <v>32</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>468</v>
+        <v>782</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K68" s="10">
         <v>3.9</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="64">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="96">
       <c r="A69" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K69" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="48">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="64">
       <c r="A70" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>452</v>
+        <v>478</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>24</v>
+        <v>480</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>25</v>
+        <v>784</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="K70" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="80">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="48">
       <c r="A71" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>447</v>
+        <v>22</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>25</v>
@@ -6622,885 +6662,923 @@
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K71" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="80">
       <c r="A72" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K72" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="48">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="64">
       <c r="A73" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>553</v>
+        <v>586</v>
       </c>
       <c r="K73" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="48">
       <c r="A74" s="1" t="s">
-        <v>607</v>
+        <v>313</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>608</v>
+        <v>69</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>610</v>
+        <v>444</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>611</v>
+        <v>70</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>612</v>
+        <v>71</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>609</v>
+        <v>788</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K74" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="48">
+      <c r="A75" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J75" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="K74" s="10">
+      <c r="K75" s="10">
         <v>4.2</v>
       </c>
-      <c r="L74" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="32">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:12" ht="32">
+      <c r="A76" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H75" s="2" t="s">
+      <c r="G76" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="K75" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="64">
-      <c r="A76" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J76" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="K76" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
+      <c r="A77" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="K76" s="10">
+      <c r="K77" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L76" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="48">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:12" ht="48">
+      <c r="A78" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C78" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D78" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E78" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F78" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G78" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="K78" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="96">
+      <c r="A79" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="K77" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="96">
-      <c r="A78" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H78" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J78" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="K78" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
-      <c r="A79" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K79" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="112">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="64">
       <c r="A80" s="1" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>368</v>
+        <v>505</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="K80" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="96">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="112">
       <c r="A81" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>13</v>
+        <v>469</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>15</v>
+        <v>471</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>16</v>
+        <v>795</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="K81" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="96">
       <c r="A82" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>721</v>
+        <v>796</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>590</v>
+        <v>557</v>
       </c>
       <c r="K82" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="48">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="64">
       <c r="A83" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>821</v>
+        <v>721</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="K83" s="10"/>
+        <v>590</v>
+      </c>
+      <c r="K83" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L83" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="96">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="48">
       <c r="A84" s="1" t="s">
-        <v>808</v>
+        <v>397</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>818</v>
+        <v>87</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="E84" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>823</v>
+      <c r="H84" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="K84" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L84" s="6" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" ht="64">
+      <c r="K84" s="10"/>
+      <c r="L84" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="96">
       <c r="A85" s="1" t="s">
-        <v>398</v>
+        <v>807</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>450</v>
+        <v>817</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>376</v>
+        <v>818</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>798</v>
+        <v>821</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>377</v>
+        <v>822</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>591</v>
+        <v>825</v>
       </c>
       <c r="K85" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="48">
+      <c r="L85" s="6" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="64">
       <c r="A86" s="1" t="s">
-        <v>594</v>
+        <v>398</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>595</v>
+        <v>374</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>596</v>
+        <v>429</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>597</v>
+        <v>375</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>598</v>
+        <v>377</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="K86" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="96">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="48">
       <c r="A87" s="1" t="s">
-        <v>399</v>
+        <v>594</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>370</v>
+        <v>595</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>430</v>
+        <v>596</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>373</v>
+        <v>597</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>371</v>
+        <v>598</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="K87" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="48">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="96">
       <c r="A88" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>558</v>
+        <v>592</v>
       </c>
       <c r="K88" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="48">
       <c r="A89" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K89" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="96">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="48">
       <c r="A90" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="K90" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="48">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="96">
       <c r="A91" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="K91" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K92" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="48">
       <c r="A93" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>369</v>
+        <v>804</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K93" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="48">
       <c r="A94" s="1" t="s">
-        <v>614</v>
+        <v>485</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>616</v>
+        <v>366</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>617</v>
+        <v>367</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>618</v>
+        <v>368</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>619</v>
+        <v>369</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K94" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="48">
+      <c r="A95" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J95" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="K94" s="10">
+      <c r="K95" s="10">
         <v>3.4</v>
       </c>
-      <c r="L94" s="2" t="s">
+      <c r="L95" s="2" t="s">
         <v>718</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J93">
-    <sortCondition ref="I2:I93"/>
-    <sortCondition ref="D2:D93"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J94">
+    <sortCondition ref="I2:I94"/>
+    <sortCondition ref="D2:D94"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -7522,18 +7600,18 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H52" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H50" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H54" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H51" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H53" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H46" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H45" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H49" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H48" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H55" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H47" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H76" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H53" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H51" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H55" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H52" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H54" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H47" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H46" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H50" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H49" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H56" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H48" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H77" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
     <hyperlink ref="H26" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
     <hyperlink ref="H25" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
     <hyperlink ref="H19" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
@@ -7546,26 +7624,28 @@
     <hyperlink ref="H18" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H23" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H15" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H93" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H87" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H85" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H88" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H89" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H90" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H91" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H77" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H68" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H80" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H66" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H69" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H79" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H86" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H94" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H88" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H86" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H89" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H90" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H91" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H92" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H78" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H69" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H81" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H67" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H70" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H80" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H87" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
     <hyperlink ref="H41" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H74" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H94" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H56" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H84" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L84" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H75" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H95" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H57" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H85" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L85" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H42" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L42" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE045A27-5AAD-A448-AAB9-525566B7978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FAC69A-BA35-A24D-A9D0-644B77F3FDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4060" yWindow="3180" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="420" yWindow="980" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="854">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3251,9 +3251,6 @@
     <t>fig/XLK-311-Restaurant/AiCity-910-法國秘密甜點.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-Japoli.png</t>
-  </si>
-  <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-築地樂樂町-02.jpeg</t>
   </si>
   <si>
@@ -3491,10 +3488,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>22:02 火鍋。樂活</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-新福島.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3526,6 +3519,93 @@
     <t>&lt;p&gt;
   網路資訊:  &lt;a style="button" class="btn btn-info"  href="http://tw.openrice.com/info/event/partner-2202lohas/index.html"&gt;定位&lt;/a&gt;   &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://www.upmedia.mg/news_info.php?SerialNo=87122"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>042</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鍋。樂活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>八方悅鍋物-林口仁愛店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://8funyay.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛二路77號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2609-2369</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30 - 14:00, 17:00 - 22:00 週一公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97-113276467677766/menu/"&gt;菜單&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97-113276467677766/"&gt;臉書&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-八方悅.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>043</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat enjoy意享 - 三井店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美式餐廳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/eatenjoy2/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Eat+enjoy%E6%84%8F%E4%BA%AB%E7%BE%8E%E5%BC%8F%E5%BB%9A%E6%88%BF%E6%9E%97%E5%8F%A3%E4%B8%89%E4%BA%95%E5%BA%97+%E5%A4%96%E5%B8%B6%E7%BE%8E%E9%A3%9F+%E5%A4%96%E9%80%81%E7%BE%8E%E9%A3%9F+%E6%9E%97%E5%8F%A3%E4%B8%89%E4%BA%95%E7%BE%8E%E9%A3%9F+%E5%8D%83%E5%B1%A4%E8%9B%8B%E7%B3%95+%E7%BE%8E%E5%BC%8F%E9%A4%90%E5%BB%B3+%E8%81%9A%E9%A4%90+%E5%AF%B5%E7%89%A9%E5%8F%8B%E5%96%84/@25.072552,121.3636991,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a727fb78e64f:0x9abd8dfa7c5596c2!8m2!3d25.0725999!4d121.3658377</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段390-1號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2600-5881</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-Japoli.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-意享.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/eatenjoy2/menu/"&gt;菜單&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://kevin6071020.pixnet.net/blog/post/224509473-%E3%80%90%E6%9E%97%E5%8F%A3%E7%BE%8E%E9%A3%9F%E3%80%91eat-enjoy%E6%84%8F%E4%BA%AB%E7%BE%8E%E5%BC%8F%E5%BB%9A%E6%88%BF%EF%BC%8D%E9%81%93%E9%81%93%E9%83%BD%E5%A5%BD"&gt;推薦&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://inline.app/booking/-LACL2z10Bn3FImsV1RO?fbclid=IwAR3QE5fFefOzd_eql-EyO73SGANiiFEEWaykOhkkkAowmbjMFGgkA5k57EA"&gt;定位&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3959,7 +4039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4014,7 +4094,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="112">
+    <row r="2" spans="1:12" ht="144">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -4090,7 +4170,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80">
+    <row r="4" spans="1:12" ht="96">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4204,7 +4284,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80">
+    <row r="7" spans="1:12" ht="96">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -4356,7 +4436,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="128">
+    <row r="11" spans="1:12" ht="144">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -4629,8 +4709,8 @@
       <c r="B18" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>450</v>
+      <c r="C18" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>351</v>
@@ -5437,7 +5517,7 @@
         <v>149</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>756</v>
+        <v>851</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>150</v>
@@ -5455,2130 +5535,2206 @@
         <v>666</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="80">
+    <row r="40" spans="1:12" ht="144">
       <c r="A40" s="1" t="s">
-        <v>173</v>
+        <v>844</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>119</v>
+        <v>845</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>448</v>
+        <v>846</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>412</v>
+        <v>849</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>120</v>
+        <v>850</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>121</v>
+        <v>467</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>122</v>
+        <v>852</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>847</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>567</v>
+        <v>853</v>
       </c>
       <c r="K40" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="48">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="80">
       <c r="A41" s="1" t="s">
-        <v>600</v>
+        <v>173</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>602</v>
+        <v>412</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>603</v>
+        <v>120</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>604</v>
+        <v>121</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>605</v>
+        <v>756</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="K41" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="80">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="48">
       <c r="A42" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>829</v>
-      </c>
       <c r="H42" s="6" t="s">
-        <v>830</v>
+        <v>605</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="K42" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="80">
+      <c r="A43" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="K42" s="10">
+      <c r="C43" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="K43" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L43" s="6" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="128">
+      <c r="A44" s="1" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="64">
-      <c r="A43" s="1" t="s">
+      <c r="B44" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="K44" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="64">
+      <c r="A45" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K43" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="80">
-      <c r="A44" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="K44" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="80">
-      <c r="A45" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K45" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="80">
       <c r="A46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K46" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="80">
+      <c r="A47" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="K47" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="80">
+      <c r="A48" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="H46" s="6" t="s">
+      <c r="G48" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="K46" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="48">
-      <c r="A47" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="K47" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="64">
-      <c r="A48" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K48" s="10">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="48">
       <c r="A49" s="1" t="s">
-        <v>206</v>
+        <v>459</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="K49" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="64">
       <c r="A50" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K50" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="48">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="64">
       <c r="A51" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>448</v>
+        <v>275</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="K51" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="48">
       <c r="A52" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K52" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="48">
       <c r="A53" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K53" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="96">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="48">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>449</v>
+        <v>250</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K54" s="10">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="48">
       <c r="A55" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K55" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="96">
       <c r="A56" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K56" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="80">
       <c r="A57" s="1" t="s">
-        <v>807</v>
+        <v>229</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>808</v>
+        <v>245</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>814</v>
+        <v>450</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>815</v>
+        <v>246</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>816</v>
+        <v>247</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>811</v>
+        <v>249</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>809</v>
+        <v>248</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="K57" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="48">
+      <c r="A58" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="K58" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="64">
+      <c r="A59" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="K57" s="10">
+      <c r="D59" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K59" s="10">
         <v>4.2</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="64">
-      <c r="A58" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="K58" s="10">
-        <v>4</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="80">
-      <c r="A59" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="K59" s="10">
-        <v>4.3</v>
-      </c>
       <c r="L59" s="2" t="s">
-        <v>684</v>
+        <v>811</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="64">
       <c r="A60" s="1" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>449</v>
+        <v>37</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="K60" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="112">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="80">
       <c r="A61" s="1" t="s">
-        <v>232</v>
+        <v>460</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>447</v>
+        <v>27</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K61" s="10">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="64">
       <c r="A62" s="1" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>50</v>
+        <v>499</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="K62" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="112">
       <c r="A63" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>55</v>
+        <v>494</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K63" s="10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="80">
       <c r="A64" s="1" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>452</v>
+        <v>50</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="K64" s="10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="112">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="64">
       <c r="A65" s="1" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K65" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="48">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="80">
       <c r="A66" s="1" t="s">
-        <v>461</v>
+        <v>290</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>448</v>
+        <v>495</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K66" s="10">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="144">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="112">
       <c r="A67" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>449</v>
+        <v>496</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>476</v>
+        <v>18</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>477</v>
+        <v>778</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K67" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="48">
       <c r="A68" s="1" t="s">
-        <v>307</v>
+        <v>461</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>451</v>
+        <v>497</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="K68" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="96">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="144">
       <c r="A69" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="K69" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="64">
       <c r="A70" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>479</v>
+        <v>424</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>481</v>
+        <v>32</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>482</v>
+        <v>781</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="K70" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="48">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="96">
       <c r="A71" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>452</v>
+        <v>464</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>24</v>
+        <v>466</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>467</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>25</v>
+        <v>782</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>468</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="K71" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="80">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="64">
       <c r="A72" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>66</v>
+        <v>478</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>417</v>
+        <v>479</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>42</v>
+        <v>480</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>25</v>
+        <v>783</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K72" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="64">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="48">
       <c r="A73" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>449</v>
+        <v>22</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>586</v>
+        <v>552</v>
       </c>
       <c r="K73" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="48">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="80">
       <c r="A74" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K74" s="10">
         <v>3.8</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="48">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>607</v>
+        <v>312</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>608</v>
+        <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>610</v>
+        <v>443</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>611</v>
+        <v>75</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>612</v>
+        <v>76</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>609</v>
+        <v>786</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="K75" s="10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="32">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="48">
       <c r="A76" s="1" t="s">
-        <v>401</v>
+        <v>313</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>450</v>
+        <v>69</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="K76" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="64">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="48">
       <c r="A77" s="1" t="s">
-        <v>315</v>
+        <v>607</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>291</v>
+        <v>608</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>292</v>
+        <v>610</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>294</v>
+        <v>611</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>612</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>295</v>
+        <v>609</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="K77" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="48">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="32">
       <c r="A78" s="1" t="s">
-        <v>316</v>
+        <v>401</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>406</v>
+        <v>500</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D78" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>410</v>
+      <c r="D78" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>408</v>
+        <v>789</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>407</v>
+        <v>12</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="K78" s="10">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="64">
       <c r="A79" s="1" t="s">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>452</v>
+        <v>291</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>425</v>
+        <v>292</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>10</v>
+        <v>293</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>11</v>
+        <v>790</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>295</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="K79" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="64">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="48">
       <c r="A80" s="1" t="s">
-        <v>502</v>
+        <v>316</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>467</v>
+        <v>406</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>410</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>506</v>
+        <v>408</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="K80" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="112">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="96">
       <c r="A81" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>447</v>
+        <v>8</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>470</v>
+        <v>425</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>368</v>
+        <v>9</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>472</v>
+        <v>792</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="K81" s="10">
-        <v>3.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="64">
       <c r="A82" s="1" t="s">
-        <v>395</v>
+        <v>502</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>13</v>
+        <v>503</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>426</v>
+        <v>504</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>14</v>
+        <v>505</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>15</v>
+        <v>467</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>16</v>
+        <v>793</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K82" s="10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="64">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="112">
       <c r="A83" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>47</v>
+        <v>471</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>48</v>
+        <v>794</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K83" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="48">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="96">
       <c r="A84" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="K84" s="10"/>
+        <v>557</v>
+      </c>
+      <c r="K84" s="10">
+        <v>4.3</v>
+      </c>
       <c r="L84" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="96">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>807</v>
+        <v>396</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>817</v>
+        <v>501</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>819</v>
+        <v>427</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>388</v>
+        <v>47</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>822</v>
+        <v>721</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>825</v>
+        <v>590</v>
       </c>
       <c r="K85" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L85" s="6" t="s">
+      <c r="L85" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="48">
+      <c r="A86" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" ht="64">
-      <c r="A86" s="1" t="s">
+      <c r="K86" s="10"/>
+      <c r="L86" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="96">
+      <c r="A87" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="K87" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="64">
+      <c r="A88" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="K86" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="48">
-      <c r="A87" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="K87" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="96">
-      <c r="A88" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K88" s="10">
-        <v>4.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="48">
       <c r="A89" s="1" t="s">
-        <v>400</v>
+        <v>594</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>378</v>
+        <v>595</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>431</v>
+        <v>596</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>381</v>
+        <v>597</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>379</v>
+        <v>598</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="K89" s="10">
-        <v>3.1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="48">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="96">
       <c r="A90" s="1" t="s">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="K90" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="48">
       <c r="A91" s="1" t="s">
-        <v>463</v>
+        <v>400</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>593</v>
+        <v>558</v>
       </c>
       <c r="K91" s="10">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K92" s="10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="48">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="96">
       <c r="A93" s="1" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="K93" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="48">
       <c r="A94" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K94" s="10">
-        <v>4.4000000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>614</v>
+        <v>484</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>616</v>
+        <v>382</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>435</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>617</v>
+        <v>384</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>618</v>
+        <v>383</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>619</v>
+        <v>803</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="K95" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="48">
+      <c r="A96" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K96" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48">
+      <c r="A97" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J97" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="K95" s="10">
+      <c r="K97" s="10">
         <v>3.4</v>
       </c>
-      <c r="L95" s="2" t="s">
+      <c r="L97" s="2" t="s">
         <v>718</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J94">
-    <sortCondition ref="I2:I94"/>
-    <sortCondition ref="D2:D94"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J96">
+    <sortCondition ref="I2:I96"/>
+    <sortCondition ref="D2:D96"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -7600,18 +7756,18 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H53" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H51" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H55" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H52" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H54" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H47" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H46" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H50" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H49" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H56" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H48" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H77" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H55" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H53" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H57" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H54" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H56" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H49" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H48" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H52" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H51" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H58" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H50" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H79" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
     <hyperlink ref="H26" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
     <hyperlink ref="H25" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
     <hyperlink ref="H19" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
@@ -7624,28 +7780,31 @@
     <hyperlink ref="H18" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H23" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H15" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H94" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H88" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H86" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H89" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H90" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H91" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H92" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H78" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H69" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H81" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H67" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H70" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H80" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H87" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H41" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H75" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H95" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H57" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H85" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L85" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H42" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L42" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H96" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H90" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H88" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H91" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H92" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H93" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H94" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H80" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H71" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H83" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H69" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H72" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H82" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H89" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H42" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H77" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H97" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H59" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H87" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L87" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H43" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L43" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H44" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L44" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H40" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FAC69A-BA35-A24D-A9D0-644B77F3FDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C821B5A8-CB47-7240-BD27-EE4A6FEA774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="980" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="1300" yWindow="640" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2513,12 +2513,6 @@
   </si>
   <si>
     <t>&lt;p&gt;
-  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://editordiary.pixnet.net/blog/post/218296050"&gt;推薦&lt;/a&gt;  &amp;nbsp;
-   &lt;a style="button" class="btn btn-info"  href="https://aniseblog.tw/203738"&gt;推薦&lt;/a&gt; 
-&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.thaitown.com.tw/tw/menu"&gt;菜單&lt;/a&gt; &amp;nbsp; 
 &lt;a style="button" class="btn btn-info"  href="https://ryohei0221.pixnet.net/blog/post/68108145"&gt;推薦&lt;/a&gt; &amp;nbsp; 
  &lt;a style="button" class="btn btn-info"  href="https://en.eztable.com/restaurant/14471"&gt;訂位&lt;/a&gt;
@@ -3606,6 +3600,14 @@
   網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/eatenjoy2/menu/"&gt;菜單&lt;/a&gt;   &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://kevin6071020.pixnet.net/blog/post/224509473-%E3%80%90%E6%9E%97%E5%8F%A3%E7%BE%8E%E9%A3%9F%E3%80%91eat-enjoy%E6%84%8F%E4%BA%AB%E7%BE%8E%E5%BC%8F%E5%BB%9A%E6%88%BF%EF%BC%8D%E9%81%93%E9%81%93%E9%83%BD%E5%A5%BD"&gt;推薦&lt;/a&gt; &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://inline.app/booking/-LACL2z10Bn3FImsV1RO?fbclid=IwAR3QE5fFefOzd_eql-EyO73SGANiiFEEWaykOhkkkAowmbjMFGgkA5k57EA"&gt;定位&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:    &lt;a style="button" class="btn btn-info"  href="fig/XLK-311-Restaurant/AiCity-910-老占元-菜單.jpeg"&gt;菜單&lt;/a&gt; &amp;nbsp;
+ &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=_evGpVKi4II"&gt;推薦&lt;/a&gt;  &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://aniseblog.tw/203738"&gt;推薦&lt;/a&gt; 
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4088,13 +4090,13 @@
         <v>446</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="144">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="112">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -4114,7 +4116,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>106</v>
@@ -4129,7 +4131,7 @@
         <v>3.8</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="112">
@@ -4152,7 +4154,7 @@
         <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>48</v>
@@ -4167,10 +4169,10 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="96">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="80">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4190,7 +4192,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>99</v>
@@ -4205,7 +4207,7 @@
         <v>3.3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="80">
@@ -4228,7 +4230,7 @@
         <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>94</v>
@@ -4237,13 +4239,13 @@
         <v>95</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K5" s="10">
         <v>4.2</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48">
@@ -4251,7 +4253,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>449</v>
@@ -4266,7 +4268,7 @@
         <v>134</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
@@ -4275,21 +4277,21 @@
         <v>95</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K6" s="10">
         <v>3.8</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="96">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="80">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>450</v>
@@ -4304,7 +4306,7 @@
         <v>143</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>144</v>
@@ -4319,7 +4321,7 @@
         <v>4.7</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="80">
@@ -4342,7 +4344,7 @@
         <v>198</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>199</v>
@@ -4357,7 +4359,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17">
@@ -4365,7 +4367,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>452</v>
@@ -4380,7 +4382,7 @@
         <v>214</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>215</v>
@@ -4395,7 +4397,7 @@
         <v>4.5</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="97">
@@ -4418,7 +4420,7 @@
         <v>204</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>210</v>
@@ -4433,15 +4435,15 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="144">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="128">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>447</v>
@@ -4456,7 +4458,7 @@
         <v>204</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>205</v>
@@ -4471,7 +4473,7 @@
         <v>3.8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="96">
@@ -4479,7 +4481,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>452</v>
@@ -4494,7 +4496,7 @@
         <v>218</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>219</v>
@@ -4509,7 +4511,7 @@
         <v>4</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="64">
@@ -4532,7 +4534,7 @@
         <v>218</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>223</v>
@@ -4547,7 +4549,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="144">
@@ -4570,7 +4572,7 @@
         <v>218</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>226</v>
@@ -4585,7 +4587,7 @@
         <v>4.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="80">
@@ -4599,7 +4601,7 @@
         <v>450</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>363</v>
@@ -4608,7 +4610,7 @@
         <v>364</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>362</v>
@@ -4623,7 +4625,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="64">
@@ -4646,7 +4648,7 @@
         <v>334</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>335</v>
@@ -4661,7 +4663,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="96">
@@ -4669,7 +4671,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>449</v>
@@ -4684,7 +4686,7 @@
         <v>349</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>350</v>
@@ -4699,7 +4701,7 @@
         <v>4.7</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
@@ -4722,7 +4724,7 @@
         <v>353</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>354</v>
@@ -4737,7 +4739,7 @@
         <v>4.3</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="96">
@@ -4760,7 +4762,7 @@
         <v>320</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>321</v>
@@ -4775,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="96">
@@ -4798,7 +4800,7 @@
         <v>330</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>331</v>
@@ -4813,7 +4815,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
@@ -4836,7 +4838,7 @@
         <v>325</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>326</v>
@@ -4851,7 +4853,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="64">
@@ -4874,7 +4876,7 @@
         <v>340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>341</v>
@@ -4889,7 +4891,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="80">
@@ -4912,7 +4914,7 @@
         <v>359</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>358</v>
@@ -4927,10 +4929,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="64">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
         <v>457</v>
       </c>
@@ -4950,7 +4952,7 @@
         <v>345</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>346</v>
@@ -4959,13 +4961,13 @@
         <v>305</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>564</v>
+        <v>853</v>
       </c>
       <c r="K24" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="64">
@@ -4988,7 +4990,7 @@
         <v>303</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>304</v>
@@ -5003,7 +5005,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="96">
@@ -5026,7 +5028,7 @@
         <v>300</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>298</v>
@@ -5041,7 +5043,7 @@
         <v>4.2</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="64">
@@ -5064,7 +5066,7 @@
         <v>161</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>162</v>
@@ -5079,7 +5081,7 @@
         <v>4.8</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="80">
@@ -5102,7 +5104,7 @@
         <v>171</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>186</v>
@@ -5117,7 +5119,7 @@
         <v>3.9</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="64">
@@ -5140,7 +5142,7 @@
         <v>155</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>156</v>
@@ -5155,7 +5157,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="96">
@@ -5178,7 +5180,7 @@
         <v>161</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>176</v>
@@ -5193,7 +5195,7 @@
         <v>3.9</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="96">
@@ -5216,7 +5218,7 @@
         <v>180</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>181</v>
@@ -5231,7 +5233,7 @@
         <v>4.2</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="96">
@@ -5254,7 +5256,7 @@
         <v>180</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>190</v>
@@ -5269,7 +5271,7 @@
         <v>3.8</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="112">
@@ -5292,7 +5294,7 @@
         <v>161</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>194</v>
@@ -5307,7 +5309,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="128">
@@ -5330,7 +5332,7 @@
         <v>110</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>94</v>
@@ -5345,7 +5347,7 @@
         <v>4</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="112">
@@ -5368,7 +5370,7 @@
         <v>110</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>114</v>
@@ -5383,7 +5385,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="128">
@@ -5406,7 +5408,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>117</v>
@@ -5421,7 +5423,7 @@
         <v>3.7</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="112">
@@ -5441,7 +5443,7 @@
         <v>166</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>167</v>
@@ -5456,7 +5458,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="64">
@@ -5479,7 +5481,7 @@
         <v>171</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>172</v>
@@ -5494,7 +5496,7 @@
         <v>4.3</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="80">
@@ -5517,7 +5519,7 @@
         <v>149</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>150</v>
@@ -5532,45 +5534,45 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="144">
       <c r="A40" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>846</v>
-      </c>
       <c r="D40" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>467</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K40" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="80">
@@ -5593,7 +5595,7 @@
         <v>121</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>122</v>
@@ -5602,127 +5604,127 @@
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K41" s="10">
         <v>3.5</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="48">
       <c r="A42" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>604</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>605</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K42" s="10">
         <v>4.3</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="80">
       <c r="A43" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>831</v>
-      </c>
       <c r="G43" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>827</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>828</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K43" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="128">
       <c r="A44" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>841</v>
-      </c>
       <c r="G44" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K44" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="64">
@@ -5745,7 +5747,7 @@
         <v>129</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>130</v>
@@ -5754,13 +5756,13 @@
         <v>126</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K45" s="10">
         <v>3.9</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="80">
@@ -5783,7 +5785,7 @@
         <v>42</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>125</v>
@@ -5792,13 +5794,13 @@
         <v>126</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K46" s="10">
         <v>4.3</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="80">
@@ -5821,7 +5823,7 @@
         <v>138</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>139</v>
@@ -5830,13 +5832,13 @@
         <v>140</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K47" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="80">
@@ -5859,7 +5861,7 @@
         <v>268</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>269</v>
@@ -5868,13 +5870,13 @@
         <v>227</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K48" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="48">
@@ -5897,7 +5899,7 @@
         <v>264</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>263</v>
@@ -5912,7 +5914,7 @@
         <v>4.5</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="64">
@@ -5935,7 +5937,7 @@
         <v>289</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>288</v>
@@ -5944,13 +5946,13 @@
         <v>227</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K50" s="10">
         <v>4.7</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="64">
@@ -5973,7 +5975,7 @@
         <v>279</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>278</v>
@@ -5982,13 +5984,13 @@
         <v>227</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K51" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="48">
@@ -6011,7 +6013,7 @@
         <v>274</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>273</v>
@@ -6026,7 +6028,7 @@
         <v>4.3</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="48">
@@ -6049,7 +6051,7 @@
         <v>244</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>243</v>
@@ -6064,7 +6066,7 @@
         <v>4.3</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="48">
@@ -6087,7 +6089,7 @@
         <v>254</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>253</v>
@@ -6102,7 +6104,7 @@
         <v>4.7</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="48">
@@ -6125,7 +6127,7 @@
         <v>239</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>238</v>
@@ -6140,7 +6142,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="96">
@@ -6163,7 +6165,7 @@
         <v>259</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>258</v>
@@ -6178,7 +6180,7 @@
         <v>4</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="80">
@@ -6201,7 +6203,7 @@
         <v>249</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>248</v>
@@ -6216,7 +6218,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="48">
@@ -6239,7 +6241,7 @@
         <v>281</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>282</v>
@@ -6254,45 +6256,45 @@
         <v>4.5</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="64">
       <c r="A59" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H59" s="6" t="s">
         <v>807</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>808</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K59" s="10">
         <v>4.2</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="64">
@@ -6315,7 +6317,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>39</v>
@@ -6324,13 +6326,13 @@
         <v>411</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K60" s="10">
         <v>4</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="80">
@@ -6353,7 +6355,7 @@
         <v>29</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>30</v>
@@ -6362,13 +6364,13 @@
         <v>411</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K61" s="10">
         <v>4.3</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="64">
@@ -6391,7 +6393,7 @@
         <v>80</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>81</v>
@@ -6400,13 +6402,13 @@
         <v>411</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K62" s="10">
         <v>3.8</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="112">
@@ -6429,7 +6431,7 @@
         <v>60</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>61</v>
@@ -6438,13 +6440,13 @@
         <v>411</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K63" s="10">
         <v>3.7</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="80">
@@ -6467,7 +6469,7 @@
         <v>52</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>53</v>
@@ -6476,13 +6478,13 @@
         <v>411</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K64" s="10">
         <v>4.3</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="64">
@@ -6505,7 +6507,7 @@
         <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>57</v>
@@ -6514,13 +6516,13 @@
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K65" s="10">
         <v>3.8</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="80">
@@ -6543,7 +6545,7 @@
         <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>43</v>
@@ -6558,7 +6560,7 @@
         <v>3.5</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="112">
@@ -6581,7 +6583,7 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>20</v>
@@ -6590,13 +6592,13 @@
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K67" s="10">
         <v>3.9</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="48">
@@ -6619,7 +6621,7 @@
         <v>63</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>64</v>
@@ -6634,7 +6636,7 @@
         <v>4.2</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="144">
@@ -6657,7 +6659,7 @@
         <v>476</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>477</v>
@@ -6666,13 +6668,13 @@
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K69" s="10">
         <v>4.2</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="64">
@@ -6695,7 +6697,7 @@
         <v>33</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>34</v>
@@ -6704,13 +6706,13 @@
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K70" s="10">
         <v>3.9</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="96">
@@ -6733,7 +6735,7 @@
         <v>467</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>468</v>
@@ -6742,13 +6744,13 @@
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K71" s="10">
         <v>3.9</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="64">
@@ -6771,7 +6773,7 @@
         <v>481</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>482</v>
@@ -6780,13 +6782,13 @@
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K72" s="10">
         <v>4</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="48">
@@ -6809,7 +6811,7 @@
         <v>24</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>25</v>
@@ -6824,7 +6826,7 @@
         <v>4.3</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="80">
@@ -6847,7 +6849,7 @@
         <v>42</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>25</v>
@@ -6856,13 +6858,13 @@
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K74" s="10">
         <v>3.8</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="64">
@@ -6885,7 +6887,7 @@
         <v>76</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>77</v>
@@ -6894,13 +6896,13 @@
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K75" s="10">
         <v>4</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="48">
@@ -6923,7 +6925,7 @@
         <v>71</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>72</v>
@@ -6938,45 +6940,45 @@
         <v>3.8</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="48">
       <c r="A77" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="G77" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K77" s="10">
         <v>4.2</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="32">
@@ -6999,7 +7001,7 @@
         <v>84</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>85</v>
@@ -7008,13 +7010,13 @@
         <v>12</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K78" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="64">
@@ -7037,7 +7039,7 @@
         <v>294</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>295</v>
@@ -7046,13 +7048,13 @@
         <v>12</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K79" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="48">
@@ -7075,7 +7077,7 @@
         <v>410</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>408</v>
@@ -7090,7 +7092,7 @@
         <v>4.5</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="96">
@@ -7113,7 +7115,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>11</v>
@@ -7128,7 +7130,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="64">
@@ -7151,7 +7153,7 @@
         <v>467</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>506</v>
@@ -7166,7 +7168,7 @@
         <v>4.2</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="112">
@@ -7189,7 +7191,7 @@
         <v>368</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>472</v>
@@ -7198,13 +7200,13 @@
         <v>12</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K83" s="10">
         <v>3.3</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="96">
@@ -7227,7 +7229,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>16</v>
@@ -7242,7 +7244,7 @@
         <v>4.3</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="64">
@@ -7265,7 +7267,7 @@
         <v>47</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>48</v>
@@ -7274,13 +7276,13 @@
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K85" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="48">
@@ -7303,7 +7305,7 @@
         <v>42</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>89</v>
@@ -7312,49 +7314,49 @@
         <v>12</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="K86" s="10"/>
       <c r="L86" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="96">
       <c r="A87" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>817</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>818</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>388</v>
       </c>
       <c r="G87" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="H87" s="6" t="s">
         <v>820</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>821</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K87" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="64">
@@ -7377,7 +7379,7 @@
         <v>376</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>377</v>
@@ -7386,48 +7388,48 @@
         <v>365</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K88" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="48">
       <c r="A89" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="G89" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H89" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>598</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K89" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="96">
@@ -7450,7 +7452,7 @@
         <v>373</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>371</v>
@@ -7459,13 +7461,13 @@
         <v>365</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K90" s="10">
         <v>4.7</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="48">
@@ -7488,7 +7490,7 @@
         <v>381</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>379</v>
@@ -7503,7 +7505,7 @@
         <v>3.1</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="48">
@@ -7526,7 +7528,7 @@
         <v>388</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>385</v>
@@ -7541,7 +7543,7 @@
         <v>4.3</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="96">
@@ -7564,7 +7566,7 @@
         <v>392</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>390</v>
@@ -7573,13 +7575,13 @@
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K93" s="10">
         <v>3.8</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="48">
@@ -7602,7 +7604,7 @@
         <v>404</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>403</v>
@@ -7617,7 +7619,7 @@
         <v>3.9</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="48">
@@ -7640,7 +7642,7 @@
         <v>383</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
@@ -7652,7 +7654,7 @@
         <v>4.3</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="48">
@@ -7675,7 +7677,7 @@
         <v>368</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>369</v>
@@ -7690,45 +7692,45 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>448</v>
       </c>
       <c r="D97" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="F97" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="H97" s="6" t="s">
         <v>618</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>619</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K97" s="10">
         <v>3.4</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C821B5A8-CB47-7240-BD27-EE4A6FEA774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909764C-6AFB-EB4F-BB83-583B2925E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="640" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="2660" yWindow="1160" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="878">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3173,9 +3173,6 @@
     <t>fig/XLK-311-Restaurant/AiCity-910-原燒.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-Nini.jpeg</t>
-  </si>
-  <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-呷冰食堂.jpg</t>
   </si>
   <si>
@@ -3608,6 +3605,115 @@
   網路資訊:    &lt;a style="button" class="btn btn-info"  href="fig/XLK-311-Restaurant/AiCity-910-老占元-菜單.jpeg"&gt;菜單&lt;/a&gt; &amp;nbsp;
  &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=_evGpVKi4II"&gt;推薦&lt;/a&gt;  &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://aniseblog.tw/203738"&gt;推薦&lt;/a&gt; 
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk in Café</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區東湖路155號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2602-2736</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:30 ~ 21:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-Nini.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-WalkinCafe.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/Walk+In+Cafe+(%E6%9D%B1%E6%B9%96%E8%B7%AF%E4%B8%80%E5%BA%97)/@25.076602,121.3754823,15.03z/data=!4m5!3m4!1s0x3442a7825ca84ba9:0x10a7794b5cdf0af7!8m2!3d25.0729537!4d121.3829821?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Walkin1805/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/Walkin1805/photos/?tab=album&amp;album_id=1801334346625830"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://zineblog.com.tw/blog/post/200616"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>御鼎湯原本鍋物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛路二段2號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2601-0107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 ~ 22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-御鼎湯原本鍋物.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E5%BE%A1%E9%BC%8E%E6%B9%AF+%E5%8E%9F%E6%9C%AC%E9%8D%8B%E7%89%A9+%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0766312,121.3489812,13z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5b6h6byO5rmv5Y6f5pys6Y2L54mp!3m5!1s0x3442a748fc9abb59:0x2bdfe620d9af149b!8m2!3d25.0765474!4d121.3858298!15sCh7mlrDljJfluILlvqHpvI7mua_ljp_mnKzpjYvnialaJiIk5pawIOWMl-W4giDlvqEg6byOIOa5r-WOnyDmnKwg6Y2L54mpkgEKcmVzdGF1cmFudA?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E5%BE%A1%E9%BC%8E%E6%B9%AF-%E5%8E%9F%E6%9C%AC%E9%8D%8B%E7%89%A9-1944563872330819/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/%E5%BE%A1%E9%BC%8E%E6%B9%AF-%E5%8E%9F%E6%9C%AC%E9%8D%8B%E7%89%A9-1944563872330819/menu/"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://bobowin.blog/linkou-hot-pot/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>展悅浮島咖啡館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路二段455號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00 ~ 20:30 週一公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-展悅浮島.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.coredesignstrategy.com/resturantconsultant"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://bobowin.blog/linkou-bistronomy/"&gt;推薦&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3705,7 +3811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3726,6 +3832,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4041,7 +4149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4096,7 +4204,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="112">
+    <row r="2" spans="1:12" ht="144">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -4172,7 +4280,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80">
+    <row r="4" spans="1:12" ht="96">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4286,7 +4394,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80">
+    <row r="7" spans="1:12" ht="96">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -4438,7 +4546,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="128">
+    <row r="11" spans="1:12" ht="144">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -4572,7 +4680,7 @@
         <v>218</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>731</v>
+        <v>857</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>226</v>
@@ -4592,694 +4700,694 @@
     </row>
     <row r="15" spans="1:12" ht="80">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>804</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C15" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>364</v>
+        <v>855</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>856</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>362</v>
+        <v>858</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>860</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>519</v>
+        <v>861</v>
       </c>
       <c r="K15" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
-        <v>68</v>
+        <v>862</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>453</v>
+        <v>863</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>333</v>
+        <v>864</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>334</v>
+        <v>865</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>866</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>335</v>
+        <v>867</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>869</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>520</v>
+        <v>870</v>
       </c>
       <c r="K16" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="96">
+        <v>4.7</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>871</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>643</v>
+        <v>872</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>347</v>
+        <v>873</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>349</v>
+        <v>602</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>874</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>350</v>
+        <v>875</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>521</v>
+        <v>877</v>
       </c>
       <c r="K17" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>642</v>
+        <v>4.3</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>449</v>
+        <v>361</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>351</v>
+        <v>718</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="96">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="K19" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="96">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>327</v>
+        <v>643</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K20" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K21" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="96">
       <c r="A22" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="K22" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="96">
       <c r="A23" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>450</v>
+        <v>327</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K23" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
-        <v>457</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>853</v>
+        <v>525</v>
       </c>
       <c r="K24" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="64">
       <c r="A25" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>507</v>
+        <v>337</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="K25" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="80">
+      <c r="A26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="K26" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="80">
+      <c r="A27" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="K27" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="64">
+      <c r="A28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="G28" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>304</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="K25" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="96">
-      <c r="A26" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="K26" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="64">
-      <c r="A27" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="K27" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="80">
-      <c r="A28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K28" s="10">
-        <v>3.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="64">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="96">
       <c r="A29" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>152</v>
+        <v>297</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>155</v>
+        <v>299</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>156</v>
+        <v>742</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="K29" s="10">
         <v>4.2</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="96">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="64">
       <c r="A30" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>161</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K30" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="96">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="80">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>450</v>
+        <v>183</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K31" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="96">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="64">
       <c r="A32" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K32" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="112">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="96">
       <c r="A33" s="1" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>447</v>
@@ -5288,2469 +5396,2583 @@
         <v>153</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>161</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="K33" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="128">
+        <v>3.9</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="96">
       <c r="A34" s="1" t="s">
-        <v>458</v>
+        <v>127</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>454</v>
+        <v>178</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>94</v>
+        <v>747</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="K34" s="10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="112">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="96">
       <c r="A35" s="1" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>489</v>
+        <v>188</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>114</v>
+        <v>748</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="K35" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="128">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="112">
       <c r="A36" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>490</v>
+        <v>192</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>117</v>
+        <v>749</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="K36" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="128">
       <c r="A37" s="1" t="s">
-        <v>157</v>
+        <v>458</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>164</v>
+        <v>488</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>167</v>
+        <v>722</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="K37" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="64">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="112">
       <c r="A38" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>450</v>
+        <v>489</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>172</v>
+        <v>750</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="K38" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="80">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="128">
       <c r="A39" s="1" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>146</v>
+        <v>490</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>149</v>
+        <v>15</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>150</v>
+        <v>751</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K39" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="144">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="112">
       <c r="A40" s="1" t="s">
-        <v>843</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>844</v>
+        <v>164</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>845</v>
+        <v>448</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>849</v>
+        <v>165</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>467</v>
+        <v>166</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>851</v>
+        <v>752</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>846</v>
+        <v>167</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>852</v>
+        <v>539</v>
       </c>
       <c r="K40" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="80">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="64">
       <c r="A41" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>448</v>
+        <v>169</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>412</v>
+        <v>165</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>122</v>
+        <v>753</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="K41" s="10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="48">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="80">
       <c r="A42" s="1" t="s">
-        <v>599</v>
+        <v>168</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>600</v>
+        <v>146</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>601</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>602</v>
+        <v>148</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>603</v>
+        <v>149</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>604</v>
+        <v>849</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>605</v>
+        <v>540</v>
       </c>
       <c r="K42" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="80">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="144">
       <c r="A43" s="1" t="s">
-        <v>824</v>
+        <v>842</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>452</v>
+        <v>844</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>829</v>
+        <v>848</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>830</v>
+        <v>467</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>827</v>
+        <v>850</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>845</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="K43" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="128">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="80">
       <c r="A44" s="1" t="s">
-        <v>833</v>
+        <v>173</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>835</v>
+        <v>119</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>838</v>
+        <v>412</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>839</v>
+        <v>120</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>840</v>
+        <v>121</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>836</v>
+        <v>754</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>841</v>
+        <v>566</v>
       </c>
       <c r="K44" s="10">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="64">
+        <v>3.5</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="48">
       <c r="A45" s="1" t="s">
-        <v>177</v>
+        <v>599</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>491</v>
+        <v>600</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>414</v>
+        <v>601</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>128</v>
+        <v>602</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>603</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>130</v>
+        <v>824</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>604</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>567</v>
+        <v>605</v>
       </c>
       <c r="K45" s="10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="80">
       <c r="A46" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="K46" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="128">
+      <c r="A47" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="K47" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="64">
+      <c r="A48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="K48" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="80">
+      <c r="A49" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G49" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="K49" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="80">
+      <c r="A50" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K46" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="80">
-      <c r="A47" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="H50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K50" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="80">
+      <c r="A51" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="K47" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="80">
-      <c r="A48" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H48" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="K48" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="48">
-      <c r="A49" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="K49" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="64">
-      <c r="A50" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="K50" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="64">
-      <c r="A51" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K51" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="48">
       <c r="A52" s="1" t="s">
-        <v>211</v>
+        <v>459</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K52" s="10">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="48">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="64">
       <c r="A53" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>448</v>
+        <v>285</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="K53" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="64">
       <c r="A54" s="1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="K54" s="10">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="48">
       <c r="A55" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K55" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="96">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K56" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="48">
       <c r="A57" s="1" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K57" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="48">
       <c r="A58" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="K58" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="64">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="96">
       <c r="A59" s="1" t="s">
-        <v>805</v>
+        <v>228</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>812</v>
+        <v>255</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>813</v>
+        <v>256</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>814</v>
+        <v>257</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>809</v>
+        <v>259</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>808</v>
+        <v>766</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>807</v>
+        <v>258</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>811</v>
+        <v>547</v>
       </c>
       <c r="K59" s="10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="64">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="80">
       <c r="A60" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>420</v>
+        <v>246</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>15</v>
+        <v>247</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>39</v>
+        <v>767</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>411</v>
+        <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>573</v>
+        <v>548</v>
       </c>
       <c r="K60" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="80">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>421</v>
+        <v>283</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>29</v>
+        <v>284</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>281</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>30</v>
+        <v>768</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>282</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>411</v>
+        <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="K61" s="10">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="64">
       <c r="A62" s="1" t="s">
-        <v>314</v>
+        <v>804</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>449</v>
+        <v>805</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>811</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>437</v>
+        <v>812</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>80</v>
+        <v>813</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>808</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>81</v>
+        <v>807</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>806</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>411</v>
+        <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>575</v>
+        <v>810</v>
       </c>
       <c r="K62" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="112">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="64">
       <c r="A63" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>447</v>
+        <v>37</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="K63" s="10">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="80">
       <c r="A64" s="1" t="s">
-        <v>233</v>
+        <v>460</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>453</v>
+        <v>27</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K64" s="10">
         <v>4.3</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="64">
       <c r="A65" s="1" t="s">
-        <v>234</v>
+        <v>314</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>55</v>
+        <v>499</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="K65" s="10">
         <v>3.8</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="112">
       <c r="A66" s="1" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>452</v>
+        <v>494</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="K66" s="10">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="112">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="80">
       <c r="A67" s="1" t="s">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>452</v>
+        <v>50</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K67" s="10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="48">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="64">
       <c r="A68" s="1" t="s">
-        <v>461</v>
+        <v>234</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>497</v>
+        <v>55</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>551</v>
+        <v>578</v>
       </c>
       <c r="K68" s="10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="144">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="80">
       <c r="A69" s="1" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>449</v>
+        <v>495</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>476</v>
+        <v>41</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>477</v>
+        <v>775</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K69" s="10">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="64">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="112">
       <c r="A70" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="K70" s="10">
         <v>3.9</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="96">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="48">
       <c r="A71" s="1" t="s">
-        <v>308</v>
+        <v>461</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>467</v>
+        <v>62</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>468</v>
+        <v>777</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="K71" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="144">
       <c r="A72" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="K72" s="10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="48">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="64">
       <c r="A73" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>22</v>
+        <v>498</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>552</v>
+        <v>581</v>
       </c>
       <c r="K73" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="80">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="96">
       <c r="A74" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>66</v>
+        <v>464</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>42</v>
+        <v>466</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>467</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>25</v>
+        <v>780</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>468</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="K74" s="10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>74</v>
+        <v>478</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>76</v>
+        <v>480</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>77</v>
+        <v>781</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="K75" s="10">
         <v>4</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="48">
       <c r="A76" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>449</v>
+        <v>22</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K76" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="48">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="80">
       <c r="A77" s="1" t="s">
-        <v>606</v>
+        <v>311</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>607</v>
+        <v>66</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>609</v>
+        <v>417</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>610</v>
+        <v>67</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>611</v>
+        <v>42</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>608</v>
+        <v>783</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="K77" s="10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="32">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="64">
       <c r="A78" s="1" t="s">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>450</v>
+        <v>74</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K78" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="48">
       <c r="A79" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>291</v>
+        <v>69</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>292</v>
+        <v>444</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>294</v>
+        <v>70</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>295</v>
+        <v>785</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="K79" s="10">
-        <v>4.4000000000000004</v>
+        <v>3.8</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="48">
       <c r="A80" s="1" t="s">
-        <v>316</v>
+        <v>606</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C80" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="K80" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="32">
+      <c r="A81" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D80" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="K80" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="96">
-      <c r="A81" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>452</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="K81" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="64">
       <c r="A82" s="1" t="s">
-        <v>502</v>
+        <v>315</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>503</v>
+        <v>291</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>504</v>
+        <v>292</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>467</v>
+        <v>293</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>506</v>
+        <v>295</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="K82" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="112">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>394</v>
+        <v>316</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>471</v>
+        <v>406</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>409</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>472</v>
+        <v>408</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>588</v>
+        <v>554</v>
       </c>
       <c r="K83" s="10">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="96">
       <c r="A84" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>448</v>
+        <v>8</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K84" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>396</v>
+        <v>502</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>427</v>
+        <v>504</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>46</v>
+        <v>505</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>47</v>
+        <v>467</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>48</v>
+        <v>791</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="K85" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="48">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="112">
       <c r="A86" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>87</v>
+        <v>469</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>42</v>
+        <v>471</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>89</v>
+        <v>792</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="K86" s="10"/>
+        <v>588</v>
+      </c>
+      <c r="K86" s="10">
+        <v>3.3</v>
+      </c>
       <c r="L86" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="96">
       <c r="A87" s="1" t="s">
-        <v>805</v>
+        <v>395</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>815</v>
+        <v>13</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>817</v>
+        <v>426</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>388</v>
+        <v>15</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>820</v>
+        <v>793</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>823</v>
+        <v>557</v>
       </c>
       <c r="K87" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>821</v>
+        <v>4.3</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="64">
       <c r="A88" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>450</v>
+        <v>501</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>376</v>
+        <v>46</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>377</v>
+        <v>720</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K88" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="48">
       <c r="A89" s="1" t="s">
-        <v>593</v>
+        <v>397</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>450</v>
+        <v>87</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>595</v>
+        <v>428</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>596</v>
+        <v>88</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>597</v>
+        <v>817</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="K89" s="10">
-        <v>4.4000000000000004</v>
-      </c>
+        <v>821</v>
+      </c>
+      <c r="K89" s="10"/>
       <c r="L89" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="96">
       <c r="A90" s="1" t="s">
-        <v>399</v>
+        <v>804</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>450</v>
+        <v>814</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>373</v>
+        <v>815</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>371</v>
+        <v>819</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>591</v>
+        <v>822</v>
       </c>
       <c r="K90" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="48">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="64">
       <c r="A91" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="K91" s="10">
-        <v>3.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>462</v>
+        <v>593</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>386</v>
+        <v>594</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>432</v>
+        <v>595</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>388</v>
+        <v>596</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>385</v>
+        <v>597</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
       <c r="K92" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="96">
       <c r="A93" s="1" t="s">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K93" s="10">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="48">
       <c r="A94" s="1" t="s">
-        <v>483</v>
+        <v>400</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K94" s="10">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K95" s="10">
         <v>4.3</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="96">
       <c r="A96" s="1" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="K96" s="10">
-        <v>4.4000000000000004</v>
+        <v>3.8</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>613</v>
+        <v>483</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>615</v>
+        <v>402</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>616</v>
+        <v>405</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>617</v>
+        <v>404</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>618</v>
+        <v>403</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="K97" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="48">
+      <c r="A98" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="K98" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="48">
+      <c r="A99" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K99" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="48">
+      <c r="A100" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J100" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K97" s="10">
+      <c r="K100" s="10">
         <v>3.4</v>
       </c>
-      <c r="L97" s="2" t="s">
+      <c r="L100" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J96">
-    <sortCondition ref="I2:I96"/>
-    <sortCondition ref="D2:D96"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J99">
+    <sortCondition ref="I2:I99"/>
+    <sortCondition ref="D2:D99"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H39" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H29" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H37" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H27" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H38" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H30" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H31" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H32" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H28" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H33" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H42" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H32" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H40" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H30" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H41" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H33" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H34" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H35" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H31" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H36" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -7758,55 +7980,60 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H55" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H53" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H57" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H54" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H56" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H49" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H48" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H52" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H51" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H58" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H50" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H79" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H26" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H25" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H19" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H21" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H20" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H16" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H22" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H24" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H17" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H18" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H23" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H15" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H96" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H90" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H88" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H91" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H92" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H93" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H94" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H80" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H71" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H83" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H69" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H72" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H82" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H89" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H42" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H77" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H97" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H59" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H87" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L87" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H43" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L43" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H44" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L44" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H40" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H58" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H56" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H60" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H57" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H59" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H52" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H51" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H55" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H54" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H61" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H53" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H82" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H29" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H28" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H22" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H24" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H23" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H19" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H25" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H27" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H20" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H21" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H26" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H18" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H99" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H93" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H91" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H94" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H95" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H96" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H97" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H83" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H74" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H86" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H72" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H75" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H85" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H92" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H45" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H80" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H100" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H62" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H90" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L90" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H46" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L46" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H47" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L47" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H43" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H15" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L15" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H16" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L17" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H17" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909764C-6AFB-EB4F-BB83-583B2925E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ABDF25-05BD-5F44-A276-DDFA4589E9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="1160" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3641,13 +3641,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;p&gt;
-   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/Walkin1805/photos/?tab=album&amp;album_id=1801334346625830"&gt;菜單&lt;/a&gt; &amp;nbsp;
-   &lt;a style="button" class="btn btn-info"  href="https://zineblog.com.tw/blog/post/200616"&gt;推薦&lt;/a&gt; &amp;nbsp;
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>106</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3714,6 +3707,13 @@
     <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.coredesignstrategy.com/resturantconsultant"&gt;菜單&lt;/a&gt; &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://bobowin.blog/linkou-bistronomy/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/Walkin1805/photos/?tab=album&amp;album_id=1801334346625830"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://bobowin.blog/walk-in-cafe/"&gt;推薦&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4727,7 +4727,7 @@
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>861</v>
+        <v>877</v>
       </c>
       <c r="K15" s="10">
         <v>4.3</v>
@@ -4738,63 +4738,63 @@
     </row>
     <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>862</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>863</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>867</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K16" s="10">
         <v>4.7</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>871</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>872</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>602</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>874</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>875</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>604</v>
@@ -4803,13 +4803,13 @@
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K17" s="10">
         <v>4.3</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ABDF25-05BD-5F44-A276-DDFA4589E9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A646E07F-A54F-8549-9DA9-C3970E98CA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="4400" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="887">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3714,6 +3714,45 @@
     <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/Walkin1805/photos/?tab=album&amp;album_id=1801334346625830"&gt;菜單&lt;/a&gt; &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://bobowin.blog/walk-in-cafe/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-舒芙蕾.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>108</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜蒔吇舒芙蕾咖啡專賣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化二路一段78號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2606-8806</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一-五｜ 11:30-21:00 , 六日與例假日 ｜ 11:30-21:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/souffle.coffee/posts/360088805738952</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/souffle.coffee/photos/pcb.315664340181399/342531914161308"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://angelababy.tw/post-522856846/"&gt;推薦&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4149,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4700,694 +4739,694 @@
     </row>
     <row r="15" spans="1:12" ht="80">
       <c r="A15" s="1" t="s">
-        <v>804</v>
+        <v>879</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="K15" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>452</v>
+        <v>853</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="K16" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>450</v>
+        <v>862</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>602</v>
+        <v>864</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>604</v>
+        <v>868</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="K17" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="64">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>870</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C18" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>718</v>
+        <v>872</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>364</v>
+        <v>602</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>873</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>362</v>
+        <v>874</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>519</v>
+        <v>876</v>
       </c>
       <c r="K18" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="80">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>453</v>
+        <v>361</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>333</v>
+        <v>718</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K19" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="96">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="64">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>643</v>
+        <v>332</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K20" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="80">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="96">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>355</v>
+        <v>643</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K21" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="96">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K22" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="96">
       <c r="A23" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K23" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="96">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K24" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="80">
       <c r="A25" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="K25" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="80">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="64">
       <c r="A26" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>450</v>
+        <v>337</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="K26" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="80">
       <c r="A27" s="1" t="s">
-        <v>457</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>447</v>
+        <v>356</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>852</v>
+        <v>526</v>
       </c>
       <c r="K27" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="64">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="80">
       <c r="A28" s="1" t="s">
-        <v>102</v>
+        <v>457</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>507</v>
+        <v>342</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>111</v>
+        <v>305</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>527</v>
+        <v>852</v>
       </c>
       <c r="K28" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="96">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="64">
       <c r="A29" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>297</v>
+        <v>507</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>413</v>
+        <v>301</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K29" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="64">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="96">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>159</v>
+        <v>413</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>161</v>
+        <v>299</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>162</v>
+        <v>742</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K30" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="80">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="64">
       <c r="A31" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>448</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K31" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="64">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="80">
       <c r="A32" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="K32" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="96">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="64">
       <c r="A33" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>447</v>
@@ -5396,226 +5435,226 @@
         <v>153</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K33" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="96">
       <c r="A34" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>450</v>
+        <v>174</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K34" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="96">
       <c r="A35" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>448</v>
+        <v>178</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K35" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="112">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="96">
       <c r="A36" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K36" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="112">
       <c r="A37" s="1" t="s">
-        <v>458</v>
+        <v>136</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>488</v>
+        <v>192</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>94</v>
+        <v>749</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K37" s="10">
-        <v>4</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="128">
       <c r="A38" s="1" t="s">
-        <v>145</v>
+        <v>458</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>750</v>
+        <v>722</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K38" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="128">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="112">
       <c r="A39" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>449</v>
@@ -5624,1454 +5663,1454 @@
         <v>108</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K39" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="112">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="128">
       <c r="A40" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>164</v>
+        <v>490</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>167</v>
+        <v>751</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K40" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="64">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="112">
       <c r="A41" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>450</v>
+        <v>164</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K41" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="80">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="64">
       <c r="A42" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>453</v>
+        <v>169</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>849</v>
+        <v>753</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K42" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="144">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="80">
       <c r="A43" s="1" t="s">
-        <v>842</v>
+        <v>168</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>843</v>
+        <v>146</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>844</v>
+        <v>453</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>847</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>848</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>467</v>
+        <v>149</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>845</v>
+        <v>150</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>851</v>
+        <v>540</v>
       </c>
       <c r="K43" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="80">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="144">
       <c r="A44" s="1" t="s">
-        <v>173</v>
+        <v>842</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>119</v>
+        <v>843</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>448</v>
+        <v>844</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>412</v>
+        <v>847</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>120</v>
+        <v>848</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>121</v>
+        <v>467</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>122</v>
+        <v>850</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>845</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>566</v>
+        <v>851</v>
       </c>
       <c r="K44" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="48">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="80">
       <c r="A45" s="1" t="s">
-        <v>599</v>
+        <v>173</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>600</v>
+        <v>119</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>601</v>
+        <v>412</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>602</v>
+        <v>120</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>603</v>
+        <v>121</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>604</v>
+        <v>754</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="K45" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="80">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="48">
       <c r="A46" s="1" t="s">
-        <v>823</v>
+        <v>599</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>833</v>
+        <v>600</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>827</v>
+        <v>601</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>828</v>
+        <v>602</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>829</v>
+        <v>603</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>826</v>
+        <v>604</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>831</v>
+        <v>605</v>
       </c>
       <c r="K46" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="80">
       <c r="A47" s="1" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="K47" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="128">
+      <c r="A48" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J48" s="7" t="s">
         <v>840</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K48" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L47" s="6" t="s">
+      <c r="L48" s="6" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="64">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:12" ht="64">
+      <c r="A49" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="K48" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="80">
-      <c r="A49" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K49" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="80">
       <c r="A50" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K50" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="80">
       <c r="A51" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K51" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="80">
+      <c r="A52" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F52" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="K51" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="48">
-      <c r="A52" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K52" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="64">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="48">
       <c r="A53" s="1" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="K53" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="64">
       <c r="A54" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K54" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="64">
       <c r="A55" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K55" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>448</v>
+        <v>270</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K56" s="10">
         <v>4.3</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="48">
       <c r="A57" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K57" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="48">
       <c r="A58" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K58" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="96">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="48">
       <c r="A59" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>449</v>
+        <v>235</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K59" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="96">
       <c r="A60" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K60" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="80">
       <c r="A61" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K61" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="48">
       <c r="A62" s="1" t="s">
-        <v>804</v>
+        <v>230</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>805</v>
+        <v>280</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>811</v>
+        <v>450</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>812</v>
+        <v>283</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>813</v>
+        <v>284</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>808</v>
+        <v>281</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>807</v>
+        <v>768</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>806</v>
+        <v>282</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>810</v>
+        <v>549</v>
       </c>
       <c r="K62" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>809</v>
+        <v>681</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="64">
       <c r="A63" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="K63" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="64">
+      <c r="A64" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="K63" s="10">
-        <v>4</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="80">
-      <c r="A64" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K64" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="80">
       <c r="A65" s="1" t="s">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K65" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="112">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="64">
       <c r="A66" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K66" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="112">
       <c r="A67" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>50</v>
+        <v>494</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K67" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="80">
       <c r="A68" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K68" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="64">
       <c r="A69" s="1" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="K69" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="112">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="80">
       <c r="A70" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="K70" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="48">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="112">
       <c r="A71" s="1" t="s">
-        <v>461</v>
+        <v>296</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="K71" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="144">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="48">
       <c r="A72" s="1" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>476</v>
+        <v>62</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>477</v>
+        <v>777</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="K72" s="10">
         <v>4.2</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="144">
       <c r="A73" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>33</v>
+        <v>475</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>34</v>
+        <v>778</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K73" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="96">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="64">
       <c r="A74" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>467</v>
+        <v>32</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>468</v>
+        <v>779</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K74" s="10">
         <v>3.9</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="64">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="96">
       <c r="A75" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K75" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="48">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="64">
       <c r="A76" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>452</v>
+        <v>478</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>24</v>
+        <v>480</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>25</v>
+        <v>781</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="K76" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="80">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="48">
       <c r="A77" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>447</v>
+        <v>22</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>25</v>
@@ -7080,899 +7119,937 @@
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="K77" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="64">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="80">
       <c r="A78" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K78" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="48">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="64">
       <c r="A79" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K79" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="48">
       <c r="A80" s="1" t="s">
-        <v>606</v>
+        <v>313</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>607</v>
+        <v>69</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>609</v>
+        <v>444</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>610</v>
+        <v>70</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>608</v>
+        <v>785</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J80" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K80" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="48">
+      <c r="A81" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J81" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K80" s="10">
+      <c r="K81" s="10">
         <v>4.2</v>
       </c>
-      <c r="L80" s="2" t="s">
+      <c r="L81" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="32">
-      <c r="A81" s="1" t="s">
+    <row r="82" spans="1:12" ht="32">
+      <c r="A82" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C82" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G82" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H82" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="K81" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
-      <c r="A82" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J82" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="K82" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="64">
+      <c r="A83" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="K82" s="10">
+      <c r="K83" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="48">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:12" ht="48">
+      <c r="A84" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C84" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D84" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E84" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F84" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G84" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H83" s="6" t="s">
+      <c r="H84" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="I83" s="2" t="s">
+      <c r="I84" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="J83" s="7" t="s">
+      <c r="J84" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K84" s="10">
         <v>4.5</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="96">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:12" ht="96">
+      <c r="A85" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H85" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="K84" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="64">
-      <c r="A85" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K85" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="112">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="64">
       <c r="A86" s="1" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>368</v>
+        <v>505</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="K86" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="112">
       <c r="A87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>13</v>
+        <v>469</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>15</v>
+        <v>471</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>16</v>
+        <v>792</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="K87" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="64">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="96">
       <c r="A88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>720</v>
+        <v>793</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="K88" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="48">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="64">
       <c r="A89" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="K89" s="10"/>
+        <v>589</v>
+      </c>
+      <c r="K89" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L89" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="96">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="48">
       <c r="A90" s="1" t="s">
-        <v>804</v>
+        <v>397</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>814</v>
+        <v>87</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>816</v>
+        <v>428</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>388</v>
+        <v>42</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K90" s="10"/>
+      <c r="L90" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="96">
+      <c r="A91" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" s="7" t="s">
         <v>822</v>
-      </c>
-      <c r="K90" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="64">
-      <c r="A91" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>590</v>
       </c>
       <c r="K91" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L91" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="48">
+      <c r="L91" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="64">
       <c r="A92" s="1" t="s">
-        <v>593</v>
+        <v>398</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>594</v>
+        <v>374</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>596</v>
+        <v>375</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K92" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="96">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="48">
       <c r="A93" s="1" t="s">
-        <v>399</v>
+        <v>593</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>373</v>
+        <v>596</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>371</v>
+        <v>597</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K93" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="48">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="96">
       <c r="A94" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="K94" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K95" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="48">
       <c r="A96" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="K96" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="96">
       <c r="A97" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="K97" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="48">
       <c r="A98" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K98" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>369</v>
+        <v>801</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K99" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>613</v>
+        <v>485</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>615</v>
+        <v>366</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>616</v>
+        <v>367</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>618</v>
+        <v>369</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J100" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K100" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="48">
+      <c r="A101" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J101" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K100" s="10">
+      <c r="K101" s="10">
         <v>3.4</v>
       </c>
-      <c r="L100" s="2" t="s">
+      <c r="L101" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J99">
-    <sortCondition ref="I2:I99"/>
-    <sortCondition ref="D2:D99"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J100">
+    <sortCondition ref="I2:I100"/>
+    <sortCondition ref="D2:D100"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H42" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H32" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H40" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H30" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H41" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H33" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H34" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H35" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H31" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H36" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H43" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H33" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H41" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H31" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H42" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H34" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H35" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H36" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H32" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H37" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -7980,60 +8057,62 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H58" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H56" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H60" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H57" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H59" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H52" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H51" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H55" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H54" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H61" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H53" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H82" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H29" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H28" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H22" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H24" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H23" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H19" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H25" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H27" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H20" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H21" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H26" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H18" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H99" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H93" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H91" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H94" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H95" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H96" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H97" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H83" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H74" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H86" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H72" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H75" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H85" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H92" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H45" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H80" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H100" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H62" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H90" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L90" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H46" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L46" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H47" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L47" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H43" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H15" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L15" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H16" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L17" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H17" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H59" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H57" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H61" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H58" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H60" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H53" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H52" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H56" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H55" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H62" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H54" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H83" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H30" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H29" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H23" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H25" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H24" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H20" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H26" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H28" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H21" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H22" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H27" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H19" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H100" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H94" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H92" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H95" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H96" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H97" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H98" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H84" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H75" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H87" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H73" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H76" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H86" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H93" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H46" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H81" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H101" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H63" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H91" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L91" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H47" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L47" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H48" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L48" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H44" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H16" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L16" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H17" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L18" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H18" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H15" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L15" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A646E07F-A54F-8549-9DA9-C3970E98CA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF81A2F-54DE-2640-BEDA-29E257D2589F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4400" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="720" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="895">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3753,6 +3753,41 @@
     <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/souffle.coffee/photos/pcb.315664340181399/342531914161308"&gt;菜單&lt;/a&gt; &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://angelababy.tw/post-522856846/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哇草手創湯包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興北路68號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-1119</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 - 21:00 週二公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E5%93%87%E8%8D%89-%E6%89%8B%E5%89%B5%E6%B9%AF%E5%8C%85-106679005058415</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E5%93%87%E8%8D%89%E6%89%8B%E5%89%B5%E6%B9%AF%E5%8C%85/@25.0581331,121.3679845,17z/data=!4m5!3m4!1s0x3442a7ecfbdee3bd:0xb8557ebc92d5d538!8m2!3d25.0581331!4d121.3701732?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-哇草手創湯包.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/nsnx/wa-cao-shou-chuang-tang-bao"&gt;菜單&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/100002779066561/videos/pcb.3711669585602307/388272802895151"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4188,7 +4223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4243,7 +4278,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="144">
+    <row r="2" spans="1:12" ht="112">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -4319,7 +4354,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="96">
+    <row r="4" spans="1:12" ht="80">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4433,7 +4468,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="96">
+    <row r="7" spans="1:12" ht="80">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -4585,7 +4620,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="144">
+    <row r="11" spans="1:12" ht="128">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -7658,384 +7693,422 @@
         <v>820</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="64">
+    <row r="92" spans="1:12" ht="96">
       <c r="A92" s="1" t="s">
-        <v>398</v>
+        <v>879</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>450</v>
+        <v>887</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>376</v>
+        <v>888</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>890</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>794</v>
+        <v>893</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>377</v>
+        <v>891</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>590</v>
+        <v>894</v>
       </c>
       <c r="K92" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="64">
       <c r="A93" s="1" t="s">
-        <v>593</v>
+        <v>398</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>594</v>
+        <v>374</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>596</v>
+        <v>375</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K93" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="96">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="48">
       <c r="A94" s="1" t="s">
-        <v>399</v>
+        <v>593</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>373</v>
+        <v>596</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>371</v>
+        <v>597</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K94" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="48">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="96">
       <c r="A95" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="K95" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="48">
       <c r="A96" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K96" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="K97" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="96">
       <c r="A98" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="K98" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K99" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>369</v>
+        <v>801</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K100" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>613</v>
+        <v>485</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>615</v>
+        <v>366</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>616</v>
+        <v>367</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>618</v>
+        <v>369</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J101" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K101" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="48">
+      <c r="A102" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J102" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K101" s="10">
+      <c r="K102" s="10">
         <v>3.4</v>
       </c>
-      <c r="L101" s="2" t="s">
+      <c r="L102" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J100">
-    <sortCondition ref="I2:I100"/>
-    <sortCondition ref="D2:D100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J101">
+    <sortCondition ref="I2:I101"/>
+    <sortCondition ref="D2:D101"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8081,23 +8154,23 @@
     <hyperlink ref="H22" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H27" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H19" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H100" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H94" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H92" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H95" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H96" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H97" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H98" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H101" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H95" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H93" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H96" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H97" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H98" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H99" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
     <hyperlink ref="H84" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
     <hyperlink ref="H75" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
     <hyperlink ref="H87" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
     <hyperlink ref="H73" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
     <hyperlink ref="H76" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
     <hyperlink ref="H86" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H93" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H94" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
     <hyperlink ref="H46" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
     <hyperlink ref="H81" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H101" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H102" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
     <hyperlink ref="H63" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
     <hyperlink ref="H91" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
     <hyperlink ref="L91" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
@@ -8113,6 +8186,8 @@
     <hyperlink ref="H18" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
     <hyperlink ref="H15" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
     <hyperlink ref="L15" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H92" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L92" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF81A2F-54DE-2640-BEDA-29E257D2589F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356BAF8A-F03A-0945-88D8-7C32BE7E3FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="904">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3788,6 +3788,46 @@
     <t>&lt;p&gt;
   網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/nsnx/wa-cao-shou-chuang-tang-bao"&gt;菜單&lt;/a&gt;   &amp;nbsp;
    &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/100002779066561/videos/pcb.3711669585602307/388272802895151"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>109</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陶板屋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛路二段500號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2602-6950</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30 - 14:30, 17:30 - 22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-陶板屋.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tokiya.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E9%99%B6%E6%9D%BF%E5%B1%8B+%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.076312,121.3734869,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7a6d919d43f:0x26211c888256b831!8m2!3d25.0763135!4d121.3756823?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.tokiya.com.tw/menu.html"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://threeonelee.com/tokiya/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://cct.wowprime.com/cct/cctapp/cctwebreservation.do?&amp;prog=cctweb_reservation&amp;brnd_fid=ZMJYW&amp;stor=108043"&gt;訂餐&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4223,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4772,734 +4812,734 @@
         <v>639</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="80">
+    <row r="15" spans="1:12" ht="112">
       <c r="A15" s="1" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>878</v>
+        <v>900</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="K15" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
-        <v>804</v>
+        <v>879</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="K16" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>452</v>
+        <v>853</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="K17" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>450</v>
+        <v>862</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>602</v>
+        <v>864</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>604</v>
+        <v>868</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>870</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C19" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>718</v>
+        <v>872</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>364</v>
+        <v>602</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>873</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>362</v>
+        <v>874</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>519</v>
+        <v>876</v>
       </c>
       <c r="K19" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="80">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>453</v>
+        <v>361</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>333</v>
+        <v>718</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K20" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="96">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="64">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>643</v>
+        <v>332</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K21" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="80">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="96">
       <c r="A22" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>355</v>
+        <v>643</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K22" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="96">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="80">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K23" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="96">
       <c r="A24" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K24" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="96">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K25" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="80">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="K26" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="80">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="64">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>450</v>
+        <v>337</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="K27" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="80">
       <c r="A28" s="1" t="s">
-        <v>457</v>
+        <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>447</v>
+        <v>356</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>852</v>
+        <v>526</v>
       </c>
       <c r="K28" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="64">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="80">
       <c r="A29" s="1" t="s">
-        <v>102</v>
+        <v>457</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>507</v>
+        <v>342</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>111</v>
+        <v>305</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>527</v>
+        <v>852</v>
       </c>
       <c r="K29" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="96">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="64">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>297</v>
+        <v>507</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>413</v>
+        <v>301</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K30" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="64">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="96">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>159</v>
+        <v>413</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>161</v>
+        <v>299</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>162</v>
+        <v>742</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K31" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="80">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="64">
       <c r="A32" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>448</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K32" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="64">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="80">
       <c r="A33" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="K33" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="96">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="64">
       <c r="A34" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>447</v>
@@ -5508,226 +5548,226 @@
         <v>153</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K34" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="96">
       <c r="A35" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>450</v>
+        <v>174</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K35" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="96">
       <c r="A36" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>448</v>
+        <v>178</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K36" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="112">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="96">
       <c r="A37" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K37" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="112">
       <c r="A38" s="1" t="s">
-        <v>458</v>
+        <v>136</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>488</v>
+        <v>192</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>94</v>
+        <v>749</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K38" s="10">
-        <v>4</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="128">
       <c r="A39" s="1" t="s">
-        <v>145</v>
+        <v>458</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>750</v>
+        <v>722</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K39" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="128">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="112">
       <c r="A40" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>449</v>
@@ -5736,1454 +5776,1454 @@
         <v>108</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K40" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="112">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="128">
       <c r="A41" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>164</v>
+        <v>490</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>167</v>
+        <v>751</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K41" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="64">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="112">
       <c r="A42" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>450</v>
+        <v>164</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K42" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="80">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="64">
       <c r="A43" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>453</v>
+        <v>169</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>849</v>
+        <v>753</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K43" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="144">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="80">
       <c r="A44" s="1" t="s">
-        <v>842</v>
+        <v>168</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>843</v>
+        <v>146</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>844</v>
+        <v>453</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>847</v>
+        <v>147</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>848</v>
+        <v>148</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>467</v>
+        <v>149</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>845</v>
+        <v>150</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>851</v>
+        <v>540</v>
       </c>
       <c r="K44" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="80">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="144">
       <c r="A45" s="1" t="s">
-        <v>173</v>
+        <v>842</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>119</v>
+        <v>843</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>448</v>
+        <v>844</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>412</v>
+        <v>847</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>848</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>121</v>
+        <v>467</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>122</v>
+        <v>850</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>845</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>566</v>
+        <v>851</v>
       </c>
       <c r="K45" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="48">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="80">
       <c r="A46" s="1" t="s">
-        <v>599</v>
+        <v>173</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>600</v>
+        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>601</v>
+        <v>412</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>602</v>
+        <v>120</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>603</v>
+        <v>121</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>604</v>
+        <v>754</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="K46" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="80">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="48">
       <c r="A47" s="1" t="s">
-        <v>823</v>
+        <v>599</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>833</v>
+        <v>600</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>827</v>
+        <v>601</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>828</v>
+        <v>602</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>829</v>
+        <v>603</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>826</v>
+        <v>604</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>831</v>
+        <v>605</v>
       </c>
       <c r="K47" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="80">
       <c r="A48" s="1" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="K48" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="128">
+      <c r="A49" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J49" s="7" t="s">
         <v>840</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K49" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L48" s="6" t="s">
+      <c r="L49" s="6" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="64">
-      <c r="A49" s="1" t="s">
+    <row r="50" spans="1:12" ht="64">
+      <c r="A50" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="K49" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="80">
-      <c r="A50" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K50" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="80">
       <c r="A51" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K51" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="80">
       <c r="A52" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K52" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="80">
+      <c r="A53" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F53" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="K52" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="48">
-      <c r="A53" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K53" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="64">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="48">
       <c r="A54" s="1" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="K54" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="64">
       <c r="A55" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K55" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="64">
       <c r="A56" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K56" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="48">
       <c r="A57" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>448</v>
+        <v>270</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K57" s="10">
         <v>4.3</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="48">
       <c r="A58" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K58" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="48">
       <c r="A59" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K59" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="96">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="48">
       <c r="A60" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>449</v>
+        <v>235</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K60" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="96">
       <c r="A61" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K61" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="80">
       <c r="A62" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K62" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>804</v>
+        <v>230</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>805</v>
+        <v>280</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>811</v>
+        <v>450</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>812</v>
+        <v>283</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>813</v>
+        <v>284</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>808</v>
+        <v>281</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>807</v>
+        <v>768</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>806</v>
+        <v>282</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>810</v>
+        <v>549</v>
       </c>
       <c r="K63" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>809</v>
+        <v>681</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="64">
       <c r="A64" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="K64" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="64">
+      <c r="A65" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="K64" s="10">
-        <v>4</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="80">
-      <c r="A65" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K65" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="80">
       <c r="A66" s="1" t="s">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K66" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="112">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="64">
       <c r="A67" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K67" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="112">
       <c r="A68" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>50</v>
+        <v>494</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K68" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="80">
       <c r="A69" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K69" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="64">
       <c r="A70" s="1" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="K70" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="112">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="80">
       <c r="A71" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="K71" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="48">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="112">
       <c r="A72" s="1" t="s">
-        <v>461</v>
+        <v>296</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="K72" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="144">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="48">
       <c r="A73" s="1" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>476</v>
+        <v>62</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>477</v>
+        <v>777</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="K73" s="10">
         <v>4.2</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="144">
       <c r="A74" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>33</v>
+        <v>475</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>34</v>
+        <v>778</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K74" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="96">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>467</v>
+        <v>32</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>468</v>
+        <v>779</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K75" s="10">
         <v>3.9</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="64">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="96">
       <c r="A76" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K76" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="48">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
       <c r="A77" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>452</v>
+        <v>478</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>24</v>
+        <v>480</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>25</v>
+        <v>781</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="K77" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="80">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="48">
       <c r="A78" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>447</v>
+        <v>22</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>25</v>
@@ -7192,937 +7232,975 @@
         <v>411</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="K78" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="80">
       <c r="A79" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K79" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="48">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="64">
       <c r="A80" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K80" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="48">
       <c r="A81" s="1" t="s">
-        <v>606</v>
+        <v>313</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>607</v>
+        <v>69</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>609</v>
+        <v>444</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>610</v>
+        <v>70</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>608</v>
+        <v>785</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J81" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K81" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="48">
+      <c r="A82" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J82" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K81" s="10">
+      <c r="K82" s="10">
         <v>4.2</v>
       </c>
-      <c r="L81" s="2" t="s">
+      <c r="L82" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="32">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:12" ht="32">
+      <c r="A83" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C83" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G83" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H83" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="K82" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="64">
-      <c r="A83" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J83" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="K83" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="64">
+      <c r="A84" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K84" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="48">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:12" ht="48">
+      <c r="A85" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D85" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E85" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="F85" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H84" s="6" t="s">
+      <c r="H85" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="I84" s="2" t="s">
+      <c r="I85" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="J84" s="7" t="s">
+      <c r="J85" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K85" s="10">
         <v>4.5</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="96">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:12" ht="96">
+      <c r="A86" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="K85" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="64">
-      <c r="A86" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K86" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="112">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="64">
       <c r="A87" s="1" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>368</v>
+        <v>505</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="K87" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="112">
       <c r="A88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>13</v>
+        <v>469</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>15</v>
+        <v>471</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>16</v>
+        <v>792</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="K88" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="64">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="96">
       <c r="A89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>720</v>
+        <v>793</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="K89" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="48">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="64">
       <c r="A90" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="K90" s="10"/>
+        <v>589</v>
+      </c>
+      <c r="K90" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L90" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="96">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="48">
       <c r="A91" s="1" t="s">
-        <v>804</v>
+        <v>397</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>814</v>
+        <v>87</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>816</v>
+        <v>428</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>388</v>
+        <v>42</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="K91" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
+      </c>
+      <c r="K91" s="10"/>
+      <c r="L91" s="2" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="96">
       <c r="A92" s="1" t="s">
-        <v>879</v>
+        <v>804</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>887</v>
+        <v>814</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="K92" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="96">
+      <c r="A93" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E93" s="7" t="s">
         <v>889</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G93" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="H92" s="6" t="s">
+      <c r="H93" s="6" t="s">
         <v>891</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>894</v>
-      </c>
-      <c r="K92" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="64">
-      <c r="A93" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>590</v>
+        <v>894</v>
       </c>
       <c r="K93" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="64">
       <c r="A94" s="1" t="s">
-        <v>593</v>
+        <v>398</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>594</v>
+        <v>374</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>596</v>
+        <v>375</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K94" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="96">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>399</v>
+        <v>593</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>373</v>
+        <v>596</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>371</v>
+        <v>597</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K95" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="48">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="96">
       <c r="A96" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="K96" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K97" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="48">
       <c r="A98" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="K98" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="96">
       <c r="A99" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="K99" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K100" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>369</v>
+        <v>801</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K101" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>613</v>
+        <v>485</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>615</v>
+        <v>366</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>616</v>
+        <v>367</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>618</v>
+        <v>369</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J102" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K102" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="48">
+      <c r="A103" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J103" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K102" s="10">
+      <c r="K103" s="10">
         <v>3.4</v>
       </c>
-      <c r="L102" s="2" t="s">
+      <c r="L103" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J101">
-    <sortCondition ref="I2:I101"/>
-    <sortCondition ref="D2:D101"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J102">
+    <sortCondition ref="I2:I102"/>
+    <sortCondition ref="D2:D102"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H43" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H33" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H41" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H31" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H42" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H34" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H35" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H36" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H32" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H37" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H44" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H34" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H42" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H32" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H43" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H35" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H36" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H37" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H33" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H38" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8130,64 +8208,66 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H59" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H57" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H61" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H58" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H60" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H53" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H52" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H56" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H55" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H62" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H54" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H83" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H30" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H29" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H23" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H25" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H24" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H20" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H26" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H28" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H21" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H22" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H27" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H19" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H101" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H95" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H93" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H96" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H97" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H98" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H99" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H84" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H75" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H87" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H73" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H76" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H86" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H94" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H46" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H81" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H102" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H63" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H91" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L91" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H47" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L47" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H48" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L48" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H44" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H16" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L16" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H17" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L18" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H18" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H15" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L15" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H92" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L92" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H60" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H58" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H62" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H59" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H61" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H54" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H53" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H57" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H56" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H63" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H55" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H84" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H31" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H30" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H24" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H26" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H25" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H21" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H27" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H29" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H22" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H23" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H28" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H20" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H102" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H96" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H94" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H97" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H98" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H99" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H100" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H85" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H76" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H88" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H74" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H77" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H87" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H95" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H47" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H82" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H103" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H64" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H92" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L92" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H48" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L48" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H49" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L49" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H45" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H17" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L17" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H18" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L19" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H19" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H16" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L16" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H93" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L93" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H15" r:id="rId77" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L15" r:id="rId78" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356BAF8A-F03A-0945-88D8-7C32BE7E3FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7606DD4B-116C-6140-9B04-0CD6F0BD6A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="3620" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="912">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3254,9 +3254,6 @@
     <t>fig/XLK-311-Restaurant/AiCity-910-圓明園-02.jpeg</t>
   </si>
   <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-海苑日式.jpg</t>
-  </si>
-  <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-吳氏湯包.jpg</t>
   </si>
   <si>
@@ -3830,6 +3827,44 @@
   &lt;a style="button" class="btn btn-info"  href="https://cct.wowprime.com/cct/cctapp/cctwebreservation.do?&amp;prog=cctweb_reservation&amp;brnd_fid=ZMJYW&amp;stor=108043"&gt;訂餐&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-海苑日式.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-鱸魚湯-01.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>饗叮噹鱸魚湯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.033750933.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興北路6巷65號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0928-873-101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 - 20:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.033750933.com/32654216193375621934.html"&gt;菜單&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/permalink.php?story_fbid=369381218266531&amp;id=108448277693161"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/search?q=%E9%BE%9C%E5%B1%B1%E9%B1%B8%E9%AD%9A%E6%B9%AF&amp;sxsrf=AOaemvJa0u7lJKPsiRcVtRvDZjJyqxtl4Q:1637397953224&amp;source=hp&amp;ei=trWYYbLdOJHrmAXbm4PoCA&amp;iflsig=ALs-wAMAAAAAYZjDxqQGKRPaWKt9BL6Rh_jmWRGiCMWB&amp;ved=2ahUKEwie5O3axqb0AhVIrVYBHQC9AKkQvS56BAgKEDw&amp;uact=5&amp;oq=%E9%BE%9C%E5%B1%B1%E9%B1%B8%E9%AD%9A%E6%B9%AF&amp;gs_lcp=Cgdnd3Mtd2l6EAMyBQgAEM0COgcIIxDqAhAnOg0ILhDHARCvARDqAhAnOgQIIxAnOg4ILhCABBCxAxDHARDRAzoICAAQgAQQsQM6DgguEIAEELEDEMcBEKMCOgUILhCABDoFCAAQgAQ6BAgAEEM6CggAELEDEIMBEEM6CwgAEIAEELEDEIMBOggILhCABBCxAzoLCC4QgAQQxwEQrwE6CAgAELEDEIMBOgsILhCABBCxAxCDAToCCCZQuQ5YlUFgqUdoA3AAeACAAWaIAfsIkgEEMTYuMZgBAKABAbABCg&amp;sclient=gws-wiz&amp;tbs=lf:1,lf_ui:9&amp;tbm=lcl&amp;rflfq=1&amp;num=10&amp;rldimm=11820264403630838222&amp;lqi=Cg_pvpzlsbHpsbjprZrmua9aFCIS6b6cIOWxsSDpsbjprZog5rmvkgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSNWNHUXRNR2RCUlJBQqoBFwoKL20vMDF6MW0xeBABKgciA-a5ryhF&amp;phdesc=dUIbgtEpGm0&amp;rlst=f#rlfi=hd:;si:11820264403630838222,l,Cg_pvpzlsbHpsbjprZrmua9aFCIS6b6cIOWxsSDpsbjprZog5rmvkgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSNWNHUXRNR2RCUlJBQqoBFwoKL20vMDF6MW0xeBABKgciA-a5ryhF,y,dUIbgtEpGm0;mv:[[25.073528099999997,121.4300487],[24.9801288,121.3005194]];tbs:lrf:!1m4!1u3!2m2!3m1!1e1!1m4!1u2!2m2!2m1!1e1!2m1!1e2!2m1!1e3!3sIAE,lf:1,lf_ui:9</t>
   </si>
 </sst>
 </file>
@@ -4263,7 +4298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4794,7 +4829,7 @@
         <v>218</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>226</v>
@@ -4814,177 +4849,177 @@
     </row>
     <row r="15" spans="1:12" ht="112">
       <c r="A15" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>896</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>900</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>901</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="K15" s="10">
         <v>4.3</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>880</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>884</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K16" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>856</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K17" s="10">
         <v>4.3</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>861</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>862</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>866</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K18" s="10">
         <v>4.7</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>870</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>871</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>602</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>874</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>604</v>
@@ -4993,13 +5028,13 @@
         <v>305</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K19" s="10">
         <v>4.3</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="80">
@@ -5373,7 +5408,7 @@
         <v>305</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K29" s="10">
         <v>4.4000000000000004</v>
@@ -5931,7 +5966,7 @@
         <v>149</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>150</v>
@@ -5951,40 +5986,40 @@
     </row>
     <row r="45" spans="1:12" ht="144">
       <c r="A45" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>844</v>
-      </c>
       <c r="D45" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>848</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>467</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K45" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="80">
@@ -6045,7 +6080,7 @@
         <v>603</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>604</v>
@@ -6065,78 +6100,78 @@
     </row>
     <row r="48" spans="1:12" ht="80">
       <c r="A48" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>829</v>
-      </c>
       <c r="G48" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>825</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>826</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K48" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="128">
       <c r="A49" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>839</v>
-      </c>
       <c r="G49" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="K49" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="64">
@@ -6253,1015 +6288,1015 @@
         <v>670</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="80">
+    <row r="53" spans="1:12" ht="96">
       <c r="A53" s="1" t="s">
-        <v>191</v>
+        <v>860</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>265</v>
+        <v>905</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>266</v>
+        <v>907</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>268</v>
+        <v>908</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>909</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>758</v>
+        <v>904</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>269</v>
+        <v>906</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>570</v>
+        <v>910</v>
       </c>
       <c r="K53" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="48">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="80">
       <c r="A54" s="1" t="s">
-        <v>459</v>
+        <v>191</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>450</v>
+        <v>265</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>759</v>
+        <v>903</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K54" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="64">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="48">
       <c r="A55" s="1" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="K55" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="64">
       <c r="A56" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K56" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="64">
       <c r="A57" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K57" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="48">
       <c r="A58" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>448</v>
+        <v>270</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K58" s="10">
         <v>4.3</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="48">
       <c r="A59" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K59" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="48">
       <c r="A60" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K60" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="96">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>449</v>
+        <v>235</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K61" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="96">
       <c r="A62" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K62" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="80">
       <c r="A63" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K63" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
-        <v>804</v>
+        <v>230</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>805</v>
+        <v>280</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>811</v>
+        <v>450</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>812</v>
+        <v>283</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>813</v>
+        <v>284</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>808</v>
+        <v>281</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>807</v>
+        <v>767</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>806</v>
+        <v>282</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>810</v>
+        <v>549</v>
       </c>
       <c r="K64" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>809</v>
+        <v>681</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="64">
       <c r="A65" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="K65" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="64">
+      <c r="A66" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="K65" s="10">
-        <v>4</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="80">
-      <c r="A66" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K66" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="80">
       <c r="A67" s="1" t="s">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K67" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="112">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="64">
       <c r="A68" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K68" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="112">
       <c r="A69" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>50</v>
+        <v>494</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K69" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="80">
       <c r="A70" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K70" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="64">
       <c r="A71" s="1" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="K71" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="112">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="80">
       <c r="A72" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="K72" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="48">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="112">
       <c r="A73" s="1" t="s">
-        <v>461</v>
+        <v>296</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="K73" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="144">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="48">
       <c r="A74" s="1" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>476</v>
+        <v>62</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>477</v>
+        <v>776</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="K74" s="10">
         <v>4.2</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="144">
       <c r="A75" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>33</v>
+        <v>475</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>34</v>
+        <v>777</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K75" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="96">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="64">
       <c r="A76" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>467</v>
+        <v>32</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>468</v>
+        <v>778</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K76" s="10">
         <v>3.9</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="64">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="96">
       <c r="A77" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K77" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="48">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="64">
       <c r="A78" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>452</v>
+        <v>478</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>24</v>
+        <v>480</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>25</v>
+        <v>780</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="K78" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="80">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="48">
       <c r="A79" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>447</v>
+        <v>22</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>25</v>
@@ -7270,923 +7305,961 @@
         <v>411</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="K79" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="64">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="80">
       <c r="A80" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K80" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="48">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="64">
       <c r="A81" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K81" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="48">
       <c r="A82" s="1" t="s">
-        <v>606</v>
+        <v>313</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>607</v>
+        <v>69</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>609</v>
+        <v>444</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>610</v>
+        <v>70</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>608</v>
+        <v>784</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J82" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K82" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="48">
+      <c r="A83" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J83" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K82" s="10">
+      <c r="K83" s="10">
         <v>4.2</v>
       </c>
-      <c r="L82" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="32">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:12" ht="32">
+      <c r="A84" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C84" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F84" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H83" s="2" t="s">
+      <c r="G84" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="K83" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="64">
-      <c r="A84" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J84" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="K84" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="64">
+      <c r="A85" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K85" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="48">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:12" ht="48">
+      <c r="A86" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D86" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E86" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F86" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G86" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="K86" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="96">
+      <c r="A87" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="K85" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="96">
-      <c r="A86" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="H86" s="2" t="s">
+      <c r="H87" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="K86" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="64">
-      <c r="A87" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K87" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="112">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="64">
       <c r="A88" s="1" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>368</v>
+        <v>505</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="K88" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="112">
       <c r="A89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>13</v>
+        <v>469</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>15</v>
+        <v>471</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>16</v>
+        <v>791</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="K89" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="64">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="96">
       <c r="A90" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>720</v>
+        <v>792</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="K90" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="48">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="64">
       <c r="A91" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="K91" s="10"/>
+        <v>589</v>
+      </c>
+      <c r="K91" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L91" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="96">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>804</v>
+        <v>397</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>814</v>
+        <v>87</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="E92" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>819</v>
+      <c r="H92" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="K92" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L92" s="6" t="s">
         <v>820</v>
+      </c>
+      <c r="K92" s="10"/>
+      <c r="L92" s="2" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="96">
       <c r="A93" s="1" t="s">
-        <v>879</v>
+        <v>803</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>887</v>
+        <v>813</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K93" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="96">
+      <c r="A94" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="E94" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="F94" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="G94" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J93" s="7" t="s">
-        <v>894</v>
-      </c>
-      <c r="K93" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="64">
-      <c r="A94" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>590</v>
+        <v>893</v>
       </c>
       <c r="K94" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="64">
       <c r="A95" s="1" t="s">
-        <v>593</v>
+        <v>398</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>594</v>
+        <v>374</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>596</v>
+        <v>375</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K95" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="96">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="48">
       <c r="A96" s="1" t="s">
-        <v>399</v>
+        <v>593</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>373</v>
+        <v>596</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>371</v>
+        <v>597</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K96" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="48">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="96">
       <c r="A97" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="K97" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="48">
       <c r="A98" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K98" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="K99" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="96">
       <c r="A100" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="K100" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K101" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>369</v>
+        <v>800</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K102" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>613</v>
+        <v>485</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>615</v>
+        <v>366</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>616</v>
+        <v>367</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>618</v>
+        <v>369</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J103" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K103" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="48">
+      <c r="A104" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J104" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K103" s="10">
+      <c r="K104" s="10">
         <v>3.4</v>
       </c>
-      <c r="L103" s="2" t="s">
+      <c r="L104" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J102">
-    <sortCondition ref="I2:I102"/>
-    <sortCondition ref="D2:D102"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J103">
+    <sortCondition ref="I2:I103"/>
+    <sortCondition ref="D2:D103"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8208,18 +8281,18 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H60" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H58" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H62" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H59" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H61" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H54" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H53" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H57" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H56" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H63" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H55" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H84" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H61" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H59" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H63" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H60" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H62" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H55" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H54" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H58" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H57" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H64" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H56" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H85" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
     <hyperlink ref="H31" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
     <hyperlink ref="H30" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
     <hyperlink ref="H24" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
@@ -8232,26 +8305,26 @@
     <hyperlink ref="H23" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H28" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H20" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H102" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H96" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H94" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H97" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H98" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H99" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H100" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H85" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H76" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H88" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H74" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H77" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H87" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H95" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H103" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H97" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H95" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H98" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H99" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H100" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H101" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H86" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H77" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H89" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H75" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H78" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H88" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H96" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
     <hyperlink ref="H47" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H82" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H103" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H64" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H92" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L92" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H83" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H104" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H65" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H93" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L93" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
     <hyperlink ref="H48" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
     <hyperlink ref="L48" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
     <hyperlink ref="H49" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
@@ -8264,10 +8337,11 @@
     <hyperlink ref="H19" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
     <hyperlink ref="H16" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
     <hyperlink ref="L16" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H93" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L93" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H94" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L94" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
     <hyperlink ref="H15" r:id="rId77" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
     <hyperlink ref="L15" r:id="rId78" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H53" r:id="rId79" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7606DD4B-116C-6140-9B04-0CD6F0BD6A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EA7CA2-F753-854F-96FB-360C1E9A4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="2640" yWindow="1320" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="922">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3865,6 +3865,49 @@
   </si>
   <si>
     <t>https://www.google.com.tw/search?q=%E9%BE%9C%E5%B1%B1%E9%B1%B8%E9%AD%9A%E6%B9%AF&amp;sxsrf=AOaemvJa0u7lJKPsiRcVtRvDZjJyqxtl4Q:1637397953224&amp;source=hp&amp;ei=trWYYbLdOJHrmAXbm4PoCA&amp;iflsig=ALs-wAMAAAAAYZjDxqQGKRPaWKt9BL6Rh_jmWRGiCMWB&amp;ved=2ahUKEwie5O3axqb0AhVIrVYBHQC9AKkQvS56BAgKEDw&amp;uact=5&amp;oq=%E9%BE%9C%E5%B1%B1%E9%B1%B8%E9%AD%9A%E6%B9%AF&amp;gs_lcp=Cgdnd3Mtd2l6EAMyBQgAEM0COgcIIxDqAhAnOg0ILhDHARCvARDqAhAnOgQIIxAnOg4ILhCABBCxAxDHARDRAzoICAAQgAQQsQM6DgguEIAEELEDEMcBEKMCOgUILhCABDoFCAAQgAQ6BAgAEEM6CggAELEDEIMBEEM6CwgAEIAEELEDEIMBOggILhCABBCxAzoLCC4QgAQQxwEQrwE6CAgAELEDEIMBOgsILhCABBCxAxCDAToCCCZQuQ5YlUFgqUdoA3AAeACAAWaIAfsIkgEEMTYuMZgBAKABAbABCg&amp;sclient=gws-wiz&amp;tbs=lf:1,lf_ui:9&amp;tbm=lcl&amp;rflfq=1&amp;num=10&amp;rldimm=11820264403630838222&amp;lqi=Cg_pvpzlsbHpsbjprZrmua9aFCIS6b6cIOWxsSDpsbjprZog5rmvkgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSNWNHUXRNR2RCUlJBQqoBFwoKL20vMDF6MW0xeBABKgciA-a5ryhF&amp;phdesc=dUIbgtEpGm0&amp;rlst=f#rlfi=hd:;si:11820264403630838222,l,Cg_pvpzlsbHpsbjprZrmua9aFCIS6b6cIOWxsSDpsbjprZog5rmvkgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSNWNHUXRNR2RCUlJBQqoBFwoKL20vMDF6MW0xeBABKgciA-a5ryhF,y,dUIbgtEpGm0;mv:[[25.073528099999997,121.4300487],[24.9801288,121.3005194]];tbs:lrf:!1m4!1u3!2m2!3m1!1e1!1m4!1u2!2m2!2m1!1e1!2m1!1e2!2m1!1e3!3sIAE,lf:1,lf_ui:9</t>
+  </si>
+  <si>
+    <t>120</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛機河粉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>越南餐廳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段356號2F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-6637-0188</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一～週四 11:00 - 21:30, 週五~週日 11:00 - 22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.mapoking.com.tw/MenuO/StoreInfoE.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.mapoking.com.tw/MenuO/StoreInfoE.html"&gt;菜單&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://zineblog.com.tw/blog/post/210120"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E9%A3%9B%E6%A9%9F%E6%B2%B3%E7%B2%89+%E6%9E%97%E5%8F%A3%E4%B8%89%E4%BA%95%E5%BA%97/@25.0685803,121.362557,16.2z/data=!4m9!1m2!2m1!1z6aOb5qmf5rKz57KJ!3m5!1s0x3442a7f4d7aeac33:0xb75a61d861af9558!8m2!3d25.0706446!4d121.363835!15sCgzpo5vmqZ_msrPnsolaECIO6aOb5qmfIOaysyDnsomSARV2aWV0bmFtZXNlX3Jlc3RhdXJhbnQ?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-飛機河粉.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4298,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4353,7 +4396,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="112">
+    <row r="2" spans="1:12" ht="144">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -4429,7 +4472,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80">
+    <row r="4" spans="1:12" ht="96">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4543,7 +4586,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80">
+    <row r="7" spans="1:12" ht="96">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -4695,7 +4738,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="128">
+    <row r="11" spans="1:12" ht="144">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -4847,772 +4890,772 @@
         <v>639</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="112">
+    <row r="15" spans="1:12" ht="64">
       <c r="A15" s="1" t="s">
-        <v>894</v>
+        <v>912</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>449</v>
+        <v>914</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>900</v>
+        <v>918</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>902</v>
+        <v>919</v>
       </c>
       <c r="K15" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="112">
       <c r="A16" s="1" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>877</v>
+        <v>899</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>883</v>
+        <v>900</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="K16" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>803</v>
+        <v>878</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="K17" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>858</v>
+        <v>884</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>452</v>
+        <v>852</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="K18" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="80">
       <c r="A19" s="1" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>450</v>
+        <v>861</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>602</v>
+        <v>863</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>604</v>
+        <v>867</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="K19" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="64">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>869</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C20" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>450</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>718</v>
+        <v>871</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>364</v>
+        <v>602</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>872</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>362</v>
+        <v>873</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>519</v>
+        <v>875</v>
       </c>
       <c r="K20" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>453</v>
+        <v>361</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>333</v>
+        <v>718</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K21" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="96">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="64">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>643</v>
+        <v>332</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K22" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="80">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="96">
       <c r="A23" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>355</v>
+        <v>643</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K23" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="96">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K24" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="96">
       <c r="A25" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K25" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="96">
       <c r="A26" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K26" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="80">
       <c r="A27" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="K27" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="80">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="64">
       <c r="A28" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>450</v>
+        <v>337</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="K28" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="80">
       <c r="A29" s="1" t="s">
-        <v>457</v>
+        <v>100</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>447</v>
+        <v>356</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>305</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>851</v>
+        <v>526</v>
       </c>
       <c r="K29" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="64">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="80">
       <c r="A30" s="1" t="s">
-        <v>102</v>
+        <v>457</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>507</v>
+        <v>342</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>111</v>
+        <v>305</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>527</v>
+        <v>851</v>
       </c>
       <c r="K30" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="96">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="64">
       <c r="A31" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>297</v>
+        <v>507</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>413</v>
+        <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K31" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="64">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="96">
       <c r="A32" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>159</v>
+        <v>413</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>161</v>
+        <v>299</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>162</v>
+        <v>742</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K32" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="80">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="64">
       <c r="A33" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>448</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K33" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="64">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="80">
       <c r="A34" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="K34" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="96">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="64">
       <c r="A35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>447</v>
@@ -5621,226 +5664,226 @@
         <v>153</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K35" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="96">
       <c r="A36" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>450</v>
+        <v>174</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K36" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="96">
       <c r="A37" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>448</v>
+        <v>178</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K37" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="112">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="96">
       <c r="A38" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K38" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="112">
       <c r="A39" s="1" t="s">
-        <v>458</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>488</v>
+        <v>192</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>94</v>
+        <v>749</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K39" s="10">
-        <v>4</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="128">
       <c r="A40" s="1" t="s">
-        <v>145</v>
+        <v>458</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>750</v>
+        <v>722</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K40" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="128">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="112">
       <c r="A41" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>449</v>
@@ -5849,1492 +5892,1492 @@
         <v>108</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K41" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="112">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="128">
       <c r="A42" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>164</v>
+        <v>490</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>167</v>
+        <v>751</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K42" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="64">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="112">
       <c r="A43" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>450</v>
+        <v>164</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K43" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="80">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="64">
       <c r="A44" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>453</v>
+        <v>169</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>848</v>
+        <v>753</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K44" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="144">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="80">
       <c r="A45" s="1" t="s">
-        <v>841</v>
+        <v>168</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>842</v>
+        <v>146</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>843</v>
+        <v>453</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>846</v>
+        <v>147</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>847</v>
+        <v>148</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>467</v>
+        <v>149</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>844</v>
+        <v>150</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>850</v>
+        <v>540</v>
       </c>
       <c r="K45" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="80">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="144">
       <c r="A46" s="1" t="s">
-        <v>173</v>
+        <v>841</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>119</v>
+        <v>842</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>448</v>
+        <v>843</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>412</v>
+        <v>846</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>120</v>
+        <v>847</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>121</v>
+        <v>467</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>122</v>
+        <v>849</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>844</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>566</v>
+        <v>850</v>
       </c>
       <c r="K46" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="48">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="80">
       <c r="A47" s="1" t="s">
-        <v>599</v>
+        <v>173</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>600</v>
+        <v>119</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>601</v>
+        <v>412</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>602</v>
+        <v>120</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>603</v>
+        <v>121</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>604</v>
+        <v>754</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="K47" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="80">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="48">
       <c r="A48" s="1" t="s">
-        <v>822</v>
+        <v>599</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>832</v>
+        <v>600</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>826</v>
+        <v>601</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>827</v>
+        <v>602</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>828</v>
+        <v>603</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>825</v>
+        <v>604</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>830</v>
+        <v>605</v>
       </c>
       <c r="K48" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="80">
       <c r="A49" s="1" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="K49" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="128">
+      <c r="A50" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J50" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K50" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L49" s="6" t="s">
+      <c r="L50" s="6" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="64">
-      <c r="A50" s="1" t="s">
+    <row r="51" spans="1:12" ht="64">
+      <c r="A51" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="K50" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="80">
-      <c r="A51" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K51" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="80">
       <c r="A52" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K52" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="96">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="80">
       <c r="A53" s="1" t="s">
-        <v>860</v>
+        <v>187</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>905</v>
+        <v>493</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K53" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="96">
+      <c r="A54" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>906</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="K53" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="80">
-      <c r="A54" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>570</v>
+        <v>910</v>
       </c>
       <c r="K54" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="48">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>459</v>
+        <v>191</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>450</v>
+        <v>265</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>758</v>
+        <v>903</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K55" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="64">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="K56" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="64">
       <c r="A57" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K57" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="64">
       <c r="A58" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K58" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="48">
       <c r="A59" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>448</v>
+        <v>270</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K59" s="10">
         <v>4.3</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="48">
       <c r="A60" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>450</v>
+        <v>240</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K60" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K61" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="96">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="48">
       <c r="A62" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>449</v>
+        <v>235</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K62" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="96">
       <c r="A63" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>450</v>
+        <v>255</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K63" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="80">
       <c r="A64" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K64" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>803</v>
+        <v>230</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>804</v>
+        <v>280</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>810</v>
+        <v>450</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>811</v>
+        <v>283</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>812</v>
+        <v>284</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>807</v>
+        <v>281</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>806</v>
+        <v>767</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>805</v>
+        <v>282</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>809</v>
+        <v>549</v>
       </c>
       <c r="K65" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>808</v>
+        <v>681</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="64">
       <c r="A66" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="K66" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="64">
+      <c r="A67" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="K66" s="10">
-        <v>4</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="80">
-      <c r="A67" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K67" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="80">
       <c r="A68" s="1" t="s">
-        <v>314</v>
+        <v>460</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K68" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="112">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="64">
       <c r="A69" s="1" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K69" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="112">
       <c r="A70" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>50</v>
+        <v>494</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K70" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="80">
       <c r="A71" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K71" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="64">
       <c r="A72" s="1" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>452</v>
+        <v>55</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="K72" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="112">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="80">
       <c r="A73" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="K73" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="48">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="112">
       <c r="A74" s="1" t="s">
-        <v>461</v>
+        <v>296</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="K74" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="144">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="48">
       <c r="A75" s="1" t="s">
-        <v>306</v>
+        <v>461</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>476</v>
+        <v>62</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>477</v>
+        <v>776</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="K75" s="10">
         <v>4.2</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="64">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="144">
       <c r="A76" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>33</v>
+        <v>475</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>476</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>34</v>
+        <v>777</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K76" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="96">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
       <c r="A77" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>447</v>
+        <v>498</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>467</v>
+        <v>32</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>468</v>
+        <v>778</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K77" s="10">
         <v>3.9</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="64">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="96">
       <c r="A78" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K78" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="48">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="64">
       <c r="A79" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>452</v>
+        <v>478</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>24</v>
+        <v>480</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>25</v>
+        <v>780</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="K79" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="80">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="48">
       <c r="A80" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>447</v>
+        <v>22</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>25</v>
@@ -7343,937 +7386,975 @@
         <v>411</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="K80" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="64">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="80">
       <c r="A81" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K81" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="48">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="64">
       <c r="A82" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K82" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>606</v>
+        <v>313</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>607</v>
+        <v>69</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>449</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>609</v>
+        <v>444</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>610</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>608</v>
+        <v>784</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J83" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K83" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="48">
+      <c r="A84" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J84" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K84" s="10">
         <v>4.2</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="32">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:12" ht="32">
+      <c r="A85" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H85" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="K84" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="64">
-      <c r="A85" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="K85" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="64">
+      <c r="A86" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="K85" s="10">
+      <c r="K86" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="48">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:12" ht="48">
+      <c r="A87" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="F87" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="H86" s="6" t="s">
+      <c r="H87" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="I87" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="J86" s="7" t="s">
+      <c r="J87" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="K86" s="10">
+      <c r="K87" s="10">
         <v>4.5</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="96">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:12" ht="96">
+      <c r="A88" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="K87" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="64">
-      <c r="A88" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>506</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K88" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="112">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="64">
       <c r="A89" s="1" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>368</v>
+        <v>505</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="K89" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="112">
       <c r="A90" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>13</v>
+        <v>469</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>15</v>
+        <v>471</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>16</v>
+        <v>791</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="K90" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="64">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="96">
       <c r="A91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>720</v>
+        <v>792</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="K91" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="48">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="64">
       <c r="A92" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>87</v>
+        <v>501</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>816</v>
+        <v>720</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="K92" s="10"/>
+        <v>589</v>
+      </c>
+      <c r="K92" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L92" s="2" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="96">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="48">
       <c r="A93" s="1" t="s">
-        <v>803</v>
+        <v>397</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>813</v>
+        <v>87</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>815</v>
+        <v>428</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>388</v>
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="K93" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
+      </c>
+      <c r="K93" s="10"/>
+      <c r="L93" s="2" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="96">
       <c r="A94" s="1" t="s">
-        <v>878</v>
+        <v>803</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>886</v>
+        <v>813</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K94" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="96">
+      <c r="A95" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E95" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G95" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="H94" s="6" t="s">
+      <c r="H95" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="K94" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="64">
-      <c r="A95" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>377</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>590</v>
+        <v>893</v>
       </c>
       <c r="K95" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="64">
       <c r="A96" s="1" t="s">
-        <v>593</v>
+        <v>398</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>594</v>
+        <v>374</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>595</v>
+        <v>429</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>596</v>
+        <v>375</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>376</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>597</v>
+        <v>377</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="K96" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="96">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>399</v>
+        <v>593</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>373</v>
+        <v>596</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>371</v>
+        <v>597</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="K97" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="48">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="96">
       <c r="A98" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="K98" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K99" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="96">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="K100" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="48">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="96">
       <c r="A101" s="1" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="K101" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K102" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>369</v>
+        <v>800</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K103" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>613</v>
+        <v>485</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>615</v>
+        <v>366</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>616</v>
+        <v>367</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>618</v>
+        <v>369</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>365</v>
       </c>
       <c r="J104" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K104" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="48">
+      <c r="A105" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J105" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="K104" s="10">
+      <c r="K105" s="10">
         <v>3.4</v>
       </c>
-      <c r="L104" s="2" t="s">
+      <c r="L105" s="2" t="s">
         <v>717</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J103">
-    <sortCondition ref="I2:I103"/>
-    <sortCondition ref="D2:D103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J104">
+    <sortCondition ref="I2:I104"/>
+    <sortCondition ref="D2:D104"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H44" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H34" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H42" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H32" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H43" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H35" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H36" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H37" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H33" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H38" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H45" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H35" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H43" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H33" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H44" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H36" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H37" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H38" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H34" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H39" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8281,67 +8362,68 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H61" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H59" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H63" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H60" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H62" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H55" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H54" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H58" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H57" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H64" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H56" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H85" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H31" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H30" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H24" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H26" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H25" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H21" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H27" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H29" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H22" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H23" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H28" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H20" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H103" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H97" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H95" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H98" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H99" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H100" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H101" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H86" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H77" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H89" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H75" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H78" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H88" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H96" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H47" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H83" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H104" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H65" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H93" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L93" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H48" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L48" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H49" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L49" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H45" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H17" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L17" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H18" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L19" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H19" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H16" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L16" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H94" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L94" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H15" r:id="rId77" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L15" r:id="rId78" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H53" r:id="rId79" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H62" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H60" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H64" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
+    <hyperlink ref="H61" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H63" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H56" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H55" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H59" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H58" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H65" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H57" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H86" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H32" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H31" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H25" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H27" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H26" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H22" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H28" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H30" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H23" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H24" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H29" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H21" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H104" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H98" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H96" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H99" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H100" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H101" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H102" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H87" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H78" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H90" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H76" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H79" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H89" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H97" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H48" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H84" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H105" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H66" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H94" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L94" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H49" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L49" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H50" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L50" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H46" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H18" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L18" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H19" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L20" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H20" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H17" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L17" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H95" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L95" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H16" r:id="rId77" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L16" r:id="rId78" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H54" r:id="rId79" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H15" r:id="rId80" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EA7CA2-F753-854F-96FB-360C1E9A4B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7312280-3996-4B43-AECB-26F262A6762E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="1320" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="1560" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="913">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1048,9 +1048,6 @@
     <t>052</t>
   </si>
   <si>
-    <t>053</t>
-  </si>
-  <si>
     <t>054</t>
   </si>
   <si>
@@ -1106,28 +1103,6 @@
   <si>
     <t xml:space="preserve">
 11:30 - 14:30 、 17:30 - 21:30 週三公休</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>懷舊中卷麵線、魷魚翅麵線</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市龜山區復興北路6巷51-1號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0989-838-605</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.walkerland.com.tw/article/view/259968</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>平日11:30~18:00或售完, 
-週六11:00~14:00或售完,
-週日公休</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2428,13 +2403,6 @@
   </si>
   <si>
     <t>&lt;p&gt;
-  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/tastyoldtime/photos/p.1153757731719550/1153757731719550"&gt;菜單&lt;/a&gt;   &amp;nbsp;
-   &lt;a style="button" class="btn btn-info"  href=""&gt;推薦&lt;/a&gt;
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
   網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://letsplay.tw/taishapa/"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3019,9 +2987,6 @@
     <t>https://www.google.com.tw/maps/place/%E6%A2%85%E8%8F%8A%E6%89%8B%E4%BD%9C%E9%AD%AF%E8%82%89%E9%A3%AF%EF%BC%88%E5%AF%B5%E7%89%A9%E5%8F%8B%E5%96%84%EF%BC%89/@25.055566,121.3601271,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7c690e6c15f:0x67925f1c40e9f6b7!8m2!3d25.055566!4d121.3623211?hl=zh-TW&amp;authuser=0</t>
   </si>
   <si>
-    <t>https://www.google.com.tw/maps/place/%E6%87%B7%E8%88%8A%E4%B8%AD%E5%8D%B7%E9%BA%B5%E7%B7%9A/@25.0584549,121.3655109,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7d80725d609:0x5c28ba69a8a26dab!8m2!3d25.0584549!4d121.3677049?hl=zh-TW&amp;authuser=0</t>
-  </si>
-  <si>
     <t>https://www.google.com.tw/maps/place/%E6%B3%B0%E8%9D%A6%E6%A8%82+%E6%B5%81%E6%B0%B4%E9%81%93%E6%B3%B0%E5%9C%8B%E8%9D%A6%E5%90%83%E5%88%B0%E9%A3%BD/@25.0140635,121.2901509,13z/data=!4m8!1m2!2m1!1z6b6c5bGxIOawtOmBk-azsOWci-idpuWQg-WIsOmjvQ!3m4!1s0x346819e41bdbf829:0x89d85397dd05cdbd!8m2!3d24.9593873!4d121.2912816?hl=zh-TW&amp;authuser=0</t>
   </si>
   <si>
@@ -3276,9 +3241,6 @@
   </si>
   <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-梅菊滷肉飯.jpg</t>
-  </si>
-  <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-懷舊中卷.jpg</t>
   </si>
   <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-泰國蝦.jpg</t>
@@ -4341,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4366,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -4387,24 +4349,24 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="144">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="112">
       <c r="A2" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>104</v>
@@ -4416,7 +4378,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>106</v>
@@ -4425,24 +4387,24 @@
         <v>95</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="K2" s="10">
         <v>3.8</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="112">
       <c r="A3" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>101</v>
@@ -4454,7 +4416,7 @@
         <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>48</v>
@@ -4463,24 +4425,24 @@
         <v>95</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="K3" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="96">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="80">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>97</v>
@@ -4492,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>99</v>
@@ -4501,13 +4463,13 @@
         <v>95</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="K4" s="10">
         <v>3.3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="80">
@@ -4518,7 +4480,7 @@
         <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>92</v>
@@ -4530,7 +4492,7 @@
         <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>94</v>
@@ -4539,13 +4501,13 @@
         <v>95</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="K5" s="10">
         <v>4.2</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48">
@@ -4553,10 +4515,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>132</v>
@@ -4568,7 +4530,7 @@
         <v>134</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
@@ -4577,24 +4539,24 @@
         <v>95</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="K6" s="10">
         <v>3.8</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="96">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="80">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>141</v>
@@ -4606,7 +4568,7 @@
         <v>143</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>144</v>
@@ -4615,13 +4577,13 @@
         <v>95</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="K7" s="10">
         <v>4.7</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="80">
@@ -4632,7 +4594,7 @@
         <v>195</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>196</v>
@@ -4644,7 +4606,7 @@
         <v>198</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>199</v>
@@ -4653,13 +4615,13 @@
         <v>200</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="K8" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17">
@@ -4667,10 +4629,10 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>212</v>
@@ -4682,7 +4644,7 @@
         <v>214</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>215</v>
@@ -4691,13 +4653,13 @@
         <v>200</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="K9" s="10">
         <v>4.5</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="97">
@@ -4708,7 +4670,7 @@
         <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>208</v>
@@ -4720,7 +4682,7 @@
         <v>204</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>210</v>
@@ -4729,24 +4691,24 @@
         <v>200</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="K10" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="144">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="128">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>202</v>
@@ -4758,7 +4720,7 @@
         <v>204</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>205</v>
@@ -4767,13 +4729,13 @@
         <v>200</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="K11" s="10">
         <v>3.8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="96">
@@ -4781,10 +4743,10 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>202</v>
@@ -4796,7 +4758,7 @@
         <v>218</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>219</v>
@@ -4805,13 +4767,13 @@
         <v>200</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="K12" s="10">
         <v>4</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="64">
@@ -4822,7 +4784,7 @@
         <v>221</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>202</v>
@@ -4834,7 +4796,7 @@
         <v>218</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>223</v>
@@ -4843,13 +4805,13 @@
         <v>200</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="K13" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="144">
@@ -4857,10 +4819,10 @@
         <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>202</v>
@@ -4872,7 +4834,7 @@
         <v>218</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>226</v>
@@ -4881,241 +4843,241 @@
         <v>200</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="K14" s="10">
         <v>4.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="64">
       <c r="A15" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>914</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>921</v>
-      </c>
       <c r="H15" s="4" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="K15" s="10">
         <v>3.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="112">
       <c r="A16" s="1" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="K16" s="10">
         <v>4.3</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="K17" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="K18" s="10">
         <v>4.3</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="80">
       <c r="A19" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="K19" s="10">
         <v>4.7</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="64">
       <c r="A20" s="1" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="K20" s="10">
         <v>4.3</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
@@ -5123,37 +5085,37 @@
         <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="K21" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="64">
@@ -5161,37 +5123,37 @@
         <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="K22" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="96">
@@ -5199,37 +5161,37 @@
         <v>73</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="K23" s="10">
         <v>4.7</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="80">
@@ -5237,37 +5199,37 @@
         <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="K24" s="10">
         <v>4.3</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="96">
@@ -5275,37 +5237,37 @@
         <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="K25" s="10">
         <v>4</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="96">
@@ -5313,37 +5275,37 @@
         <v>86</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="K26" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="80">
@@ -5351,37 +5313,37 @@
         <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="K27" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="64">
@@ -5389,37 +5351,37 @@
         <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="K28" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="80">
@@ -5427,75 +5389,75 @@
         <v>100</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="K29" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="80">
       <c r="A30" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="K30" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="64">
@@ -5503,37 +5465,37 @@
         <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="K31" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="96">
@@ -5541,37 +5503,37 @@
         <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="K32" s="10">
         <v>4.2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="64">
@@ -5582,7 +5544,7 @@
         <v>158</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>159</v>
@@ -5594,7 +5556,7 @@
         <v>161</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>162</v>
@@ -5603,13 +5565,13 @@
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="K33" s="10">
         <v>4.8</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="80">
@@ -5620,7 +5582,7 @@
         <v>183</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>184</v>
@@ -5632,7 +5594,7 @@
         <v>171</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>186</v>
@@ -5641,13 +5603,13 @@
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="K34" s="10">
         <v>3.9</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="64">
@@ -5658,7 +5620,7 @@
         <v>152</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>153</v>
@@ -5670,7 +5632,7 @@
         <v>155</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>156</v>
@@ -5679,13 +5641,13 @@
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="K35" s="10">
         <v>4.2</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="96">
@@ -5696,7 +5658,7 @@
         <v>174</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>153</v>
@@ -5708,7 +5670,7 @@
         <v>161</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>176</v>
@@ -5717,13 +5679,13 @@
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="K36" s="10">
         <v>3.9</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="96">
@@ -5734,7 +5696,7 @@
         <v>178</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>153</v>
@@ -5746,7 +5708,7 @@
         <v>180</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>181</v>
@@ -5755,13 +5717,13 @@
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="K37" s="10">
         <v>4.2</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="96">
@@ -5772,7 +5734,7 @@
         <v>188</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>153</v>
@@ -5784,7 +5746,7 @@
         <v>180</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>190</v>
@@ -5793,13 +5755,13 @@
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="K38" s="10">
         <v>3.8</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="112">
@@ -5810,7 +5772,7 @@
         <v>192</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>153</v>
@@ -5822,7 +5784,7 @@
         <v>161</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>194</v>
@@ -5831,24 +5793,24 @@
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="K39" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="128">
       <c r="A40" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>108</v>
@@ -5860,7 +5822,7 @@
         <v>110</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>94</v>
@@ -5869,13 +5831,13 @@
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="K40" s="10">
         <v>4</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="112">
@@ -5883,10 +5845,10 @@
         <v>145</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>108</v>
@@ -5898,7 +5860,7 @@
         <v>110</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>114</v>
@@ -5907,13 +5869,13 @@
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="K41" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="128">
@@ -5921,10 +5883,10 @@
         <v>151</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>108</v>
@@ -5936,7 +5898,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>117</v>
@@ -5945,13 +5907,13 @@
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="K42" s="10">
         <v>3.7</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="112">
@@ -5962,7 +5924,7 @@
         <v>164</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>165</v>
@@ -5971,7 +5933,7 @@
         <v>166</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>167</v>
@@ -5980,13 +5942,13 @@
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="K43" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="64">
@@ -5997,7 +5959,7 @@
         <v>169</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>165</v>
@@ -6009,7 +5971,7 @@
         <v>171</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>172</v>
@@ -6018,13 +5980,13 @@
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="K44" s="10">
         <v>4.3</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="80">
@@ -6035,7 +5997,7 @@
         <v>146</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>147</v>
@@ -6047,7 +6009,7 @@
         <v>149</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>150</v>
@@ -6056,51 +6018,51 @@
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="K45" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="144">
       <c r="A46" s="1" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="K46" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="80">
@@ -6111,10 +6073,10 @@
         <v>119</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>120</v>
@@ -6123,7 +6085,7 @@
         <v>121</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>122</v>
@@ -6132,127 +6094,127 @@
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="K47" s="10">
         <v>3.5</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="48">
       <c r="A48" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="K48" s="10">
         <v>4.3</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="80">
       <c r="A49" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="K49" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="128">
       <c r="A50" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>840</v>
-      </c>
       <c r="H50" s="6" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="K50" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="64">
@@ -6260,13 +6222,13 @@
         <v>177</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>128</v>
@@ -6275,7 +6237,7 @@
         <v>129</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>130</v>
@@ -6284,13 +6246,13 @@
         <v>126</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="K51" s="10">
         <v>3.9</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="80">
@@ -6298,13 +6260,13 @@
         <v>182</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>124</v>
@@ -6313,7 +6275,7 @@
         <v>42</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>125</v>
@@ -6322,13 +6284,13 @@
         <v>126</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="K52" s="10">
         <v>4.3</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="80">
@@ -6336,13 +6298,13 @@
         <v>187</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>137</v>
@@ -6351,7 +6313,7 @@
         <v>138</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>139</v>
@@ -6360,51 +6322,51 @@
         <v>140</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="K53" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="96">
       <c r="A54" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="K54" s="10">
         <v>4.8</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="80">
@@ -6412,75 +6374,75 @@
         <v>191</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="K55" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="K56" s="10">
         <v>4.5</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="64">
@@ -6488,37 +6450,37 @@
         <v>201</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="K57" s="10">
         <v>4.7</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="64">
@@ -6526,37 +6488,37 @@
         <v>206</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="K58" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="48">
@@ -6564,37 +6526,37 @@
         <v>211</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="K59" s="10">
         <v>4.3</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="48">
@@ -6602,37 +6564,37 @@
         <v>216</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>243</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="K60" s="10">
         <v>4.3</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="48">
@@ -6640,37 +6602,37 @@
         <v>220</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="K61" s="10">
         <v>4.7</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="48">
@@ -6678,37 +6640,37 @@
         <v>224</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="K62" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="96">
@@ -6716,1631 +6678,1593 @@
         <v>228</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="K63" s="10">
         <v>4</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="80">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
         <v>229</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="K64" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="48">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="64">
       <c r="A65" s="1" t="s">
-        <v>230</v>
+        <v>794</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>280</v>
+        <v>795</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>450</v>
+        <v>801</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>283</v>
+        <v>802</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>284</v>
+        <v>803</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>281</v>
+        <v>798</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>767</v>
+        <v>797</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>282</v>
+        <v>796</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>549</v>
+        <v>800</v>
       </c>
       <c r="K65" s="10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>681</v>
+        <v>799</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="64">
       <c r="A66" s="1" t="s">
-        <v>803</v>
+        <v>230</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>804</v>
+        <v>37</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>810</v>
+        <v>446</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>811</v>
+        <v>414</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>807</v>
+        <v>38</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>805</v>
+        <v>759</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>227</v>
+        <v>405</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>809</v>
+        <v>566</v>
       </c>
       <c r="K66" s="10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="80">
       <c r="A67" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="K67" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="64">
+      <c r="A68" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="K68" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="112">
+      <c r="A69" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="K67" s="10">
-        <v>4</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="80">
-      <c r="A68" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="K68" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="64">
-      <c r="A69" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="B69" s="2" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="K69" s="10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="112">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="80">
       <c r="A70" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>494</v>
+        <v>50</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="K70" s="10">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="64">
       <c r="A71" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="K71" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="80">
       <c r="A72" s="1" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>447</v>
+        <v>489</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
       <c r="K72" s="10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="80">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="112">
       <c r="A73" s="1" t="s">
         <v>290</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="K73" s="10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="112">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="48">
       <c r="A74" s="1" t="s">
-        <v>296</v>
+        <v>455</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>452</v>
+        <v>491</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>579</v>
+        <v>544</v>
       </c>
       <c r="K74" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="48">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="144">
       <c r="A75" s="1" t="s">
-        <v>461</v>
+        <v>300</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>63</v>
+        <v>469</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>64</v>
+        <v>768</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="K75" s="10">
         <v>4.2</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="144">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="64">
       <c r="A76" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>449</v>
+        <v>492</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>474</v>
+        <v>418</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>476</v>
+        <v>32</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>477</v>
+        <v>769</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="K76" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="96">
       <c r="A77" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>451</v>
+        <v>458</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>33</v>
+        <v>460</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>461</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>34</v>
+        <v>770</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="K77" s="10">
         <v>3.9</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="96">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="64">
       <c r="A78" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="I78" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="K78" s="10">
+        <v>4</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="48">
+      <c r="A79" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="K79" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="80">
+      <c r="A80" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="J78" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="K78" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
-      <c r="A79" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="K79" s="10">
-        <v>4</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="48">
-      <c r="A80" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="E80" s="2" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="K80" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="80">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="64">
       <c r="A81" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="K81" s="10">
+        <v>4</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="48">
+      <c r="A82" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K82" s="10">
         <v>3.8</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
-      <c r="A82" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="K82" s="10">
-        <v>4</v>
-      </c>
       <c r="L82" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>313</v>
+        <v>599</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>69</v>
+        <v>600</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="K83" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="32">
+      <c r="A84" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="K83" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="48">
-      <c r="A84" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>609</v>
+        <v>413</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>610</v>
+        <v>83</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>611</v>
+        <v>84</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>608</v>
+        <v>777</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>411</v>
+        <v>12</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
       <c r="K84" s="10">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="32">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>401</v>
+        <v>309</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>450</v>
+        <v>285</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>419</v>
+        <v>286</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>84</v>
+        <v>287</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>85</v>
+        <v>778</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="K85" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="64">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="48">
       <c r="A86" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>293</v>
+        <v>400</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>294</v>
+        <v>404</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>295</v>
+        <v>402</v>
       </c>
       <c r="I86" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="K86" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="96">
+      <c r="A87" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J86" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="K86" s="10">
+      <c r="J87" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="K87" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L86" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="48">
-      <c r="A87" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="K87" s="10">
-        <v>4.5</v>
-      </c>
       <c r="L87" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="96">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="64">
       <c r="A88" s="1" t="s">
-        <v>393</v>
+        <v>496</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>452</v>
+        <v>497</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>425</v>
+        <v>498</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>9</v>
+        <v>499</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>10</v>
+        <v>461</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>11</v>
+        <v>781</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>500</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="K88" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="64">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="112">
       <c r="A89" s="1" t="s">
-        <v>502</v>
+        <v>388</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>503</v>
+        <v>463</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>504</v>
+        <v>464</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>506</v>
+        <v>466</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="K89" s="10">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="112">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="96">
       <c r="A90" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>469</v>
+        <v>13</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>368</v>
+        <v>14</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>472</v>
+        <v>783</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>588</v>
+        <v>550</v>
       </c>
       <c r="K90" s="10">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="96">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="64">
       <c r="A91" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>13</v>
+        <v>495</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>792</v>
+        <v>712</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="K91" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="64">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>501</v>
+        <v>87</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>720</v>
+        <v>807</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="K92" s="10">
-        <v>4.0999999999999996</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="K92" s="10"/>
       <c r="L92" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="48">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="96">
       <c r="A93" s="1" t="s">
-        <v>397</v>
+        <v>794</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>87</v>
+        <v>804</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>88</v>
+        <v>805</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>806</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>42</v>
+        <v>382</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>89</v>
+        <v>808</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>809</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="K93" s="10"/>
-      <c r="L93" s="2" t="s">
-        <v>707</v>
+        <v>812</v>
+      </c>
+      <c r="K93" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="96">
       <c r="A94" s="1" t="s">
-        <v>803</v>
+        <v>869</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>813</v>
+        <v>877</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>814</v>
+        <v>878</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>815</v>
+        <v>879</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>388</v>
+        <v>880</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>817</v>
+        <v>883</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>818</v>
+        <v>881</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>821</v>
+        <v>884</v>
       </c>
       <c r="K94" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="64">
+      <c r="A95" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="K95" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L94" s="6" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="96">
-      <c r="A95" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>888</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="I95" s="2" t="s">
+      <c r="L95" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="48">
+      <c r="A96" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="K96" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="96">
+      <c r="A97" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H97" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="J95" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="K95" s="10">
+      <c r="I97" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="K97" s="10">
         <v>4.7</v>
       </c>
-      <c r="L95" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="64">
-      <c r="A96" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B96" s="2" t="s">
+      <c r="L97" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="48">
+      <c r="A98" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="F98" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="K96" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="48">
-      <c r="A97" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="K97" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="96">
-      <c r="A98" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F98" s="7" t="s">
+      <c r="G98" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>371</v>
-      </c>
       <c r="I98" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="K98" s="10">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>400</v>
+        <v>456</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>379</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="K99" s="10">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="96">
       <c r="A100" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F100" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>388</v>
-      </c>
       <c r="G100" s="2" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="K100" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="96">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>592</v>
+        <v>553</v>
       </c>
       <c r="K101" s="10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>403</v>
+        <v>791</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="K102" s="10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>363</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="K103" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>485</v>
+        <v>606</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>436</v>
+        <v>607</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>608</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>367</v>
+        <v>609</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>368</v>
+        <v>610</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>369</v>
+        <v>611</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>562</v>
+        <v>612</v>
       </c>
       <c r="K104" s="10">
-        <v>4.4000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="48">
-      <c r="A105" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="K105" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J104">
-    <sortCondition ref="I2:I104"/>
-    <sortCondition ref="D2:D104"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J103">
+    <sortCondition ref="I2:I103"/>
+    <sortCondition ref="D2:D103"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8364,66 +8288,65 @@
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
     <hyperlink ref="H62" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
     <hyperlink ref="H60" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H64" r:id="rId21" xr:uid="{02BCB13E-490C-5A49-B385-D01FC01F5A3B}"/>
-    <hyperlink ref="H61" r:id="rId22" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H63" r:id="rId23" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H56" r:id="rId24" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H55" r:id="rId25" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H59" r:id="rId26" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H58" r:id="rId27" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H65" r:id="rId28" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H57" r:id="rId29" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H86" r:id="rId30" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H32" r:id="rId31" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H31" r:id="rId32" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H25" r:id="rId33" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H27" r:id="rId34" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H26" r:id="rId35" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H22" r:id="rId36" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H28" r:id="rId37" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H30" r:id="rId38" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H23" r:id="rId39" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H24" r:id="rId40" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H29" r:id="rId41" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H21" r:id="rId42" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H104" r:id="rId43" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H98" r:id="rId44" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H96" r:id="rId45" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H99" r:id="rId46" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H100" r:id="rId47" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H101" r:id="rId48" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H102" r:id="rId49" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H87" r:id="rId50" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H78" r:id="rId51" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H90" r:id="rId52" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H76" r:id="rId53" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H79" r:id="rId54" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H89" r:id="rId55" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H97" r:id="rId56" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H48" r:id="rId57" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H84" r:id="rId58" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H105" r:id="rId59" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H66" r:id="rId60" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H94" r:id="rId61" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L94" r:id="rId62" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H49" r:id="rId63" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L49" r:id="rId64" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H50" r:id="rId65" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L50" r:id="rId66" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H46" r:id="rId67" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H18" r:id="rId68" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L18" r:id="rId69" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H19" r:id="rId70" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L20" r:id="rId71" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H20" r:id="rId72" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H17" r:id="rId73" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L17" r:id="rId74" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H95" r:id="rId75" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L95" r:id="rId76" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H16" r:id="rId77" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L16" r:id="rId78" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H54" r:id="rId79" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H15" r:id="rId80" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H61" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H63" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H56" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H55" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H59" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H58" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H64" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H57" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H85" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H32" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H31" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H25" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H27" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H26" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H22" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H28" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H30" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H23" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H24" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H29" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H21" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H103" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H97" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H95" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H98" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H99" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H100" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H101" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H86" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H77" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H89" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H75" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H78" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H88" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H96" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H48" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H83" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H104" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H65" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H93" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L93" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H49" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L49" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H50" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L50" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H46" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H18" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L18" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H19" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L20" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H20" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H17" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L17" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H94" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L94" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H16" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L16" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H54" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H15" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7312280-3996-4B43-AECB-26F262A6762E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E36B832-8EEE-6745-AA9B-327A2590B6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="500" windowWidth="39860" windowHeight="22540" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="4820" yWindow="1200" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="922">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3869,6 +3869,44 @@
   </si>
   <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-飛機河粉.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一藤燒肉丼飯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化北路二段88號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2600-9159</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30 - 14:30, 17:30-21:00, 週一公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://restaurant-1118261.business.site/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E4%B8%80%E8%97%A4%E7%87%92%E8%82%89%E4%B8%BC%E9%A3%AF/@25.0827839,121.3691437,15.07z/data=!4m5!3m4!1s0x3442a793f7cffb7b:0xf4ecb7e0fc4dab0a!8m2!3d25.0827293!4d121.3708801?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:    &lt;a style="button" class="btn btn-info"  href="https://shop.ichefpos.com/store/Xs9G1JvD/ordering"&gt;菜單&lt;/a&gt; &amp;nbsp;
+ &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/hashtag/%E4%B8%80%E8%97%A4%E7%87%92%E8%82%89%E4%B8%BC%E9%A3%AF"&gt;推薦&lt;/a&gt;  &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-一藤燒肉丼飯.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4303,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5460,202 +5498,202 @@
         <v>643</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="64">
+    <row r="31" spans="1:12" ht="96">
       <c r="A31" s="1" t="s">
-        <v>102</v>
+        <v>913</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>501</v>
+        <v>914</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>295</v>
+        <v>915</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>296</v>
+        <v>916</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>297</v>
+        <v>917</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>733</v>
+        <v>921</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>298</v>
+        <v>918</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="K31" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="96">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="64">
       <c r="A32" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>407</v>
+        <v>295</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K32" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="96">
       <c r="A33" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>161</v>
+        <v>293</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>162</v>
+        <v>734</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K33" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="64">
       <c r="A34" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K34" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="80">
       <c r="A35" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K35" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="96">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="64">
       <c r="A36" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>441</v>
@@ -5664,226 +5702,226 @@
         <v>153</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K36" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="96">
       <c r="A37" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>444</v>
+        <v>174</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K37" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="96">
       <c r="A38" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>442</v>
+        <v>178</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K38" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="112">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="96">
       <c r="A39" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K39" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="112">
       <c r="A40" s="1" t="s">
-        <v>452</v>
+        <v>136</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>94</v>
+        <v>741</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K40" s="10">
-        <v>4</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="128">
       <c r="A41" s="1" t="s">
-        <v>145</v>
+        <v>452</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K41" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="128">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="112">
       <c r="A42" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>443</v>
@@ -5892,1454 +5930,1454 @@
         <v>108</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K42" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="112">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="128">
       <c r="A43" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>167</v>
+        <v>743</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K43" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="64">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="112">
       <c r="A44" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>444</v>
+        <v>164</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K44" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="80">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="64">
       <c r="A45" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>447</v>
+        <v>169</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>839</v>
+        <v>745</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K45" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="144">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="80">
       <c r="A46" s="1" t="s">
-        <v>832</v>
+        <v>168</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>833</v>
+        <v>146</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>834</v>
+        <v>447</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>838</v>
+        <v>148</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>835</v>
+        <v>150</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>841</v>
+        <v>534</v>
       </c>
       <c r="K46" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="144">
       <c r="A47" s="1" t="s">
-        <v>173</v>
+        <v>832</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>442</v>
+        <v>834</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>406</v>
+        <v>837</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>120</v>
+        <v>838</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>122</v>
+        <v>840</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>559</v>
+        <v>841</v>
       </c>
       <c r="K47" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="48">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="80">
       <c r="A48" s="1" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>597</v>
+        <v>746</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K48" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="80">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="48">
       <c r="A49" s="1" t="s">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>819</v>
+        <v>596</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>816</v>
+        <v>597</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>821</v>
+        <v>598</v>
       </c>
       <c r="K49" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="80">
       <c r="A50" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>446</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K50" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="128">
+      <c r="A51" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K50" s="10">
+      <c r="K51" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L50" s="6" t="s">
+      <c r="L51" s="6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="64">
-      <c r="A51" s="1" t="s">
+    <row r="52" spans="1:12" ht="64">
+      <c r="A52" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K51" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="80">
-      <c r="A52" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K52" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="80">
       <c r="A53" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K53" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="96">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="80">
       <c r="A54" s="1" t="s">
-        <v>851</v>
+        <v>187</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>896</v>
+        <v>487</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K54" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="96">
+      <c r="A55" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K54" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="80">
-      <c r="A55" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>563</v>
+        <v>901</v>
       </c>
       <c r="K55" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="48">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="80">
       <c r="A56" s="1" t="s">
-        <v>453</v>
+        <v>191</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>444</v>
+        <v>259</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>750</v>
+        <v>894</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K56" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="64">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="48">
       <c r="A57" s="1" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="K57" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="64">
       <c r="A58" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K58" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="48">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="64">
       <c r="A59" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="K59" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="48">
       <c r="A60" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>442</v>
+        <v>264</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K60" s="10">
         <v>4.3</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>444</v>
+        <v>239</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K61" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="48">
       <c r="A62" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K62" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="96">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K63" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="48">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="96">
       <c r="A64" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>444</v>
+        <v>249</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K64" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>795</v>
+        <v>274</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>801</v>
+        <v>444</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>803</v>
+        <v>278</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>798</v>
+        <v>275</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>796</v>
+        <v>276</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>800</v>
+        <v>542</v>
       </c>
       <c r="K65" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>799</v>
+        <v>673</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="64">
       <c r="A66" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="K66" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="64">
+      <c r="A67" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K66" s="10">
-        <v>4</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="80">
-      <c r="A67" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K67" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="80">
       <c r="A68" s="1" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>443</v>
+        <v>27</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K68" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="112">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="64">
       <c r="A69" s="1" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K69" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="112">
       <c r="A70" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K70" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="64">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="80">
       <c r="A71" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K71" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="64">
       <c r="A72" s="1" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>446</v>
+        <v>55</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K72" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="112">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="80">
       <c r="A73" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K73" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="112">
       <c r="A74" s="1" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>442</v>
+        <v>490</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="K74" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="144">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="48">
       <c r="A75" s="1" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>470</v>
+        <v>62</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>471</v>
+        <v>767</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="K75" s="10">
         <v>4.2</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="144">
       <c r="A76" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>445</v>
+        <v>467</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>33</v>
+        <v>469</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>34</v>
+        <v>768</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K76" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="96">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
       <c r="A77" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>441</v>
+        <v>492</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>461</v>
+        <v>32</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>462</v>
+        <v>769</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K77" s="10">
         <v>3.9</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="96">
       <c r="A78" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K78" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="48">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="64">
       <c r="A79" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>446</v>
+        <v>472</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>25</v>
+        <v>771</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K79" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="48">
       <c r="A80" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>25</v>
@@ -7348,937 +7386,975 @@
         <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K80" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="64">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="80">
       <c r="A81" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K81" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="48">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="64">
       <c r="A82" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K82" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>603</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>604</v>
+        <v>71</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>601</v>
+        <v>775</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J83" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K83" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="48">
+      <c r="A84" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J84" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K84" s="10">
         <v>4.2</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="32">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:12" ht="32">
+      <c r="A85" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C85" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H85" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K84" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="64">
-      <c r="A85" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J85" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K85" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="64">
+      <c r="A86" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="K85" s="10">
+      <c r="K86" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="48">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:12" ht="48">
+      <c r="A87" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="F87" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H86" s="6" t="s">
+      <c r="H87" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="I87" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J86" s="7" t="s">
+      <c r="J87" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="K86" s="10">
+      <c r="K87" s="10">
         <v>4.5</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="96">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:12" ht="96">
+      <c r="A88" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K87" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="64">
-      <c r="A88" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K88" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="112">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="64">
       <c r="A89" s="1" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>362</v>
+        <v>499</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K89" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="96">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="112">
       <c r="A90" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>16</v>
+        <v>782</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="K90" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="96">
       <c r="A91" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="K91" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="48">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="64">
       <c r="A92" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>87</v>
+        <v>495</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>807</v>
+        <v>712</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K92" s="10"/>
+        <v>582</v>
+      </c>
+      <c r="K92" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L92" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="96">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="48">
       <c r="A93" s="1" t="s">
-        <v>794</v>
+        <v>391</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>806</v>
+        <v>422</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K93" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
+      </c>
+      <c r="K93" s="10"/>
+      <c r="L93" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="96">
       <c r="A94" s="1" t="s">
-        <v>869</v>
+        <v>794</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K94" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="96">
+      <c r="A95" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E95" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G95" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="H94" s="6" t="s">
+      <c r="H95" s="6" t="s">
         <v>881</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K94" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="64">
-      <c r="A95" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>583</v>
+        <v>884</v>
       </c>
       <c r="K95" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="64">
       <c r="A96" s="1" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>588</v>
+        <v>423</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>589</v>
+        <v>369</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="K96" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>364</v>
+        <v>587</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>424</v>
+        <v>588</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>367</v>
+        <v>589</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>365</v>
+        <v>590</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K97" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="48">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="96">
       <c r="A98" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K98" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K99" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K100" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="96">
       <c r="A101" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K101" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K102" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>363</v>
+        <v>791</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K103" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>608</v>
+        <v>360</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>611</v>
+        <v>363</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K104" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="48">
+      <c r="A105" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J105" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K104" s="10">
+      <c r="K105" s="10">
         <v>3.4</v>
       </c>
-      <c r="L104" s="2" t="s">
+      <c r="L105" s="2" t="s">
         <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J103">
-    <sortCondition ref="I2:I103"/>
-    <sortCondition ref="D2:D103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J104">
+    <sortCondition ref="I2:I104"/>
+    <sortCondition ref="D2:D104"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H45" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H35" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H43" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H33" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H44" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H36" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H37" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H38" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H34" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H39" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H46" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H36" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H44" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H34" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H45" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H37" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H38" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H39" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H35" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H40" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8286,19 +8362,19 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H62" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H60" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H61" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H63" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H56" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H55" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H59" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H58" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H64" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H57" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H85" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H32" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H31" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H63" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H61" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H62" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H64" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H57" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H56" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H60" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H59" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H65" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H58" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H86" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H33" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H32" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
     <hyperlink ref="H25" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
     <hyperlink ref="H27" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
     <hyperlink ref="H26" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
@@ -8309,31 +8385,31 @@
     <hyperlink ref="H24" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H29" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H21" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H103" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H97" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H95" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H98" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H99" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H100" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H101" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H86" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H77" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H89" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H75" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H78" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H88" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H96" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H48" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H83" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H104" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H65" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H93" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L93" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H49" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L49" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H50" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L50" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H46" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H104" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H98" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H96" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H99" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H100" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H101" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H102" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H87" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H78" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H90" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H76" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H79" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H89" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H97" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H49" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H84" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H105" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H66" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H94" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L94" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H50" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L50" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H51" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L51" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H47" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
     <hyperlink ref="H18" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
     <hyperlink ref="L18" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
     <hyperlink ref="H19" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
@@ -8341,12 +8417,13 @@
     <hyperlink ref="H20" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
     <hyperlink ref="H17" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
     <hyperlink ref="L17" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H94" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L94" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H95" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L95" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
     <hyperlink ref="H16" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
     <hyperlink ref="L16" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H54" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H55" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
     <hyperlink ref="H15" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H31" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E36B832-8EEE-6745-AA9B-327A2590B6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279EC881-B0D4-4646-8C90-9C88339957C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4820" yWindow="1200" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="1500" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="931">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3907,6 +3907,43 @@
   </si>
   <si>
     <t>fig/XLK-311-Restaurant/AiCity-910-一藤燒肉丼飯.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>121</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>展悅浮島咖啡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖啡店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>244台灣新北市林口區文化三路二段455號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00-20:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0880761,121.376978,15.52z/data=!4m5!3m4!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>https://www.coredesignstrategy.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-浮島.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   &lt;a style="button" class="btn btn-info"  href="https://h20vicky.pixnet.net/blog/post/561262413-%e5%8f%b0%e5%8c%97%e7%be%8e%e9%a3%9f-%e6%9e%97%e5%8f%a3-%e6%b5%ae%e5%b3%b6%e5%b1%95%e6%82%85%e5%92%96%e5%95%a1-%e6%88%b0%e6%96%a7%e8%b1%ac%e6%8e%92-%e6%b3%95%e5%bc%8f/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4341,7 +4378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4890,848 +4927,848 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="64">
+    <row r="15" spans="1:12" ht="128">
       <c r="A15" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>907</v>
+        <v>595</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>909</v>
+        <v>929</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>928</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="K15" s="10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="112">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="64">
       <c r="A16" s="1" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>443</v>
+        <v>905</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="K16" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="112">
       <c r="A17" s="1" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="K17" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="80">
       <c r="A18" s="1" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="80">
       <c r="A19" s="1" t="s">
-        <v>851</v>
+        <v>794</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>446</v>
+        <v>843</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K19" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="80">
       <c r="A20" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>444</v>
+        <v>852</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>595</v>
+        <v>854</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>597</v>
+        <v>858</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="K20" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="64">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>860</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C21" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>710</v>
+        <v>862</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>358</v>
+        <v>595</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>863</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>356</v>
+        <v>864</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>513</v>
+        <v>866</v>
       </c>
       <c r="K21" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>447</v>
+        <v>355</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>327</v>
+        <v>710</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K22" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="96">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="64">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K23" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="80">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="96">
       <c r="A24" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>349</v>
+        <v>636</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K24" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="96">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="80">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K25" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="96">
       <c r="A26" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K26" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="80">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="96">
       <c r="A27" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K27" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="64">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="80">
       <c r="A28" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="K28" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="80">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="64">
       <c r="A29" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>444</v>
+        <v>331</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="K29" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="80">
       <c r="A30" s="1" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>441</v>
+        <v>350</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>842</v>
+        <v>520</v>
       </c>
       <c r="K30" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L30" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="80">
+      <c r="A31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="K31" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="96">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:12" ht="96">
+      <c r="A32" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>918</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="K31" s="10">
-        <v>5</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="64">
-      <c r="A32" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="K32" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="96">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="64">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>407</v>
+        <v>295</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K33" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="96">
       <c r="A34" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>161</v>
+        <v>293</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>162</v>
+        <v>734</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K34" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="64">
       <c r="A35" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K35" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="80">
       <c r="A36" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K36" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="96">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="64">
       <c r="A37" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>441</v>
@@ -5740,226 +5777,226 @@
         <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K37" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="96">
       <c r="A38" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>444</v>
+        <v>174</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K38" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="96">
       <c r="A39" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>442</v>
+        <v>178</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K39" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="112">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="96">
       <c r="A40" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K40" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="112">
       <c r="A41" s="1" t="s">
-        <v>452</v>
+        <v>136</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>94</v>
+        <v>741</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K41" s="10">
-        <v>4</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="128">
       <c r="A42" s="1" t="s">
-        <v>145</v>
+        <v>452</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K42" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="128">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="112">
       <c r="A43" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>443</v>
@@ -5968,1454 +6005,1454 @@
         <v>108</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K43" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="112">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="128">
       <c r="A44" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>167</v>
+        <v>743</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K44" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="64">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="112">
       <c r="A45" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>444</v>
+        <v>164</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K45" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="80">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="64">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>447</v>
+        <v>169</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>839</v>
+        <v>745</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K46" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="144">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="80">
       <c r="A47" s="1" t="s">
-        <v>832</v>
+        <v>168</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>833</v>
+        <v>146</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>834</v>
+        <v>447</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>838</v>
+        <v>148</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>835</v>
+        <v>150</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>841</v>
+        <v>534</v>
       </c>
       <c r="K47" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="144">
       <c r="A48" s="1" t="s">
-        <v>173</v>
+        <v>832</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>442</v>
+        <v>834</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>406</v>
+        <v>837</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>120</v>
+        <v>838</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>122</v>
+        <v>840</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>559</v>
+        <v>841</v>
       </c>
       <c r="K48" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="48">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="80">
       <c r="A49" s="1" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>597</v>
+        <v>746</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K49" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="80">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="48">
       <c r="A50" s="1" t="s">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>819</v>
+        <v>596</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>816</v>
+        <v>597</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>821</v>
+        <v>598</v>
       </c>
       <c r="K50" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="80">
       <c r="A51" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>446</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K51" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="128">
+      <c r="A52" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J52" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K52" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L51" s="6" t="s">
+      <c r="L52" s="6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="64">
-      <c r="A52" s="1" t="s">
+    <row r="53" spans="1:12" ht="64">
+      <c r="A53" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K52" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="80">
-      <c r="A53" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K53" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="80">
       <c r="A54" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K54" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="96">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>851</v>
+        <v>187</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>896</v>
+        <v>487</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K55" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="96">
+      <c r="A56" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G56" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K55" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="80">
-      <c r="A56" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>563</v>
+        <v>901</v>
       </c>
       <c r="K56" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="48">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="80">
       <c r="A57" s="1" t="s">
-        <v>453</v>
+        <v>191</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>444</v>
+        <v>259</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>750</v>
+        <v>894</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K57" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="64">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="48">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="K58" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="64">
       <c r="A59" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K59" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="48">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="64">
       <c r="A60" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="K60" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>442</v>
+        <v>264</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K61" s="10">
         <v>4.3</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="48">
       <c r="A62" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>444</v>
+        <v>239</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K62" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K63" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="96">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K64" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="48">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="96">
       <c r="A65" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>444</v>
+        <v>249</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K65" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>795</v>
+        <v>274</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>801</v>
+        <v>444</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>803</v>
+        <v>278</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>798</v>
+        <v>275</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>796</v>
+        <v>276</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>800</v>
+        <v>542</v>
       </c>
       <c r="K66" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>799</v>
+        <v>673</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="64">
       <c r="A67" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="K67" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="64">
+      <c r="A68" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K67" s="10">
-        <v>4</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="80">
-      <c r="A68" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K68" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="80">
       <c r="A69" s="1" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>443</v>
+        <v>27</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K69" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="112">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="64">
       <c r="A70" s="1" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K70" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="112">
       <c r="A71" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K71" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="80">
       <c r="A72" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K72" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="64">
       <c r="A73" s="1" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>446</v>
+        <v>55</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K73" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="112">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="80">
       <c r="A74" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K74" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="112">
       <c r="A75" s="1" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>442</v>
+        <v>490</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="K75" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="144">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="48">
       <c r="A76" s="1" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>470</v>
+        <v>62</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>471</v>
+        <v>767</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="K76" s="10">
         <v>4.2</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="144">
       <c r="A77" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>445</v>
+        <v>467</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>33</v>
+        <v>469</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>34</v>
+        <v>768</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K77" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="96">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="64">
       <c r="A78" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>441</v>
+        <v>492</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>461</v>
+        <v>32</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>462</v>
+        <v>769</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K78" s="10">
         <v>3.9</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="96">
       <c r="A79" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K79" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="48">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="64">
       <c r="A80" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>446</v>
+        <v>472</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>25</v>
+        <v>771</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K80" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="48">
       <c r="A81" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>25</v>
@@ -7424,937 +7461,975 @@
         <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K81" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="80">
       <c r="A82" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K82" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="48">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="64">
       <c r="A83" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K83" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="48">
       <c r="A84" s="1" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>603</v>
+        <v>70</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>604</v>
+        <v>71</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>601</v>
+        <v>775</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J84" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K84" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="48">
+      <c r="A85" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K85" s="10">
         <v>4.2</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="32">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:12" ht="32">
+      <c r="A86" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K85" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="64">
-      <c r="A86" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J86" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K86" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="64">
+      <c r="A87" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="K86" s="10">
+      <c r="K87" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="48">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:12" ht="48">
+      <c r="A88" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D88" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E88" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F88" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H87" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I87" s="2" t="s">
+      <c r="I88" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J87" s="7" t="s">
+      <c r="J88" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="K87" s="10">
+      <c r="K88" s="10">
         <v>4.5</v>
       </c>
-      <c r="L87" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="96">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:12" ht="96">
+      <c r="A89" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H89" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K88" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="64">
-      <c r="A89" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K89" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="112">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="64">
       <c r="A90" s="1" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>362</v>
+        <v>499</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K90" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="96">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="112">
       <c r="A91" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>16</v>
+        <v>782</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="K91" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="96">
       <c r="A92" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="K92" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="48">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="64">
       <c r="A93" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>87</v>
+        <v>495</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>807</v>
+        <v>712</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K93" s="10"/>
+        <v>582</v>
+      </c>
+      <c r="K93" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L93" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="96">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="48">
       <c r="A94" s="1" t="s">
-        <v>794</v>
+        <v>391</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>806</v>
+        <v>422</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K94" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
+      </c>
+      <c r="K94" s="10"/>
+      <c r="L94" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="96">
       <c r="A95" s="1" t="s">
-        <v>869</v>
+        <v>794</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K95" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="96">
+      <c r="A96" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E96" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G96" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="H95" s="6" t="s">
+      <c r="H96" s="6" t="s">
         <v>881</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J95" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K95" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="64">
-      <c r="A96" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>583</v>
+        <v>884</v>
       </c>
       <c r="K96" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="64">
       <c r="A97" s="1" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>588</v>
+        <v>423</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>589</v>
+        <v>369</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="K97" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="48">
       <c r="A98" s="1" t="s">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>364</v>
+        <v>587</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>424</v>
+        <v>588</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>367</v>
+        <v>589</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>365</v>
+        <v>590</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K98" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="48">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="96">
       <c r="A99" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K99" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K100" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K101" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="96">
       <c r="A102" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K102" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K103" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>363</v>
+        <v>791</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K104" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="48">
       <c r="A105" s="1" t="s">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>608</v>
+        <v>360</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>611</v>
+        <v>363</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J105" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K105" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="48">
+      <c r="A106" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J106" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K105" s="10">
+      <c r="K106" s="10">
         <v>3.4</v>
       </c>
-      <c r="L105" s="2" t="s">
+      <c r="L106" s="2" t="s">
         <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J104">
-    <sortCondition ref="I2:I104"/>
-    <sortCondition ref="D2:D104"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
+    <sortCondition ref="I2:I105"/>
+    <sortCondition ref="D2:D105"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H46" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H36" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H44" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H34" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H45" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H37" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H38" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H39" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H35" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H40" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H47" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H37" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H45" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H35" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H46" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H38" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H39" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H40" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H36" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H41" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8362,68 +8437,69 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H63" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H61" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H62" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H64" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H57" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H56" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H60" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H59" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H65" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H58" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H86" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H33" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H32" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H25" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H27" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H26" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H22" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H28" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H30" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H23" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H24" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H29" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H21" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H104" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H98" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H96" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H99" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H100" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H101" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H102" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H87" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H78" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H90" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H76" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H79" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H89" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H97" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H49" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H84" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H105" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H66" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H94" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L94" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H50" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L50" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H51" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L51" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H47" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H18" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L18" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H19" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L20" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H20" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H17" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L17" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H95" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L95" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H16" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L16" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H55" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H15" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H31" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H64" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H62" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H63" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H65" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H58" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H57" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H61" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H60" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H66" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H59" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H87" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H34" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H33" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H26" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H28" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H27" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H23" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H29" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H31" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H24" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H25" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H30" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H22" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H105" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H99" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H97" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H100" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H101" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H102" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H103" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H88" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H79" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H91" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H77" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H80" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H90" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H98" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H50" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H85" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H106" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H67" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H95" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L95" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H51" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L51" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H52" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L52" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H48" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H19" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L19" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H20" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L21" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H21" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H18" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L18" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H96" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L96" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H17" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L17" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H56" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H16" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H32" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H15" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279EC881-B0D4-4646-8C90-9C88339957C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1491A473-73CA-B54C-AE43-D674354A2BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="930">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3914,35 +3914,33 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>展悅浮島咖啡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>咖啡店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>244台灣新北市林口區文化三路二段455號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:00-20:30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.google.ca/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0880761,121.376978,15.52z/data=!4m5!3m4!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853?hl=zh-TW&amp;authuser=0</t>
-  </si>
-  <si>
-    <t>https://www.coredesignstrategy.com/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-311-Restaurant/AiCity-910-浮島.jpeg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
-   &lt;a style="button" class="btn btn-info"  href="https://h20vicky.pixnet.net/blog/post/561262413-%e5%8f%b0%e5%8c%97%e7%be%8e%e9%a3%9f-%e6%9e%97%e5%8f%a3-%e6%b5%ae%e5%b3%b6%e5%b1%95%e6%82%85%e5%92%96%e5%95%a1-%e6%88%b0%e6%96%a7%e8%b1%ac%e6%8e%92-%e6%b3%95%e5%bc%8f/"&gt;推薦&lt;/a&gt; &amp;nbsp;
+    <t>食之有情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>244台灣新北市林口區文化三路一段358-2號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2609-2911</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-食之有情.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://restaurant-52955.business.site/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   &lt;a style="button" class="btn btn-info"  href="https://www.walkerland.com.tw/article/view/316626?page=full&amp;fbclid=IwAR19gOB7xr1em2_o4u9H8VBfB2eqRIB92NPUs-zAqL5e2ASc9KpMhzHwZKU"&gt;推薦&lt;/a&gt; &amp;nbsp;
+   &lt;a style="button" class="btn btn-info" href="https://inline.app/booking/-MFdKw1RPdXt9p0FMp0V:inline-live-1/-MFdKw9Vk6AEuFh9Rovj"&gt;預約&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4935,19 +4933,19 @@
         <v>923</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="F15" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>929</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>928</v>
@@ -4956,12 +4954,12 @@
         <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="K15" s="10">
         <v>4.3</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="6" t="s">
         <v>927</v>
       </c>
     </row>
@@ -8500,6 +8498,7 @@
     <hyperlink ref="H16" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
     <hyperlink ref="H32" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
     <hyperlink ref="H15" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L15" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1491A473-73CA-B54C-AE43-D674354A2BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F236487E-419E-EA4C-8313-D77AC7AE6BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="939">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3918,10 +3918,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>244台灣新北市林口區文化三路一段358-2號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>02-2609-2911</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3943,6 +3939,49 @@
    &lt;a style="button" class="btn btn-info" href="https://inline.app/booking/-MFdKw1RPdXt9p0FMp0V:inline-live-1/-MFdKw9Vk6AEuFh9Rovj"&gt;預約&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>122</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂一鍋－林口昕境店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段402巷2號3樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段358-2號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2608-8346</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30 - 15:00, 17:00 - 21:30, 週六 11:00 - 22:00, 週日 11:00 - 21:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-狂一鍋.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/twfondueretro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E7%8B%82%E4%B8%80%E9%8D%8B%EF%BC%8D%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a78d12f7e6cf:0x27f5b8688b188ede!8m2!3d25.0736495!4d121.3688417?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/twfondueretro/menu/"&gt;菜單&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://www.walkerland.com.tw/article/view/318842"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4376,7 +4415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4925,886 +4964,886 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="128">
+    <row r="15" spans="1:12" ht="64">
       <c r="A15" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>443</v>
+        <v>930</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>404</v>
+        <v>934</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>928</v>
+        <v>935</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>936</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="K15" s="10">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="128">
+      <c r="A16" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>927</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="64">
-      <c r="A16" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>909</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="K16" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="112">
+        <v>4.3</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>443</v>
+        <v>905</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="K17" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="112">
       <c r="A18" s="1" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="K18" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="80">
       <c r="A19" s="1" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="K19" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="80">
       <c r="A20" s="1" t="s">
-        <v>851</v>
+        <v>794</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>446</v>
+        <v>843</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K20" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>444</v>
+        <v>852</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>595</v>
+        <v>854</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>597</v>
+        <v>858</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="K21" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="64">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>860</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C22" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>710</v>
+        <v>862</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>358</v>
+        <v>595</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>863</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>356</v>
+        <v>864</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>513</v>
+        <v>866</v>
       </c>
       <c r="K22" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="80">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>447</v>
+        <v>355</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>327</v>
+        <v>710</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K23" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="96">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="64">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K24" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="80">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="96">
       <c r="A25" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>349</v>
+        <v>636</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K25" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="96">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="80">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K26" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="96">
       <c r="A27" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K27" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="80">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="96">
       <c r="A28" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K28" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="64">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="80">
       <c r="A29" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="K29" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="80">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="64">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>444</v>
+        <v>331</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="K30" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="80">
       <c r="A31" s="1" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>441</v>
+        <v>350</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>842</v>
+        <v>520</v>
       </c>
       <c r="K31" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="80">
+      <c r="A32" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="K32" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="96">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:12" ht="96">
+      <c r="A33" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>918</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="K32" s="10">
-        <v>5</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="64">
-      <c r="A33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="K33" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="96">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="64">
       <c r="A34" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>407</v>
+        <v>295</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K34" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="96">
       <c r="A35" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>161</v>
+        <v>293</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>162</v>
+        <v>734</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K35" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="64">
       <c r="A36" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K36" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="80">
       <c r="A37" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K37" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="96">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="64">
       <c r="A38" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>441</v>
@@ -5813,226 +5852,226 @@
         <v>153</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K38" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="96">
       <c r="A39" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>444</v>
+        <v>174</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K39" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="96">
       <c r="A40" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>442</v>
+        <v>178</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K40" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="112">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="96">
       <c r="A41" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K41" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="112">
       <c r="A42" s="1" t="s">
-        <v>452</v>
+        <v>136</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>94</v>
+        <v>741</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K42" s="10">
-        <v>4</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="128">
       <c r="A43" s="1" t="s">
-        <v>145</v>
+        <v>452</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K43" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="128">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="112">
       <c r="A44" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>443</v>
@@ -6041,1454 +6080,1454 @@
         <v>108</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K44" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="112">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="128">
       <c r="A45" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>167</v>
+        <v>743</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K45" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="64">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="112">
       <c r="A46" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>444</v>
+        <v>164</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K46" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="80">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="64">
       <c r="A47" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>447</v>
+        <v>169</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>839</v>
+        <v>745</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K47" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="144">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="80">
       <c r="A48" s="1" t="s">
-        <v>832</v>
+        <v>168</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>833</v>
+        <v>146</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>834</v>
+        <v>447</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>838</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>835</v>
+        <v>150</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>841</v>
+        <v>534</v>
       </c>
       <c r="K48" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="144">
       <c r="A49" s="1" t="s">
-        <v>173</v>
+        <v>832</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>442</v>
+        <v>834</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>406</v>
+        <v>837</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>120</v>
+        <v>838</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>122</v>
+        <v>840</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>559</v>
+        <v>841</v>
       </c>
       <c r="K49" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="48">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="80">
       <c r="A50" s="1" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>597</v>
+        <v>746</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K50" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="80">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="48">
       <c r="A51" s="1" t="s">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>819</v>
+        <v>596</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>816</v>
+        <v>597</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>821</v>
+        <v>598</v>
       </c>
       <c r="K51" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="80">
       <c r="A52" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>446</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K52" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="128">
+      <c r="A53" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J53" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K53" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L52" s="6" t="s">
+      <c r="L53" s="6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="64">
-      <c r="A53" s="1" t="s">
+    <row r="54" spans="1:12" ht="64">
+      <c r="A54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K53" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="80">
-      <c r="A54" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K54" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K55" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="96">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="80">
       <c r="A56" s="1" t="s">
-        <v>851</v>
+        <v>187</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>896</v>
+        <v>487</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K56" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="96">
+      <c r="A57" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H57" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K56" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="80">
-      <c r="A57" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>563</v>
+        <v>901</v>
       </c>
       <c r="K57" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="48">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="80">
       <c r="A58" s="1" t="s">
-        <v>453</v>
+        <v>191</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>444</v>
+        <v>259</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>750</v>
+        <v>894</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K58" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="64">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="48">
       <c r="A59" s="1" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="K59" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="64">
       <c r="A60" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K60" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="48">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="64">
       <c r="A61" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="K61" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="48">
       <c r="A62" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>442</v>
+        <v>264</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K62" s="10">
         <v>4.3</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>444</v>
+        <v>239</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K63" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K64" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="96">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K65" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="48">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="96">
       <c r="A66" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>444</v>
+        <v>249</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K66" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="48">
       <c r="A67" s="1" t="s">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>795</v>
+        <v>274</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>801</v>
+        <v>444</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>803</v>
+        <v>278</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>798</v>
+        <v>275</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>796</v>
+        <v>276</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>800</v>
+        <v>542</v>
       </c>
       <c r="K67" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>799</v>
+        <v>673</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="64">
       <c r="A68" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="K68" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="64">
+      <c r="A69" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K68" s="10">
-        <v>4</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="80">
-      <c r="A69" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K69" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="80">
       <c r="A70" s="1" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>443</v>
+        <v>27</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K70" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="112">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="64">
       <c r="A71" s="1" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K71" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="112">
       <c r="A72" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K72" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="64">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="80">
       <c r="A73" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K73" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="64">
       <c r="A74" s="1" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>446</v>
+        <v>55</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K74" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="112">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="80">
       <c r="A75" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K75" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="112">
       <c r="A76" s="1" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>442</v>
+        <v>490</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="K76" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="144">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="48">
       <c r="A77" s="1" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>470</v>
+        <v>62</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>471</v>
+        <v>767</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="K77" s="10">
         <v>4.2</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="144">
       <c r="A78" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>445</v>
+        <v>467</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>33</v>
+        <v>469</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>34</v>
+        <v>768</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K78" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="96">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="64">
       <c r="A79" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>441</v>
+        <v>492</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>461</v>
+        <v>32</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>462</v>
+        <v>769</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K79" s="10">
         <v>3.9</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="96">
       <c r="A80" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K80" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="48">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="64">
       <c r="A81" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>446</v>
+        <v>472</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>25</v>
+        <v>771</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K81" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="48">
       <c r="A82" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>25</v>
@@ -7497,937 +7536,975 @@
         <v>405</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K82" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="64">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="80">
       <c r="A83" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K83" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="48">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="64">
       <c r="A84" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K84" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="48">
       <c r="A85" s="1" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>603</v>
+        <v>70</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>604</v>
+        <v>71</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>601</v>
+        <v>775</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J85" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K85" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="48">
+      <c r="A86" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="K85" s="10">
+      <c r="K86" s="10">
         <v>4.2</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="32">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:12" ht="32">
+      <c r="A87" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C87" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H87" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K86" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="64">
-      <c r="A87" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J87" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K87" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="64">
+      <c r="A88" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J88" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="K87" s="10">
+      <c r="K88" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L87" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="48">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:12" ht="48">
+      <c r="A89" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D89" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E89" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F89" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H88" s="6" t="s">
+      <c r="H89" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="I89" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J88" s="7" t="s">
+      <c r="J89" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="K88" s="10">
+      <c r="K89" s="10">
         <v>4.5</v>
       </c>
-      <c r="L88" s="2" t="s">
+      <c r="L89" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="96">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:12" ht="96">
+      <c r="A90" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C90" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G90" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H90" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K89" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="64">
-      <c r="A90" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K90" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="112">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="64">
       <c r="A91" s="1" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>362</v>
+        <v>499</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K91" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="96">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="112">
       <c r="A92" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>16</v>
+        <v>782</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="K92" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="96">
       <c r="A93" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="K93" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="48">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="64">
       <c r="A94" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>87</v>
+        <v>495</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>807</v>
+        <v>712</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K94" s="10"/>
+        <v>582</v>
+      </c>
+      <c r="K94" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L94" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="96">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>794</v>
+        <v>391</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>806</v>
+        <v>422</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K95" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
+      </c>
+      <c r="K95" s="10"/>
+      <c r="L95" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="96">
       <c r="A96" s="1" t="s">
-        <v>869</v>
+        <v>794</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K96" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="96">
+      <c r="A97" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E97" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G97" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="H96" s="6" t="s">
+      <c r="H97" s="6" t="s">
         <v>881</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K96" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="64">
-      <c r="A97" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>583</v>
+        <v>884</v>
       </c>
       <c r="K97" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="64">
       <c r="A98" s="1" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>588</v>
+        <v>423</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>589</v>
+        <v>369</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="K98" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>364</v>
+        <v>587</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>424</v>
+        <v>588</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>367</v>
+        <v>589</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>365</v>
+        <v>590</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K99" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="48">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="96">
       <c r="A100" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K100" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K101" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K102" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="96">
       <c r="A103" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K103" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K104" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="48">
       <c r="A105" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>363</v>
+        <v>791</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K105" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="48">
       <c r="A106" s="1" t="s">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>608</v>
+        <v>360</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>611</v>
+        <v>363</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J106" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K106" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="48">
+      <c r="A107" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J107" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K106" s="10">
+      <c r="K107" s="10">
         <v>3.4</v>
       </c>
-      <c r="L106" s="2" t="s">
+      <c r="L107" s="2" t="s">
         <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
-    <sortCondition ref="I2:I105"/>
-    <sortCondition ref="D2:D105"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J106">
+    <sortCondition ref="I2:I106"/>
+    <sortCondition ref="D2:D106"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H47" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H37" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H45" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H35" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H46" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H38" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H39" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H40" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H36" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H41" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H48" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H38" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H46" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H36" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H47" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H39" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H40" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H41" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H37" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H42" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8435,70 +8512,72 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H64" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H62" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H63" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H65" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H58" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H57" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H61" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H60" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H66" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H59" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H87" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H34" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H33" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H26" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H28" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H27" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H23" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H29" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H31" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H24" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H25" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H30" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H22" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H105" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H99" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H97" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H100" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H101" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H102" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H103" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H88" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H79" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H91" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H77" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H80" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H90" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H98" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H50" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H85" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H106" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H67" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H95" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L95" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H51" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L51" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H52" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L52" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H48" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H19" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L19" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H20" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L21" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H21" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H18" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L18" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H96" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L96" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H17" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L17" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H56" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H16" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H32" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
-    <hyperlink ref="H15" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
-    <hyperlink ref="L15" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H65" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H63" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H64" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H66" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H59" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H58" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H62" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H61" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H67" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H60" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H88" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H35" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H34" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H27" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H29" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H28" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H24" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H30" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H32" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H25" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H26" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H31" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H23" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H106" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H100" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H98" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H101" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H102" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H103" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H104" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H89" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H80" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H92" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H78" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H81" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H91" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H99" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H51" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H86" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H107" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H68" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H96" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L96" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H52" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L52" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H53" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L53" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H49" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H20" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L20" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H21" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L22" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H22" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H19" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L19" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H97" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L97" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H18" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L18" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H57" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H17" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H33" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H16" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L16" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H15" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
+    <hyperlink ref="L15" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F236487E-419E-EA4C-8313-D77AC7AE6BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819286F0-0C59-324E-902B-2CF1273EED4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="948">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3982,6 +3982,44 @@
   &lt;a style="button" class="btn btn-info"  href="https://www.walkerland.com.tw/article/view/318842"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>123</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超夯の燒肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段402巷2號6樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2609-2066</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00 - 01:00, 週六日 11:00 - 01:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-超夯燒肉.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://st-paul.ego.tw/?fbclid=IwAR0e3RuSNMQx3lpBuk4V4bsBCy0F3F4bfWXQsVkqk4iyFU3O5iZDrV06qcg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="fig/XLK-311-Restaurant/AiCity-910-超夯燒肉菜單.jpeg"&gt;菜單&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://nash.tw/chaohang/"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E8%B6%85%E5%A4%AF%E3%81%AE%E7%87%92%E8%82%89-%E6%9E%97%E5%8F%A3%E5%BA%97+%E9%A0%82%E7%B4%9A%E5%92%8C%E7%89%9B%E7%87%92%E8%82%89%E5%90%83%E5%88%B0%E9%A3%BD/@25.0737528,121.3666483,17z/data=!3m2!4b1!5s0x3442a6d8f30e1025:0x367943ec0aa44314!4m5!3m4!1s0x3442a7316d91d851:0x55fd0de8c182b5a3!8m2!3d25.073748!4d121.368837?hl=zh-TW&amp;authuser=0</t>
   </si>
 </sst>
 </file>
@@ -4415,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4966,922 +5004,922 @@
     </row>
     <row r="15" spans="1:12" ht="64">
       <c r="A15" s="1" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="K15" s="10">
-        <v>5</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="128">
+        <v>4.5</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="64">
       <c r="A16" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>443</v>
+        <v>930</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>404</v>
+        <v>934</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>927</v>
+        <v>935</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>936</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="K16" s="10">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="64">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="128">
       <c r="A17" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>905</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>908</v>
+        <v>404</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>909</v>
+        <v>925</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>927</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="K17" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="112">
+        <v>4.3</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="64">
       <c r="A18" s="1" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>443</v>
+        <v>905</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="112">
       <c r="A19" s="1" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="K19" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="80">
       <c r="A20" s="1" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="K20" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
-        <v>851</v>
+        <v>794</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>446</v>
+        <v>843</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K21" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>444</v>
+        <v>852</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>595</v>
+        <v>854</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>597</v>
+        <v>858</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="K22" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="64">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>860</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C23" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>710</v>
+        <v>862</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>358</v>
+        <v>595</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>863</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>356</v>
+        <v>864</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>513</v>
+        <v>866</v>
       </c>
       <c r="K23" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>447</v>
+        <v>355</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>327</v>
+        <v>710</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K24" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="96">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="64">
       <c r="A25" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K25" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="80">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="96">
       <c r="A26" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>349</v>
+        <v>636</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K26" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="96">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="80">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K27" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="96">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K28" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="80">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="96">
       <c r="A29" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K29" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="64">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="80">
       <c r="A30" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="K30" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="80">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="64">
       <c r="A31" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>444</v>
+        <v>331</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="K31" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="80">
       <c r="A32" s="1" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>441</v>
+        <v>350</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>842</v>
+        <v>520</v>
       </c>
       <c r="K32" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="80">
+      <c r="A33" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="K33" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="96">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:12" ht="96">
+      <c r="A34" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>918</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="K33" s="10">
-        <v>5</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="64">
-      <c r="A34" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="K34" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="96">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="64">
       <c r="A35" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>407</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K35" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="96">
       <c r="A36" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>161</v>
+        <v>293</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>162</v>
+        <v>734</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K36" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="64">
       <c r="A37" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K37" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="80">
       <c r="A38" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K38" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="96">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="64">
       <c r="A39" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>441</v>
@@ -5890,226 +5928,226 @@
         <v>153</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K39" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="96">
       <c r="A40" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>444</v>
+        <v>174</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K40" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="96">
       <c r="A41" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>442</v>
+        <v>178</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K41" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="112">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="96">
       <c r="A42" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K42" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L42" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="112">
       <c r="A43" s="1" t="s">
-        <v>452</v>
+        <v>136</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>94</v>
+        <v>741</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K43" s="10">
-        <v>4</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="128">
       <c r="A44" s="1" t="s">
-        <v>145</v>
+        <v>452</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K44" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="128">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="112">
       <c r="A45" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>443</v>
@@ -6118,1454 +6156,1454 @@
         <v>108</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K45" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="112">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="128">
       <c r="A46" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>167</v>
+        <v>743</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K46" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="64">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="112">
       <c r="A47" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>444</v>
+        <v>164</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K47" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="80">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="64">
       <c r="A48" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>447</v>
+        <v>169</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>839</v>
+        <v>745</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K48" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="144">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="80">
       <c r="A49" s="1" t="s">
-        <v>832</v>
+        <v>168</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>833</v>
+        <v>146</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>834</v>
+        <v>447</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>838</v>
+        <v>148</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>835</v>
+        <v>150</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>841</v>
+        <v>534</v>
       </c>
       <c r="K49" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="144">
       <c r="A50" s="1" t="s">
-        <v>173</v>
+        <v>832</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>442</v>
+        <v>834</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>406</v>
+        <v>837</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>120</v>
+        <v>838</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>122</v>
+        <v>840</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>559</v>
+        <v>841</v>
       </c>
       <c r="K50" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="48">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="80">
       <c r="A51" s="1" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>597</v>
+        <v>746</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K51" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="80">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="48">
       <c r="A52" s="1" t="s">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>819</v>
+        <v>596</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>816</v>
+        <v>597</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>821</v>
+        <v>598</v>
       </c>
       <c r="K52" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="80">
       <c r="A53" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>446</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J53" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K53" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="128">
+      <c r="A54" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J54" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K54" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L53" s="6" t="s">
+      <c r="L54" s="6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="64">
-      <c r="A54" s="1" t="s">
+    <row r="55" spans="1:12" ht="64">
+      <c r="A55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K54" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="80">
-      <c r="A55" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K55" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="80">
       <c r="A56" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K56" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="96">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="80">
       <c r="A57" s="1" t="s">
-        <v>851</v>
+        <v>187</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>896</v>
+        <v>487</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K57" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="96">
+      <c r="A58" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K57" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="80">
-      <c r="A58" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>563</v>
+        <v>901</v>
       </c>
       <c r="K58" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="48">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="80">
       <c r="A59" s="1" t="s">
-        <v>453</v>
+        <v>191</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>444</v>
+        <v>259</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>750</v>
+        <v>894</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K59" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="64">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="48">
       <c r="A60" s="1" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="K60" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="64">
       <c r="A61" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K61" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="48">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="64">
       <c r="A62" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="K62" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>442</v>
+        <v>264</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K63" s="10">
         <v>4.3</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>444</v>
+        <v>239</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K64" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K65" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="96">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K66" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="48">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="96">
       <c r="A67" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>444</v>
+        <v>249</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K67" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="48">
       <c r="A68" s="1" t="s">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>795</v>
+        <v>274</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>801</v>
+        <v>444</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>803</v>
+        <v>278</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>798</v>
+        <v>275</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>796</v>
+        <v>276</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>800</v>
+        <v>542</v>
       </c>
       <c r="K68" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>799</v>
+        <v>673</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="64">
       <c r="A69" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="K69" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="64">
+      <c r="A70" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K69" s="10">
-        <v>4</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="80">
-      <c r="A70" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K70" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="80">
       <c r="A71" s="1" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>443</v>
+        <v>27</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K71" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="112">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="64">
       <c r="A72" s="1" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K72" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="112">
       <c r="A73" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K73" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="64">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="80">
       <c r="A74" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K74" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>446</v>
+        <v>55</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K75" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="112">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="80">
       <c r="A76" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K76" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="112">
       <c r="A77" s="1" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>442</v>
+        <v>490</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="K77" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="144">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="48">
       <c r="A78" s="1" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>470</v>
+        <v>62</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>471</v>
+        <v>767</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="K78" s="10">
         <v>4.2</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="144">
       <c r="A79" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>445</v>
+        <v>467</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>33</v>
+        <v>469</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>34</v>
+        <v>768</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K79" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="96">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="64">
       <c r="A80" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>441</v>
+        <v>492</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>461</v>
+        <v>32</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>462</v>
+        <v>769</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K80" s="10">
         <v>3.9</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="96">
       <c r="A81" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K81" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="48">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="64">
       <c r="A82" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>446</v>
+        <v>472</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>25</v>
+        <v>771</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K82" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>25</v>
@@ -7574,937 +7612,975 @@
         <v>405</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K83" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="64">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="80">
       <c r="A84" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K84" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="48">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K85" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="48">
       <c r="A86" s="1" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>603</v>
+        <v>70</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>604</v>
+        <v>71</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>601</v>
+        <v>775</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J86" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K86" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="48">
+      <c r="A87" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="K86" s="10">
+      <c r="K87" s="10">
         <v>4.2</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="32">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:12" ht="32">
+      <c r="A88" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C88" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K87" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="64">
-      <c r="A88" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J88" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K88" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="64">
+      <c r="A89" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="K88" s="10">
+      <c r="K89" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L88" s="2" t="s">
+      <c r="L89" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="48">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:12" ht="48">
+      <c r="A90" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C90" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D90" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E90" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F89" s="7" t="s">
+      <c r="F90" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G90" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H89" s="6" t="s">
+      <c r="H90" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="I90" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J89" s="7" t="s">
+      <c r="J90" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="K89" s="10">
+      <c r="K90" s="10">
         <v>4.5</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="96">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:12" ht="96">
+      <c r="A91" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H91" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K90" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="64">
-      <c r="A91" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K91" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="112">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="64">
       <c r="A92" s="1" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>362</v>
+        <v>499</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K92" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="96">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="112">
       <c r="A93" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>16</v>
+        <v>782</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="K93" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="96">
       <c r="A94" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="K94" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="48">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="64">
       <c r="A95" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>87</v>
+        <v>495</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>807</v>
+        <v>712</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K95" s="10"/>
+        <v>582</v>
+      </c>
+      <c r="K95" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L95" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="96">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="48">
       <c r="A96" s="1" t="s">
-        <v>794</v>
+        <v>391</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>806</v>
+        <v>422</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K96" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
+      </c>
+      <c r="K96" s="10"/>
+      <c r="L96" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="96">
       <c r="A97" s="1" t="s">
-        <v>869</v>
+        <v>794</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K97" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="96">
+      <c r="A98" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E98" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F98" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G98" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="H97" s="6" t="s">
+      <c r="H98" s="6" t="s">
         <v>881</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K97" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="64">
-      <c r="A98" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>583</v>
+        <v>884</v>
       </c>
       <c r="K98" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="64">
       <c r="A99" s="1" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>588</v>
+        <v>423</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>589</v>
+        <v>369</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="K99" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="48">
       <c r="A100" s="1" t="s">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>364</v>
+        <v>587</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>424</v>
+        <v>588</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>367</v>
+        <v>589</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>365</v>
+        <v>590</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K100" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="48">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="96">
       <c r="A101" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K101" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="48">
       <c r="A102" s="1" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K102" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K103" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="96">
       <c r="A104" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K104" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="48">
       <c r="A105" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K105" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="48">
       <c r="A106" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>363</v>
+        <v>791</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K106" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="48">
       <c r="A107" s="1" t="s">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>608</v>
+        <v>360</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>611</v>
+        <v>363</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J107" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K107" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="48">
+      <c r="A108" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J108" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K107" s="10">
+      <c r="K108" s="10">
         <v>3.4</v>
       </c>
-      <c r="L107" s="2" t="s">
+      <c r="L108" s="2" t="s">
         <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J106">
-    <sortCondition ref="I2:I106"/>
-    <sortCondition ref="D2:D106"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J107">
+    <sortCondition ref="I2:I107"/>
+    <sortCondition ref="D2:D107"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H48" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H38" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H46" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H36" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H47" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H39" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H40" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H41" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H37" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H42" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H49" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H39" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H47" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H37" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H48" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H40" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H41" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H42" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H38" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H43" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8512,72 +8588,73 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H65" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H63" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H64" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H66" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H59" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H58" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H62" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H61" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H67" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H60" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H88" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H35" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H34" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H27" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H29" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H28" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H24" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H30" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H32" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H25" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H26" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H31" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H23" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H106" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H100" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H98" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H101" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H102" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H103" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H104" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H89" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H80" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H92" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H78" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H81" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H91" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H99" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H51" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H86" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H107" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H68" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H96" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L96" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H52" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L52" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H53" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L53" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H49" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H20" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L20" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H21" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L22" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H22" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H19" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L19" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H97" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L97" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H18" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L18" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H57" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H17" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H33" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
-    <hyperlink ref="H16" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
-    <hyperlink ref="L16" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
-    <hyperlink ref="H15" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
-    <hyperlink ref="L15" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
+    <hyperlink ref="H66" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H64" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H65" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H67" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H60" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H59" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H63" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H62" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H68" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H61" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H89" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H36" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H35" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H28" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H30" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H29" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H25" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H31" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H33" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H26" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H27" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H32" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H24" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H107" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H101" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H99" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H102" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H103" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H104" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H105" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H90" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H81" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H93" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H79" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H82" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H92" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H100" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H52" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H87" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H108" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H69" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H97" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L97" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H53" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L53" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H54" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L54" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H50" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H21" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L21" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H22" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L23" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H23" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H20" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L20" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H98" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L98" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H19" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L19" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H58" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H18" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H34" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H17" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L17" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H16" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
+    <hyperlink ref="L16" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
+    <hyperlink ref="H15" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819286F0-0C59-324E-902B-2CF1273EED4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883B659C-7A66-734D-8527-E4E43889C93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="956">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4020,6 +4020,41 @@
   </si>
   <si>
     <t>https://www.google.ca/maps/place/%E8%B6%85%E5%A4%AF%E3%81%AE%E7%87%92%E8%82%89-%E6%9E%97%E5%8F%A3%E5%BA%97+%E9%A0%82%E7%B4%9A%E5%92%8C%E7%89%9B%E7%87%92%E8%82%89%E5%90%83%E5%88%B0%E9%A3%BD/@25.0737528,121.3666483,17z/data=!3m2!4b1!5s0x3442a6d8f30e1025:0x367943ec0aa44314!4m5!3m4!1s0x3442a7316d91d851:0x55fd0de8c182b5a3!8m2!3d25.073748!4d121.368837?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>124</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明水然無菜單鐵板燒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2606-8258</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30-15:00, 17:30-21:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-明水然.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://inline.app/booking/-MFnomV1i6SqY_R0HX7j:inline-live-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://tw.news.yahoo.com/%E8%B6%85%E9%9B%A3%E8%A8%82%E4%BD%8D%E9%90%B5%E6%9D%BF%E7%87%92-%E6%98%8E%E6%B0%B4%E7%84%B6-%E6%A8%82%E6%90%B6%E9%80%B2%E6%9E%97%E5%8F%A3-141029874.html"&gt;推薦&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=6Ed_cUtTWPc"&gt;介紹影片&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4453,7 +4488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5002,962 +5037,962 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="64">
+    <row r="15" spans="1:12" ht="112">
       <c r="A15" s="1" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>446</v>
+        <v>949</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>801</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="K15" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>947</v>
+        <v>4.3</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="64">
       <c r="A16" s="1" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="K16" s="10">
-        <v>5</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="128">
+        <v>4.5</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>443</v>
+        <v>930</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>404</v>
+        <v>934</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>927</v>
+        <v>935</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>936</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="K17" s="10">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="64">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="128">
       <c r="A18" s="1" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>905</v>
+        <v>443</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>908</v>
+        <v>404</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>909</v>
+        <v>925</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>927</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="K18" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="112">
+        <v>4.3</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>443</v>
+        <v>905</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
       <c r="K19" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="112">
       <c r="A20" s="1" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="K20" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="K21" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>851</v>
+        <v>794</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>446</v>
+        <v>843</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K22" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="80">
       <c r="A23" s="1" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>444</v>
+        <v>852</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>595</v>
+        <v>854</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>597</v>
+        <v>858</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="K23" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="64">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>860</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C24" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>444</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>710</v>
+        <v>862</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>358</v>
+        <v>595</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>863</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>356</v>
+        <v>864</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>513</v>
+        <v>866</v>
       </c>
       <c r="K24" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="80">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>447</v>
+        <v>355</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>327</v>
+        <v>710</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K25" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="96">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="64">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K26" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="80">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="96">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>349</v>
+        <v>636</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K27" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="96">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="80">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K28" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="96">
       <c r="A29" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K29" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="80">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="96">
       <c r="A30" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K30" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="64">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="80">
       <c r="A31" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="K31" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="80">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="64">
       <c r="A32" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>444</v>
+        <v>331</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="K32" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="80">
       <c r="A33" s="1" t="s">
-        <v>451</v>
+        <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>441</v>
+        <v>350</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>299</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>842</v>
+        <v>520</v>
       </c>
       <c r="K33" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L33" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="80">
+      <c r="A34" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="K34" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="96">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:12" ht="96">
+      <c r="A35" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>918</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="K34" s="10">
-        <v>5</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="64">
-      <c r="A35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
       <c r="K35" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="96">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="64">
       <c r="A36" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>407</v>
+        <v>295</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K36" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="64">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="96">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>159</v>
+        <v>407</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>161</v>
+        <v>293</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>162</v>
+        <v>734</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K37" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="80">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="64">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K38" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="64">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="80">
       <c r="A39" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K39" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="96">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="64">
       <c r="A40" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>441</v>
@@ -5966,226 +6001,226 @@
         <v>153</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K40" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="96">
       <c r="A41" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>444</v>
+        <v>174</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K41" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="96">
       <c r="A42" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>442</v>
+        <v>178</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>180</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K42" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="112">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="96">
       <c r="A43" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K43" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="112">
       <c r="A44" s="1" t="s">
-        <v>452</v>
+        <v>136</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>482</v>
+        <v>192</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>94</v>
+        <v>741</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K44" s="10">
-        <v>4</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="128">
       <c r="A45" s="1" t="s">
-        <v>145</v>
+        <v>452</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K45" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="128">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="112">
       <c r="A46" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>443</v>
@@ -6194,1454 +6229,1454 @@
         <v>108</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K46" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="112">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="128">
       <c r="A47" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>167</v>
+        <v>743</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K47" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="64">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="112">
       <c r="A48" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>444</v>
+        <v>164</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K48" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="80">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="64">
       <c r="A49" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>447</v>
+        <v>169</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>839</v>
+        <v>745</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K49" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="144">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="80">
       <c r="A50" s="1" t="s">
-        <v>832</v>
+        <v>168</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>833</v>
+        <v>146</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>834</v>
+        <v>447</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>838</v>
+        <v>148</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>461</v>
+        <v>149</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>835</v>
+        <v>150</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>841</v>
+        <v>534</v>
       </c>
       <c r="K50" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="144">
       <c r="A51" s="1" t="s">
-        <v>173</v>
+        <v>832</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>119</v>
+        <v>833</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>442</v>
+        <v>834</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>406</v>
+        <v>837</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>838</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>121</v>
+        <v>461</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>122</v>
+        <v>840</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>835</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>559</v>
+        <v>841</v>
       </c>
       <c r="K51" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="48">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="80">
       <c r="A52" s="1" t="s">
-        <v>592</v>
+        <v>173</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>597</v>
+        <v>746</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="K52" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="80">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="48">
       <c r="A53" s="1" t="s">
-        <v>813</v>
+        <v>592</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>823</v>
+        <v>593</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>819</v>
+        <v>596</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>816</v>
+        <v>597</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>821</v>
+        <v>598</v>
       </c>
       <c r="K53" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="80">
       <c r="A54" s="1" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>446</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J54" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="K54" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="128">
+      <c r="A55" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J55" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="K54" s="10">
+      <c r="K55" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L54" s="6" t="s">
+      <c r="L55" s="6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="64">
-      <c r="A55" s="1" t="s">
+    <row r="56" spans="1:12" ht="64">
+      <c r="A56" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K55" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="80">
-      <c r="A56" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>126</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K56" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="80">
       <c r="A57" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K57" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="96">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="80">
       <c r="A58" s="1" t="s">
-        <v>851</v>
+        <v>187</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>896</v>
+        <v>487</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K58" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="96">
+      <c r="A59" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H59" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K58" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="80">
-      <c r="A59" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>563</v>
+        <v>901</v>
       </c>
       <c r="K59" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="48">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="80">
       <c r="A60" s="1" t="s">
-        <v>453</v>
+        <v>191</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>444</v>
+        <v>259</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>750</v>
+        <v>894</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K60" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="64">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="48">
       <c r="A61" s="1" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="K61" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="64">
       <c r="A62" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K62" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="48">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="64">
       <c r="A63" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="K63" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="48">
       <c r="A64" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>442</v>
+        <v>264</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K64" s="10">
         <v>4.3</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>444</v>
+        <v>239</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K65" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K66" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="96">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="48">
       <c r="A67" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>443</v>
+        <v>234</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K67" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="48">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="96">
       <c r="A68" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>444</v>
+        <v>249</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K68" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="64">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="48">
       <c r="A69" s="1" t="s">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>795</v>
+        <v>274</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>801</v>
+        <v>444</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>803</v>
+        <v>278</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>798</v>
+        <v>275</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>797</v>
+        <v>758</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>796</v>
+        <v>276</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>227</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>800</v>
+        <v>542</v>
       </c>
       <c r="K69" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>799</v>
+        <v>673</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="64">
       <c r="A70" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="K70" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="64">
+      <c r="A71" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K70" s="10">
-        <v>4</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="80">
-      <c r="A71" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K71" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="80">
       <c r="A72" s="1" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>443</v>
+        <v>27</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K72" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="112">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="64">
       <c r="A73" s="1" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K73" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="80">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="112">
       <c r="A74" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>50</v>
+        <v>488</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K74" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="64">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="80">
       <c r="A75" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K75" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="80">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="64">
       <c r="A76" s="1" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>446</v>
+        <v>55</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K76" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="112">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="80">
       <c r="A77" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K77" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="48">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="112">
       <c r="A78" s="1" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>442</v>
+        <v>490</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="K78" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="144">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="48">
       <c r="A79" s="1" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>470</v>
+        <v>62</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>471</v>
+        <v>767</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="K79" s="10">
         <v>4.2</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="64">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="144">
       <c r="A80" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>445</v>
+        <v>467</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>33</v>
+        <v>469</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>34</v>
+        <v>768</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K80" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="96">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="64">
       <c r="A81" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>441</v>
+        <v>492</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>461</v>
+        <v>32</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>462</v>
+        <v>769</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K81" s="10">
         <v>3.9</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="96">
       <c r="A82" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K82" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="48">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="64">
       <c r="A83" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>446</v>
+        <v>472</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>24</v>
+        <v>474</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>25</v>
+        <v>771</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K83" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="80">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="48">
       <c r="A84" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>441</v>
+        <v>22</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>446</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>25</v>
@@ -7650,937 +7685,975 @@
         <v>405</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K84" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="64">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="80">
       <c r="A85" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K85" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="48">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="64">
       <c r="A86" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K86" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="48">
       <c r="A87" s="1" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>603</v>
+        <v>70</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>604</v>
+        <v>71</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>601</v>
+        <v>775</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>405</v>
       </c>
       <c r="J87" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K87" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="48">
+      <c r="A88" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J88" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="K87" s="10">
+      <c r="K88" s="10">
         <v>4.2</v>
       </c>
-      <c r="L87" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="32">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:12" ht="32">
+      <c r="A89" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H89" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K88" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="64">
-      <c r="A89" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J89" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K89" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="64">
+      <c r="A90" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="K89" s="10">
+      <c r="K90" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="48">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:12" ht="48">
+      <c r="A91" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D91" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E91" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F91" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H90" s="6" t="s">
+      <c r="H91" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I90" s="2" t="s">
+      <c r="I91" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J90" s="7" t="s">
+      <c r="J91" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="K90" s="10">
+      <c r="K91" s="10">
         <v>4.5</v>
       </c>
-      <c r="L90" s="2" t="s">
+      <c r="L91" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="96">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:12" ht="96">
+      <c r="A92" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C92" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G92" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H92" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K91" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="64">
-      <c r="A92" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K92" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="112">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="64">
       <c r="A93" s="1" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>362</v>
+        <v>499</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K93" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="96">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="112">
       <c r="A94" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>15</v>
+        <v>465</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>16</v>
+        <v>782</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="K94" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="96">
       <c r="A95" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>712</v>
+        <v>783</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="K95" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="48">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="64">
       <c r="A96" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>87</v>
+        <v>495</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>807</v>
+        <v>712</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K96" s="10"/>
+        <v>582</v>
+      </c>
+      <c r="K96" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L96" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="96">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48">
       <c r="A97" s="1" t="s">
-        <v>794</v>
+        <v>391</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>806</v>
+        <v>422</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K97" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
+      </c>
+      <c r="K97" s="10"/>
+      <c r="L97" s="2" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="96">
       <c r="A98" s="1" t="s">
-        <v>869</v>
+        <v>794</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>877</v>
+        <v>804</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K98" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="96">
+      <c r="A99" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E99" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G99" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="H98" s="6" t="s">
+      <c r="H99" s="6" t="s">
         <v>881</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K98" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="64">
-      <c r="A99" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>371</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>583</v>
+        <v>884</v>
       </c>
       <c r="K99" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="64">
       <c r="A100" s="1" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>587</v>
+        <v>368</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>588</v>
+        <v>423</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>589</v>
+        <v>369</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>590</v>
+        <v>371</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="K100" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="96">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>364</v>
+        <v>587</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>424</v>
+        <v>588</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>367</v>
+        <v>589</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>365</v>
+        <v>590</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="K101" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="48">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="96">
       <c r="A102" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="K102" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K103" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="96">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="K104" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="48">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="96">
       <c r="A105" s="1" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="K105" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="48">
       <c r="A106" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K106" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="48">
       <c r="A107" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>363</v>
+        <v>791</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K107" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="48">
       <c r="A108" s="1" t="s">
-        <v>606</v>
+        <v>479</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>608</v>
+        <v>360</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>611</v>
+        <v>363</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>359</v>
       </c>
       <c r="J108" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K108" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="48">
+      <c r="A109" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J109" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="K108" s="10">
+      <c r="K109" s="10">
         <v>3.4</v>
       </c>
-      <c r="L108" s="2" t="s">
+      <c r="L109" s="2" t="s">
         <v>709</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J107">
-    <sortCondition ref="I2:I107"/>
-    <sortCondition ref="D2:D107"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J108">
+    <sortCondition ref="I2:I108"/>
+    <sortCondition ref="D2:D108"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H49" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H39" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H47" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H37" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H48" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H40" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H41" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H42" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H38" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H43" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H50" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H40" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H48" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H38" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H49" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H41" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H42" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H43" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H39" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H44" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8588,73 +8661,75 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H66" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H64" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H65" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H67" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H60" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H59" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H63" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H62" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H68" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H61" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H89" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H36" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H35" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H28" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H30" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H29" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H25" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H31" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H33" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H26" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H27" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H32" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H24" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H107" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H101" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H99" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H102" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H103" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H104" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H105" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H90" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H81" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H93" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H79" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H82" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H92" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H100" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H52" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H87" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H108" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H69" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H97" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L97" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H53" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L53" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H54" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L54" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H50" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H21" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L21" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H22" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L23" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H23" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H20" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L20" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H98" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L98" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H19" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L19" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H58" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H18" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H34" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
-    <hyperlink ref="H17" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
-    <hyperlink ref="L17" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
-    <hyperlink ref="H16" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
-    <hyperlink ref="L16" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
-    <hyperlink ref="H15" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
+    <hyperlink ref="H67" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H65" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H66" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H68" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H61" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H60" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H64" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H63" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H69" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H62" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H90" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H37" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H36" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H29" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H31" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H30" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H26" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H32" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H34" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H27" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H28" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H33" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H25" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H108" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H102" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H100" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H103" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H104" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H105" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H106" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H91" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H82" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H94" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H80" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H83" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H93" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H101" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H53" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H88" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H109" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H70" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H98" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L98" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H54" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L54" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H55" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L55" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H51" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H22" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L22" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H23" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L24" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H24" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H21" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L21" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H99" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L99" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H20" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L20" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H59" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H19" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H35" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H18" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L18" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H17" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
+    <hyperlink ref="L17" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
+    <hyperlink ref="H16" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
+    <hyperlink ref="H15" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
+    <hyperlink ref="L15" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883B659C-7A66-734D-8527-E4E43889C93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6436D0-E412-384E-810D-84361E3A6AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="-6980" yWindow="-20580" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="964">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -416,9 +416,6 @@
   </si>
   <si>
     <t>http://villager.com.tw/</t>
-  </si>
-  <si>
-    <t>桃園區</t>
   </si>
   <si>
     <t>031</t>
@@ -4054,6 +4051,44 @@
   </si>
   <si>
     <t>https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>044</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南崁路46號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-222-8777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>青青格麗絲莊園</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-格麗絲莊園.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.grace-wed.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E9%9D%92%E9%9D%92%E6%A0%BC%E9%BA%97%E7%B5%B2%E8%8E%8A%E5%9C%92/@25.0446029,121.2929711,15.91z/data=!4m5!3m4!1s0x3442a00ea46130dd:0xf3352097e25f706d!8m2!3d25.044866!4d121.296633?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+  網路資訊:  &lt;a style="button" class="btn btn-info"  href="https://inline.app/booking/-MWNE4vnVbmKjEr5qqDz:inline-live-2/-MWNE550mazqX2RwaN53"&gt;預約&amp;amp;菜單&lt;/a&gt;   &amp;nbsp;
+   &lt;a style="button" class="btn btn-info"  href="https://carlming.net/23772"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4488,7 +4523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4513,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -4534,24 +4569,24 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="112">
       <c r="A2" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>104</v>
@@ -4563,7 +4598,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>106</v>
@@ -4572,24 +4607,24 @@
         <v>95</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K2" s="10">
         <v>3.8</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="112">
       <c r="A3" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>101</v>
@@ -4601,7 +4636,7 @@
         <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>48</v>
@@ -4610,13 +4645,13 @@
         <v>95</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K3" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="80">
@@ -4624,10 +4659,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>97</v>
@@ -4639,7 +4674,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>99</v>
@@ -4648,13 +4683,13 @@
         <v>95</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K4" s="10">
         <v>3.3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="80">
@@ -4665,7 +4700,7 @@
         <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>92</v>
@@ -4677,7 +4712,7 @@
         <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>94</v>
@@ -4686,13 +4721,13 @@
         <v>95</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="K5" s="10">
         <v>4.2</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48">
@@ -4700,37 +4735,37 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K6" s="10">
         <v>3.8</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="80">
@@ -4738,37 +4773,37 @@
         <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K7" s="10">
         <v>4.7</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="80">
@@ -4776,37 +4811,37 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="J8" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K8" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17">
@@ -4814,37 +4849,37 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K9" s="10">
         <v>4.5</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="97">
@@ -4852,37 +4887,37 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K10" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="128">
@@ -4890,37 +4925,37 @@
         <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K11" s="10">
         <v>3.8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="96">
@@ -4928,37 +4963,37 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K12" s="10">
         <v>4</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="64">
@@ -4966,37 +5001,37 @@
         <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K13" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="144">
@@ -5004,417 +5039,417 @@
         <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K14" s="10">
         <v>4.2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="112">
       <c r="A15" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>953</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>954</v>
       </c>
       <c r="K15" s="10">
         <v>4.3</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="64">
       <c r="A16" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>945</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>946</v>
       </c>
       <c r="K16" s="10">
         <v>4.5</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>931</v>
-      </c>
       <c r="E17" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>936</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="K17" s="10">
         <v>5</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="128">
       <c r="A18" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>925</v>
-      </c>
       <c r="H18" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>927</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>928</v>
       </c>
       <c r="K18" s="10">
         <v>4.3</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>909</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>910</v>
       </c>
       <c r="K19" s="10">
         <v>3.5</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="112">
       <c r="A20" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>891</v>
-      </c>
       <c r="I20" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K20" s="10">
         <v>4.3</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="80">
       <c r="A21" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>874</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K21" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>846</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K22" s="10">
         <v>4.3</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="80">
       <c r="A23" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>856</v>
-      </c>
       <c r="H23" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>858</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>859</v>
       </c>
       <c r="K23" s="10">
         <v>4.7</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="64">
       <c r="A24" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>864</v>
-      </c>
       <c r="H24" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K24" s="10">
         <v>4.3</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="80">
@@ -5422,37 +5457,37 @@
         <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>356</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K25" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="64">
@@ -5460,37 +5495,37 @@
         <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>329</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K26" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="96">
@@ -5498,37 +5533,37 @@
         <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>344</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K27" s="10">
         <v>4.7</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="80">
@@ -5536,37 +5571,37 @@
         <v>78</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="G28" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K28" s="10">
         <v>4.3</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="96">
@@ -5574,37 +5609,37 @@
         <v>82</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G29" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>315</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K29" s="10">
         <v>4</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="96">
@@ -5612,37 +5647,37 @@
         <v>86</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>325</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K30" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="80">
@@ -5650,37 +5685,37 @@
         <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="G31" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>320</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K31" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="64">
@@ -5688,37 +5723,37 @@
         <v>96</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="G32" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="I32" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K32" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="80">
@@ -5726,113 +5761,113 @@
         <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>352</v>
-      </c>
       <c r="I33" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K33" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="80">
       <c r="A34" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="G34" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>340</v>
-      </c>
       <c r="I34" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K34" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="96">
       <c r="A35" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="G35" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>917</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>918</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="K35" s="10">
         <v>5</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="64">
@@ -5840,37 +5875,37 @@
         <v>102</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="G36" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K36" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="96">
@@ -5878,37 +5913,37 @@
         <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K37" s="10">
         <v>4.2</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="64">
@@ -5916,37 +5951,37 @@
         <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K38" s="10">
         <v>4.8</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="80">
@@ -5954,37 +5989,37 @@
         <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="H39" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K39" s="10">
         <v>3.9</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="64">
@@ -5992,37 +6027,37 @@
         <v>118</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="H40" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K40" s="10">
         <v>4.2</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="96">
@@ -6030,162 +6065,162 @@
         <v>123</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K41" s="10">
         <v>3.9</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="96">
       <c r="A42" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K42" s="10">
         <v>4.2</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="96">
       <c r="A43" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K43" s="10">
         <v>3.8</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="112">
       <c r="A44" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K44" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="128">
       <c r="A45" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -6197,7 +6232,7 @@
         <v>110</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>94</v>
@@ -6206,24 +6241,24 @@
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K45" s="10">
         <v>4</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="112">
       <c r="A46" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>108</v>
@@ -6235,7 +6270,7 @@
         <v>110</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>114</v>
@@ -6244,24 +6279,24 @@
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K46" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="128">
       <c r="A47" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>108</v>
@@ -6273,7 +6308,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>117</v>
@@ -6282,176 +6317,176 @@
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K47" s="10">
         <v>3.7</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="112">
       <c r="A48" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K48" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="64">
       <c r="A49" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K49" s="10">
         <v>4.3</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="80">
       <c r="A50" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K50" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="144">
       <c r="A51" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="K51" s="10">
         <v>4.5999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="80">
       <c r="A52" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>120</v>
@@ -6460,7 +6495,7 @@
         <v>121</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>122</v>
@@ -6469,179 +6504,179 @@
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K52" s="10">
         <v>3.5</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="48">
       <c r="A53" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="G53" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>596</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>597</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K53" s="10">
         <v>4.3</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="80">
       <c r="A54" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>819</v>
-      </c>
       <c r="G54" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>815</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>816</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K54" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="128">
       <c r="A55" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>824</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>825</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K55" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="64">
       <c r="A56" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="I56" s="2" t="s">
-        <v>126</v>
+        <v>963</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K56" s="10">
         <v>3.9</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="80">
       <c r="A57" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>124</v>
@@ -6650,1996 +6685,2034 @@
         <v>42</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>125</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>126</v>
+        <v>963</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K57" s="10">
         <v>4.3</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="80">
       <c r="A58" s="1" t="s">
-        <v>187</v>
+        <v>955</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>487</v>
+        <v>958</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>410</v>
+        <v>956</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="K58" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="80">
+      <c r="A59" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G59" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="K58" s="10">
+      <c r="J59" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="K59" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="96">
-      <c r="A59" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="L59" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="96">
+      <c r="A60" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="K59" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="80">
-      <c r="A60" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>262</v>
+        <v>898</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>899</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>894</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>263</v>
+        <v>896</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>563</v>
+        <v>900</v>
       </c>
       <c r="K60" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="80">
+      <c r="A61" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="K61" s="10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="L61" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="48">
+      <c r="A62" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="K62" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L62" s="2" t="s">
         <v>664</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="48">
-      <c r="A61" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="K61" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="64">
-      <c r="A62" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="K62" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="64">
       <c r="A63" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="K63" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="64">
+      <c r="A64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F64" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="K63" s="10">
+      <c r="I64" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="K64" s="10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="48">
-      <c r="A64" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="K64" s="10">
-        <v>4.3</v>
-      </c>
       <c r="L64" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>442</v>
+        <v>263</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K65" s="10">
         <v>4.3</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>444</v>
+        <v>238</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K66" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="48">
       <c r="A67" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="K67" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="48">
+      <c r="A68" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="F68" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="I68" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="K68" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="96">
+      <c r="A69" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J67" s="7" t="s">
+      <c r="H69" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J69" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="K67" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L67" s="2" t="s">
+      <c r="K69" s="10">
+        <v>4</v>
+      </c>
+      <c r="L69" s="2" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="96">
-      <c r="A68" s="1" t="s">
+    <row r="70" spans="1:12" ht="48">
+      <c r="A70" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C68" s="1" t="s">
+      <c r="B70" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="D70" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="H68" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J68" s="7" t="s">
+      <c r="H70" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J70" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K68" s="10">
-        <v>4</v>
-      </c>
-      <c r="L68" s="2" t="s">
+      <c r="K70" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>672</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="48">
-      <c r="A69" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="K69" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="64">
-      <c r="A70" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>796</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>800</v>
-      </c>
-      <c r="K70" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="64">
       <c r="A71" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="K71" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="64">
+      <c r="A72" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="K72" s="10">
+        <v>4</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="80">
+      <c r="A73" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="K73" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="64">
+      <c r="A74" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="K74" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="112">
+      <c r="A75" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="B75" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="K75" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="80">
+      <c r="A76" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="D76" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="K76" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
+      <c r="A77" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K71" s="10">
-        <v>4</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="80">
-      <c r="A72" s="1" t="s">
+      <c r="G77" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="K77" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="80">
+      <c r="A78" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="K78" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="112">
+      <c r="A79" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="K79" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="48">
+      <c r="A80" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="K72" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="64">
-      <c r="A73" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="K73" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="112">
-      <c r="A74" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="B80" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="K74" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="80">
-      <c r="A75" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="K75" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="64">
-      <c r="A76" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D76" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J76" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="K76" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="80">
-      <c r="A77" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J77" s="7" t="s">
+      <c r="E80" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J80" s="7" t="s">
         <v>543</v>
-      </c>
-      <c r="K77" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="112">
-      <c r="A78" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J78" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="K78" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="48">
-      <c r="A79" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="K79" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="144">
-      <c r="A80" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>573</v>
       </c>
       <c r="K80" s="10">
         <v>4.2</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="64">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="144">
       <c r="A81" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>445</v>
+        <v>466</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="K81" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="64">
+      <c r="A82" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H81" s="2" t="s">
+      <c r="G82" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="K81" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="96">
-      <c r="A82" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>462</v>
-      </c>
       <c r="I82" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K82" s="10">
         <v>3.9</v>
       </c>
       <c r="L82" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="96">
+      <c r="A83" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="K83" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="64">
+      <c r="A84" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="K84" s="10">
+        <v>4</v>
+      </c>
+      <c r="L84" s="2" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="64">
-      <c r="A83" s="1" t="s">
+    <row r="85" spans="1:12" ht="48">
+      <c r="A85" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="G83" s="2" t="s">
+      <c r="B85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="K83" s="10">
-        <v>4</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="48">
-      <c r="A84" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="K84" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="80">
-      <c r="A85" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J85" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="K85" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="80">
+      <c r="A86" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="K86" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="64">
+      <c r="A87" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="K85" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L85" s="2" t="s">
+      <c r="K87" s="10">
+        <v>4</v>
+      </c>
+      <c r="L87" s="2" t="s">
         <v>687</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="64">
-      <c r="A86" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="K86" s="10">
-        <v>4</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="48">
-      <c r="A87" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="K87" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="48">
       <c r="A88" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="K88" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="48">
+      <c r="A89" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="H89" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="I89" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="K89" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="32">
+      <c r="A90" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="G88" s="2" t="s">
+      <c r="D90" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="H88" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="K88" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="32">
-      <c r="A89" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="H89" s="2" t="s">
+      <c r="H90" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="K89" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="64">
-      <c r="A90" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="K90" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="64">
+      <c r="A91" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="K91" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L90" s="2" t="s">
+      <c r="L91" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="48">
+      <c r="A92" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K92" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L92" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="48">
-      <c r="A91" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G91" s="2" t="s">
+    <row r="93" spans="1:12" ht="96">
+      <c r="A93" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H91" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="K91" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="96">
-      <c r="A92" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H92" s="2" t="s">
+      <c r="H93" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="K92" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="64">
-      <c r="A93" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>500</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K93" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="112">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="64">
       <c r="A94" s="1" t="s">
-        <v>388</v>
+        <v>495</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>362</v>
+        <v>498</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>466</v>
+        <v>499</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>581</v>
+        <v>548</v>
       </c>
       <c r="K94" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="96">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="112">
       <c r="A95" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>13</v>
+        <v>462</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>15</v>
+        <v>464</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>16</v>
+        <v>781</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>465</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="K95" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="64">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="96">
       <c r="A96" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>495</v>
+        <v>13</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>712</v>
+        <v>782</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>582</v>
+        <v>549</v>
       </c>
       <c r="K96" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="48">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="64">
       <c r="A97" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>87</v>
+        <v>494</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>807</v>
+        <v>711</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K97" s="10"/>
+        <v>581</v>
+      </c>
+      <c r="K97" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L97" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="96">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="48">
       <c r="A98" s="1" t="s">
-        <v>794</v>
+        <v>390</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>804</v>
+        <v>87</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E98" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>809</v>
+      <c r="H98" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="K98" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L98" s="6" t="s">
         <v>810</v>
+      </c>
+      <c r="K98" s="10"/>
+      <c r="L98" s="2" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="96">
       <c r="A99" s="1" t="s">
-        <v>869</v>
+        <v>793</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="K99" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="96">
+      <c r="A100" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D99" s="2" t="s">
+      <c r="E100" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="F100" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="G100" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>880</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="I100" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J100" s="7" t="s">
         <v>883</v>
       </c>
-      <c r="H99" s="6" t="s">
+      <c r="K100" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="L100" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="K99" s="10">
+    </row>
+    <row r="101" spans="1:12" ht="64">
+      <c r="A101" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="K101" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="48">
+      <c r="A102" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="K102" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="96">
+      <c r="A103" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="K103" s="10">
         <v>4.7</v>
       </c>
-      <c r="L99" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="64">
-      <c r="A100" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J100" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="K100" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="48">
-      <c r="A101" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="K101" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L101" s="2" t="s">
+      <c r="L103" s="2" t="s">
         <v>701</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="96">
-      <c r="A102" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="K102" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="48">
-      <c r="A103" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J103" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="K103" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="48">
       <c r="A104" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="K104" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="48">
+      <c r="A105" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="K105" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="96">
+      <c r="A106" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="B106" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="G104" s="2" t="s">
+      <c r="E106" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="H104" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J104" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="K104" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L104" s="2" t="s">
+      <c r="H106" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="K106" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L106" s="2" t="s">
         <v>704</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="96">
-      <c r="A105" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="K105" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="48">
-      <c r="A106" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J106" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="K106" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="48">
       <c r="A107" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K107" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="48">
       <c r="A108" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>363</v>
+        <v>790</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="K108" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="48">
       <c r="A109" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="K109" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="48">
+      <c r="A110" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C110" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D110" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="E110" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="F110" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="F109" s="7" t="s">
+      <c r="G110" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H109" s="6" t="s">
+      <c r="I110" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J110" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="I109" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J109" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="K109" s="10">
+      <c r="K110" s="10">
         <v>3.4</v>
       </c>
-      <c r="L109" s="2" t="s">
-        <v>709</v>
+      <c r="L110" s="2" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J108">
-    <sortCondition ref="I2:I108"/>
-    <sortCondition ref="D2:D108"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J109">
+    <sortCondition ref="I2:I109"/>
+    <sortCondition ref="D2:D109"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8661,17 +8734,17 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H67" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H65" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H66" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H68" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H61" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H60" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H64" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H63" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H69" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H62" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H90" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H68" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H66" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H67" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H69" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H62" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H61" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H65" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H64" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H70" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H63" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H91" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
     <hyperlink ref="H37" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
     <hyperlink ref="H36" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
     <hyperlink ref="H29" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
@@ -8684,26 +8757,26 @@
     <hyperlink ref="H28" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
     <hyperlink ref="H33" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
     <hyperlink ref="H25" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H108" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H102" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H100" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H103" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H104" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H105" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H106" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H91" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H82" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H94" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H80" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H83" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H93" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H101" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H109" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H103" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H101" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H104" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H105" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H106" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H107" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H92" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H83" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H95" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H81" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H84" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H94" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H102" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
     <hyperlink ref="H53" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H88" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H109" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H70" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H98" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L98" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H89" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H110" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H71" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H99" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L99" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
     <hyperlink ref="H54" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
     <hyperlink ref="L54" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
     <hyperlink ref="H55" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
@@ -8716,11 +8789,11 @@
     <hyperlink ref="H24" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
     <hyperlink ref="H21" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
     <hyperlink ref="L21" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H99" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L99" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H100" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L100" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
     <hyperlink ref="H20" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
     <hyperlink ref="L20" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H59" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H60" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
     <hyperlink ref="H19" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
     <hyperlink ref="H35" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
     <hyperlink ref="H18" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
@@ -8730,6 +8803,7 @@
     <hyperlink ref="H16" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
     <hyperlink ref="H15" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
     <hyperlink ref="L15" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
+    <hyperlink ref="H58" r:id="rId88" xr:uid="{E42A52B1-D676-8D44-AA60-7F68949475E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6436D0-E412-384E-810D-84361E3A6AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8419AFB8-FE88-174E-B7F1-01CB22DE7C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6980" yWindow="-20580" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="-7700" yWindow="-20600" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="973">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4090,6 +4090,44 @@
   <si>
     <t>桃園市</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>125</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天鳥拉麵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-TN.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.ca/maps/place/%E5%A4%A9%E9%B3%A5%E6%8B%89%E9%BA%B5/@25.0785667,121.3801178,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7377e7f5fa9:0x75824ec23a79bebd!8m2!3d25.0785619!4d121.3823119?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>新北市林口區信義路58-1號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0985-259-468</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30-14:00, 17:00-20:00, 週一公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E5%A4%A9%E9%B3%A5%E6%8B%89%E9%BA%B5-111658204487940/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/imhs/tian-niao-la-mian?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google_reserve_place_order_action"&gt;外送/菜單&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=SHuguEY_0FI"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;J14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4523,7 +4561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5072,1000 +5110,1000 @@
         <v>631</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="112">
+    <row r="15" spans="1:12" ht="80">
       <c r="A15" s="1" t="s">
-        <v>947</v>
+        <v>964</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>930</v>
+        <v>968</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>952</v>
+        <v>971</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>953</v>
+        <v>972</v>
       </c>
       <c r="K15" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="64">
+        <v>4.7</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="112">
       <c r="A16" s="1" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>445</v>
+        <v>948</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>800</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="K16" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>946</v>
+        <v>4.3</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="64">
       <c r="A17" s="1" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="K17" s="10">
-        <v>5</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="128">
+        <v>4.5</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="64">
       <c r="A18" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>442</v>
+        <v>929</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>403</v>
+        <v>933</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>926</v>
+        <v>934</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>935</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="64">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="128">
       <c r="A19" s="1" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>904</v>
+        <v>442</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>905</v>
+        <v>931</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>906</v>
+        <v>923</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>907</v>
+        <v>403</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>908</v>
+        <v>924</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>926</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="K19" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="112">
+        <v>4.3</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="64">
       <c r="A20" s="1" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>442</v>
+        <v>904</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>889</v>
+        <v>911</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="K20" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="112">
       <c r="A21" s="1" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>867</v>
+        <v>889</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>873</v>
+        <v>890</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
       <c r="K21" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="80">
       <c r="A22" s="1" t="s">
-        <v>793</v>
+        <v>868</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="K22" s="10">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>848</v>
+        <v>874</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="80">
       <c r="A23" s="1" t="s">
-        <v>850</v>
+        <v>793</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>445</v>
+        <v>842</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="K23" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>443</v>
+        <v>851</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>594</v>
+        <v>853</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>596</v>
+        <v>857</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="K24" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="80">
+        <v>4.7</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="64">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>859</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C25" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>709</v>
+        <v>861</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>357</v>
+        <v>594</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>862</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>355</v>
+        <v>863</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>596</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>512</v>
+        <v>865</v>
       </c>
       <c r="K25" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="64">
+        <v>4.3</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="80">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>446</v>
+        <v>354</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>326</v>
+        <v>709</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K26" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="96">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="64">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>635</v>
+        <v>325</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K27" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="80">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="96">
       <c r="A28" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>348</v>
+        <v>635</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K28" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="96">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="80">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K29" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="96">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K30" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="80">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="96">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K31" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="64">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="80">
       <c r="A32" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="K32" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="80">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="64">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>443</v>
+        <v>330</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="K33" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="80">
       <c r="A34" s="1" t="s">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>440</v>
+        <v>349</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>841</v>
+        <v>519</v>
       </c>
       <c r="K34" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L34" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="80">
+      <c r="A35" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="K35" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="96">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:12" ht="96">
+      <c r="A36" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>917</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="K35" s="10">
-        <v>5</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="64">
-      <c r="A36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>520</v>
+        <v>919</v>
       </c>
       <c r="K36" s="10">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="96">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="64">
       <c r="A37" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>406</v>
+        <v>294</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K37" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="64">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="96">
       <c r="A38" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>158</v>
+        <v>406</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>160</v>
+        <v>292</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>161</v>
+        <v>733</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K38" s="10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="80">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="64">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K39" s="10">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="64">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="80">
       <c r="A40" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="K40" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="96">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="64">
       <c r="A41" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>440</v>
@@ -6074,226 +6112,226 @@
         <v>152</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K41" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="96">
       <c r="A42" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>443</v>
+        <v>173</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K42" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="96">
       <c r="A43" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>441</v>
+        <v>177</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>179</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K43" s="10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="112">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="96">
       <c r="A44" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K44" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="128">
+        <v>3.8</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="112">
       <c r="A45" s="1" t="s">
-        <v>451</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>481</v>
+        <v>191</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>94</v>
+        <v>740</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K45" s="10">
-        <v>4</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="112">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="128">
       <c r="A46" s="1" t="s">
-        <v>144</v>
+        <v>451</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K46" s="10">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="128">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="112">
       <c r="A47" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>442</v>
@@ -6302,1492 +6340,1492 @@
         <v>108</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K47" s="10">
-        <v>3.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="112">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="128">
       <c r="A48" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>164</v>
+        <v>108</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>166</v>
+        <v>742</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K48" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="64">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="112">
       <c r="A49" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>443</v>
+        <v>163</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K49" s="10">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="80">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="64">
       <c r="A50" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>446</v>
+        <v>168</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>838</v>
+        <v>744</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K50" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="144">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="80">
       <c r="A51" s="1" t="s">
-        <v>831</v>
+        <v>167</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>832</v>
+        <v>145</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>833</v>
+        <v>446</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>836</v>
+        <v>146</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>837</v>
+        <v>147</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>460</v>
+        <v>148</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>834</v>
+        <v>149</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>840</v>
+        <v>533</v>
       </c>
       <c r="K51" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="80">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="144">
       <c r="A52" s="1" t="s">
-        <v>172</v>
+        <v>831</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>119</v>
+        <v>832</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>441</v>
+        <v>833</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>405</v>
+        <v>836</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>120</v>
+        <v>837</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>121</v>
+        <v>460</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>122</v>
+        <v>839</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>834</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>558</v>
+        <v>840</v>
       </c>
       <c r="K52" s="10">
-        <v>3.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="48">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="80">
       <c r="A53" s="1" t="s">
-        <v>591</v>
+        <v>172</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>592</v>
+        <v>119</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>593</v>
+        <v>405</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>594</v>
+        <v>120</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>595</v>
+        <v>121</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>596</v>
+        <v>745</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="K53" s="10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="80">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="48">
       <c r="A54" s="1" t="s">
-        <v>812</v>
+        <v>591</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>822</v>
+        <v>592</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>816</v>
+        <v>593</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>817</v>
+        <v>594</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>818</v>
+        <v>595</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>815</v>
+        <v>596</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>820</v>
+        <v>597</v>
       </c>
       <c r="K54" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="128">
+        <v>4.3</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>445</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J55" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="K55" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="128">
+      <c r="A56" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J56" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K56" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L55" s="6" t="s">
+      <c r="L56" s="6" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="64">
-      <c r="A56" s="1" t="s">
+    <row r="57" spans="1:12" ht="64">
+      <c r="A57" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="K56" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="80">
-      <c r="A57" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>963</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K57" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="80">
       <c r="A58" s="1" t="s">
-        <v>955</v>
+        <v>181</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>958</v>
+        <v>485</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>956</v>
+        <v>408</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>957</v>
+        <v>124</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>460</v>
+        <v>42</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>960</v>
+        <v>747</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>963</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>962</v>
+        <v>560</v>
       </c>
       <c r="K58" s="10">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>961</v>
+        <v>661</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="80">
       <c r="A59" s="1" t="s">
-        <v>186</v>
+        <v>955</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>486</v>
+        <v>958</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>409</v>
+        <v>956</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>957</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>137</v>
+        <v>460</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>138</v>
+        <v>959</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>960</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>139</v>
+        <v>963</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>561</v>
+        <v>962</v>
       </c>
       <c r="K59" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="96">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="80">
       <c r="A60" s="1" t="s">
-        <v>850</v>
+        <v>186</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>895</v>
+        <v>486</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="K60" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="96">
+      <c r="A61" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="H60" s="6" t="s">
+      <c r="H61" s="6" t="s">
         <v>896</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="K60" s="10">
-        <v>4.8</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="80">
-      <c r="A61" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>562</v>
+        <v>900</v>
       </c>
       <c r="K61" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="48">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="80">
       <c r="A62" s="1" t="s">
-        <v>452</v>
+        <v>190</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>443</v>
+        <v>258</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>749</v>
+        <v>893</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="K62" s="10">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="64">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="48">
       <c r="A63" s="1" t="s">
-        <v>200</v>
+        <v>452</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="K63" s="10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="64">
       <c r="A64" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K64" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="48">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="64">
       <c r="A65" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="K65" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="48">
       <c r="A66" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>441</v>
+        <v>263</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K66" s="10">
         <v>4.3</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="48">
       <c r="A67" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>443</v>
+        <v>238</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K67" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="48">
       <c r="A68" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K68" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="96">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="48">
       <c r="A69" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>442</v>
+        <v>233</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K69" s="10">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="48">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="96">
       <c r="A70" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>443</v>
+        <v>248</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K70" s="10">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="64">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="48">
       <c r="A71" s="1" t="s">
-        <v>793</v>
+        <v>228</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>794</v>
+        <v>273</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>800</v>
+        <v>443</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>801</v>
+        <v>276</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>802</v>
+        <v>277</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>797</v>
+        <v>274</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>796</v>
+        <v>757</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>795</v>
+        <v>275</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>799</v>
+        <v>541</v>
       </c>
       <c r="K71" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>798</v>
+        <v>672</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="64">
       <c r="A72" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="K72" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="64">
+      <c r="A73" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="K72" s="10">
-        <v>4</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="80">
-      <c r="A73" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K73" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="64">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="80">
       <c r="A74" s="1" t="s">
-        <v>307</v>
+        <v>453</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>442</v>
+        <v>27</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K74" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="112">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K75" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="80">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="112">
       <c r="A76" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>50</v>
+        <v>487</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="K76" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="64">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="80">
       <c r="A77" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K77" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="80">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="64">
       <c r="A78" s="1" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>445</v>
+        <v>55</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K78" s="10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="112">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="80">
       <c r="A79" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="K79" s="10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="48">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="112">
       <c r="A80" s="1" t="s">
-        <v>454</v>
+        <v>289</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>441</v>
+        <v>489</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="K80" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="144">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="48">
       <c r="A81" s="1" t="s">
-        <v>299</v>
+        <v>454</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>469</v>
+        <v>62</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>470</v>
+        <v>766</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="K81" s="10">
         <v>4.2</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="64">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="144">
       <c r="A82" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>444</v>
+        <v>466</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>33</v>
+        <v>468</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>34</v>
+        <v>767</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>470</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K82" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="96">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="64">
       <c r="A83" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>440</v>
+        <v>491</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>460</v>
+        <v>32</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>461</v>
+        <v>768</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K83" s="10">
         <v>3.9</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="64">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="96">
       <c r="A84" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K84" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="48">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>445</v>
+        <v>471</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>24</v>
+        <v>473</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>474</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>25</v>
+        <v>770</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>475</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="K85" s="10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="80">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="48">
       <c r="A86" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>440</v>
+        <v>22</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>25</v>
@@ -7796,937 +7834,975 @@
         <v>404</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K86" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="64">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="80">
       <c r="A87" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K87" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="48">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="64">
       <c r="A88" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="K88" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="48">
       <c r="A89" s="1" t="s">
-        <v>598</v>
+        <v>306</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>599</v>
+        <v>69</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>601</v>
+        <v>437</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>602</v>
+        <v>70</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>603</v>
+        <v>71</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>600</v>
+        <v>774</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J89" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="K89" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="48">
+      <c r="A90" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J90" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="K89" s="10">
+      <c r="K90" s="10">
         <v>4.2</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="32">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:12" ht="32">
+      <c r="A91" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H91" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="K90" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="64">
-      <c r="A91" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J91" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="K91" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="64">
+      <c r="A92" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="K91" s="10">
+      <c r="K92" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L91" s="2" t="s">
+      <c r="L92" s="2" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="48">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:12" ht="48">
+      <c r="A93" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C93" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="D93" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E93" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="F93" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G93" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="H92" s="6" t="s">
+      <c r="H93" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="I92" s="2" t="s">
+      <c r="I93" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="J92" s="7" t="s">
+      <c r="J93" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="K92" s="10">
+      <c r="K93" s="10">
         <v>4.5</v>
       </c>
-      <c r="L92" s="2" t="s">
+      <c r="L93" s="2" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="96">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:12" ht="96">
+      <c r="A94" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C94" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G94" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H94" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J93" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="K93" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="64">
-      <c r="A94" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>499</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K94" s="10">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="112">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="64">
       <c r="A95" s="1" t="s">
-        <v>387</v>
+        <v>495</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>361</v>
+        <v>498</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="K95" s="10">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="96">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="112">
       <c r="A96" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>13</v>
+        <v>462</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>15</v>
+        <v>464</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>16</v>
+        <v>781</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>465</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
       <c r="K96" s="10">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="64">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="96">
       <c r="A97" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>494</v>
+        <v>13</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>711</v>
+        <v>782</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="K97" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="48">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="64">
       <c r="A98" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>87</v>
+        <v>494</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>806</v>
+        <v>711</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="K98" s="10"/>
+        <v>581</v>
+      </c>
+      <c r="K98" s="10">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L98" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="96">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="48">
       <c r="A99" s="1" t="s">
-        <v>793</v>
+        <v>390</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>803</v>
+        <v>87</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>805</v>
+        <v>421</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>381</v>
+        <v>42</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K99" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
+      </c>
+      <c r="K99" s="10"/>
+      <c r="L99" s="2" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="96">
       <c r="A100" s="1" t="s">
-        <v>868</v>
+        <v>793</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>876</v>
+        <v>803</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="K100" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="96">
+      <c r="A101" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E101" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="H100" s="6" t="s">
+      <c r="H101" s="6" t="s">
         <v>880</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J100" s="7" t="s">
-        <v>883</v>
-      </c>
-      <c r="K100" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="64">
-      <c r="A101" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>582</v>
+        <v>883</v>
       </c>
       <c r="K101" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L101" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="48">
+        <v>4.7</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="64">
       <c r="A102" s="1" t="s">
-        <v>585</v>
+        <v>391</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>586</v>
+        <v>367</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>587</v>
+        <v>422</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>588</v>
+        <v>368</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>589</v>
+        <v>370</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="K102" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="96">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="48">
       <c r="A103" s="1" t="s">
-        <v>392</v>
+        <v>585</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>363</v>
+        <v>586</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>423</v>
+        <v>587</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>366</v>
+        <v>588</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>364</v>
+        <v>589</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="K103" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="48">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="96">
       <c r="A104" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>550</v>
+        <v>583</v>
       </c>
       <c r="K104" s="10">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="48">
       <c r="A105" s="1" t="s">
-        <v>455</v>
+        <v>393</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K105" s="10">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="96">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="48">
       <c r="A106" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>584</v>
+        <v>551</v>
       </c>
       <c r="K106" s="10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="48">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="96">
       <c r="A107" s="1" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="K107" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="48">
       <c r="A108" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K108" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="48">
       <c r="A109" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>362</v>
+        <v>790</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K109" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="48">
       <c r="A110" s="1" t="s">
-        <v>605</v>
+        <v>478</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>607</v>
+        <v>359</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>608</v>
+        <v>360</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>609</v>
+        <v>361</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>610</v>
+        <v>362</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J110" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="K110" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="48">
+      <c r="A111" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J111" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="K110" s="10">
+      <c r="K111" s="10">
         <v>3.4</v>
       </c>
-      <c r="L110" s="2" t="s">
+      <c r="L111" s="2" t="s">
         <v>708</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J109">
-    <sortCondition ref="I2:I109"/>
-    <sortCondition ref="D2:D109"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J110">
+    <sortCondition ref="I2:I110"/>
+    <sortCondition ref="D2:D110"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H50" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H40" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H48" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H38" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H49" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H41" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H42" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H43" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H39" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H44" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H51" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H41" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H49" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H39" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H50" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H42" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H43" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H44" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H40" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H45" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8734,76 +8810,77 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H68" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H66" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H67" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H69" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H62" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H61" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H65" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H64" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H70" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H63" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H91" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H37" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H36" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H29" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H31" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H30" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H26" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H32" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H34" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H27" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H28" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H33" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H25" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H109" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H103" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H101" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H104" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H105" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H106" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H107" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H92" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H83" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H95" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H81" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H84" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H94" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H102" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H53" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H89" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H110" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H71" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H99" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L99" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H54" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L54" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H55" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L55" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H51" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H22" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L22" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H23" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L24" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H24" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H21" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L21" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H100" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L100" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H20" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L20" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H60" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H19" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H35" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
-    <hyperlink ref="H18" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
-    <hyperlink ref="L18" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
-    <hyperlink ref="H17" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
-    <hyperlink ref="L17" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
-    <hyperlink ref="H16" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
-    <hyperlink ref="H15" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
-    <hyperlink ref="L15" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
-    <hyperlink ref="H58" r:id="rId88" xr:uid="{E42A52B1-D676-8D44-AA60-7F68949475E8}"/>
+    <hyperlink ref="H69" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H67" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H68" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H70" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H63" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H62" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H66" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H65" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H71" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H64" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H92" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H38" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H37" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H30" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H32" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H31" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H27" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H33" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H35" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H28" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H29" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H34" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H26" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H110" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H104" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H102" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H105" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H106" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H107" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H108" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H93" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H84" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H96" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H82" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H85" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H95" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H103" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H54" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H90" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H111" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H72" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H100" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L100" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H55" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L55" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H56" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L56" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H52" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H23" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L23" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H24" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L25" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H25" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H22" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L22" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H101" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L101" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H21" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L21" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H61" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H20" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H36" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H19" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L19" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H18" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
+    <hyperlink ref="L18" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
+    <hyperlink ref="H17" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
+    <hyperlink ref="H16" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
+    <hyperlink ref="L16" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
+    <hyperlink ref="H59" r:id="rId88" xr:uid="{E42A52B1-D676-8D44-AA60-7F68949475E8}"/>
+    <hyperlink ref="H15" r:id="rId89" xr:uid="{CE730D97-1D2C-7C46-ACA3-E12040378435}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8419AFB8-FE88-174E-B7F1-01CB22DE7C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91103662-83A1-A246-9C69-90798A1413C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7700" yWindow="-20600" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
@@ -4126,7 +4126,7 @@
     <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/imhs/tian-niao-la-mian?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google_reserve_place_order_action"&gt;外送/菜單&lt;/a&gt; &amp;nbsp;
   &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=SHuguEY_0FI"&gt;推薦&lt;/a&gt;
-&lt;/p&gt;J14</t>
+&lt;/p&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4616,7 +4616,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="112">
+    <row r="2" spans="1:12" ht="144">
       <c r="A2" s="1" t="s">
         <v>448</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="80">
+    <row r="4" spans="1:12" ht="96">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="80">
+    <row r="7" spans="1:12" ht="96">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="128">
+    <row r="11" spans="1:12" ht="144">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91103662-83A1-A246-9C69-90798A1413C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592B447D-4FAC-EE46-BC6B-893651BD30D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7700" yWindow="-20600" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
+    <workbookView xWindow="-12240" yWindow="-18580" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="991">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4126,6 +4126,83 @@
     <t>&lt;p&gt;
    網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/imhs/tian-niao-la-mian?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google_reserve_place_order_action"&gt;外送/菜單&lt;/a&gt; &amp;nbsp;
   &lt;a style="button" class="btn btn-info"  href="https://www.youtube.com/watch?v=SHuguEY_0FI"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>126</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>藏王極上鍋物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>127</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/search?q=%E8%97%8F%E7%8E%8B%E6%A5%B5%E4%B8%8A%E9%8D%8B%E7%89%A9&amp;sxsrf=APq-WBuT_84kELfWNvV1MJRVsRiQu6xYFg:1649114002448&amp;source=hp&amp;ei=b3tLYvqvGYXA0PEPwO20-AI&amp;iflsig=AHkkrS4AAAAAYkuJf-gODtRkoWLcUzJhRpWf3FqFlel9&amp;oq=%E8%97%8F%E7%8E%8B&amp;gs_lcp=Cgdnd3Mtd2l6EAEYADIFCAAQgAQyBQgAEIAEMgsILhCABBDHARCvATIFCAAQgAQyBQgAEIAEMgsILhCABBDHARCvATIFCAAQgAQyBQgAEIAEMgUIABCABDILCC4QgAQQxwEQrwE6BwgjEOoCECc6DQguEMcBEK8BEOoCECc6BQguEIAEUMEiWP3xAWDDhwJoBHAAeACAAXCIAaAGkgEDNy4ymAEAoAECoAEBsAEK&amp;sclient=gws-wiz&amp;tbs=lf:1,lf_ui:9&amp;tbm=lcl&amp;rflfq=1&amp;num=10&amp;rldimm=7116132348224642836&amp;lqi=ChLol4_njovmpbXkuIrpjYvnialIyIjNwa6wgIAIWicQABABEAIQAxgAGAEYAhgDIhXol48g546LIOalteS4iiDpjYvniamSARJob3RfcG90X3Jlc3RhdXJhbnQ&amp;phdesc=PcRATLUf8pU&amp;ved=2ahUKEwiFh72yxPv2AhWdDjQIHf7GCsYQvS56BAgHEAE&amp;rlst=f#rlfi=hd:;si:7116132348224642836,l,ChLol4_njovmpbXkuIrpjYvnialIyIjNwa6wgIAIWicQABABEAIQAxgAGAEYAhgDIhXol48g546LIOalteS4iiDpjYvniamSARJob3RfcG90X3Jlc3RhdXJhbnQ,y,PcRATLUf8pU;mv:[[25.120601,121.5498437],[24.957292199999998,121.2068584]];tbs:lrf:!1m4!1u3!2m2!3m1!1e1!1m4!1u2!2m2!2m1!1e1!2m1!1e2!2m1!1e3!3sIAE,lf:1,lf_ui:9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ZaoShabu1/</t>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-藏王極上鍋物.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區文化三路一段402巷2號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-2608-7478</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30–15:30, 17:30–22:30, 週六 11:00-23:00, 週日11:00-22:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫家將臺式牛排-文青店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/search?q=%E5%AD%AB%E5%AE%B6%E5%B0%87%E7%89%9B%E6%8E%92&amp;tbm=lcl&amp;sxsrf=APq-WBsBo11Z-QrwNH1867AfgJFzwaBVMw%3A1649114745598&amp;ei=eX5LYqqcJOP99AP44rnoBg&amp;oq=%E5%AD%AB%E5%AE%B6%E5%B0%87%E7%89%9B%E6%8E%92&amp;gs_l=psy-ab.3...0.0.0.27840.0.0.0.0.0.0.0.0..0.0....0...1c..64.psy-ab..0.0.0....0.J-o0R9UDd1A#rlfi=hd:;si:5841049586421414644,l,Cg_lravlrrblsIfniZvmjpJaGCIS5a2rIOWutiDlsIcg54mb5o6SKgIIApIBFGNob3Bob3VzZV9yZXN0YXVyYW50,y,SdklJsA0LOs;mv:[[25.044223101187008,121.39279001761095],[25.035299701719218,121.3688647131981],null,[25.03976148260657,121.38082736540453],16]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文青路137號1樓四室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-6857</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00-21:30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-311-Restaurant/AiCity-910-孫家將.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/aj7w/sun-jia-jiang-tai-shi-niu-pai-tao-yuan-gui-shan-wen-qing-dian"&gt;外送/菜單&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://zaq0930.pixnet.net/blog/post/362621357-%E3%80%90a7%E9%A3%9F%E8%A8%98%E3%80%91%E5%AD%AB%E5%AE%B6%E5%B0%87%E7%89%9B%E6%8E%92"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E5%AD%AB%E5%AE%B6%E5%B0%87%E8%87%BA%E5%BC%8F%E7%89%9B%E6%8E%92-100634701401295/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   網路資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/ZaoShabu1/menu"&gt;菜單&lt;/a&gt; &amp;nbsp;
+  &lt;a style="button" class="btn btn-info"  href="https://vivawei.tw/zaoshabu/"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4561,7 +4638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067DB8E-BE6D-BD40-8262-98D4CCD248C4}">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5110,3699 +5187,3775 @@
         <v>631</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="80">
+    <row r="15" spans="1:12" ht="112">
       <c r="A15" s="1" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>440</v>
+        <v>982</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>971</v>
+        <v>989</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
       <c r="K15" s="10">
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="112">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="64">
       <c r="A16" s="1" t="s">
-        <v>947</v>
+        <v>973</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>800</v>
+        <v>974</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>930</v>
+        <v>979</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>950</v>
+        <v>981</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>952</v>
+        <v>977</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>953</v>
+        <v>990</v>
       </c>
       <c r="K16" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="64">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="80">
       <c r="A17" s="1" t="s">
-        <v>938</v>
+        <v>964</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>445</v>
+        <v>965</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>940</v>
+        <v>968</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>941</v>
+        <v>969</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>942</v>
+        <v>970</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="K17" s="10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="64">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="112">
       <c r="A18" s="1" t="s">
-        <v>928</v>
+        <v>947</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>445</v>
+        <v>948</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>800</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>930</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>932</v>
+        <v>949</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>933</v>
+        <v>950</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>934</v>
+        <v>951</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
       <c r="K18" s="10">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="128">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
-        <v>921</v>
+        <v>938</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>442</v>
+        <v>939</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>403</v>
+        <v>942</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>926</v>
+        <v>943</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>944</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="K19" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>925</v>
+        <v>4.5</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="64">
       <c r="A20" s="1" t="s">
-        <v>902</v>
+        <v>928</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>904</v>
+        <v>929</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>905</v>
+        <v>930</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>907</v>
+        <v>933</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
       <c r="K20" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="112">
+        <v>5</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="128">
       <c r="A21" s="1" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>886</v>
+        <v>931</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>887</v>
+        <v>923</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>888</v>
+        <v>403</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>890</v>
+        <v>924</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>926</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>892</v>
+        <v>927</v>
       </c>
       <c r="K21" s="10">
         <v>4.3</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="80">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="64">
       <c r="A22" s="1" t="s">
-        <v>868</v>
+        <v>902</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>869</v>
+        <v>903</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>443</v>
+        <v>904</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>870</v>
+        <v>905</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>871</v>
+        <v>906</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>872</v>
+        <v>907</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>867</v>
+        <v>911</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>873</v>
+        <v>908</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>875</v>
+        <v>909</v>
       </c>
       <c r="K22" s="10">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="80">
+        <v>3.5</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="112">
       <c r="A23" s="1" t="s">
-        <v>793</v>
+        <v>884</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>842</v>
+        <v>885</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>843</v>
+        <v>886</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>844</v>
+        <v>887</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>845</v>
+        <v>888</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>847</v>
+        <v>889</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>866</v>
+        <v>892</v>
       </c>
       <c r="K23" s="10">
         <v>4.3</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>848</v>
+        <v>891</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="80">
       <c r="A24" s="1" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>445</v>
+        <v>869</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>852</v>
+        <v>870</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
       <c r="K24" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="64">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="80">
       <c r="A25" s="1" t="s">
-        <v>859</v>
+        <v>793</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>594</v>
+        <v>844</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>862</v>
+        <v>845</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>596</v>
+        <v>849</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="K25" s="10">
         <v>4.3</v>
       </c>
-      <c r="L25" s="13" t="s">
-        <v>864</v>
+      <c r="L25" s="6" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="80">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>850</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>354</v>
+        <v>851</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>709</v>
+        <v>852</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>357</v>
+        <v>853</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>854</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>355</v>
+        <v>855</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>857</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>512</v>
+        <v>858</v>
       </c>
       <c r="K26" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>632</v>
+        <v>4.7</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="64">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>859</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>325</v>
+        <v>860</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>326</v>
+        <v>861</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>327</v>
+        <v>594</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>862</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>328</v>
+        <v>863</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>596</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>513</v>
+        <v>865</v>
       </c>
       <c r="K27" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="96">
+        <v>4.3</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="80">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>442</v>
+        <v>354</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>340</v>
+        <v>709</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K28" s="10">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="80">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="64">
       <c r="A29" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K29" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="96">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>310</v>
+        <v>635</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K30" s="10">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="96">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="80">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K31" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="80">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="96">
       <c r="A32" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K32" s="10">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="64">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="96">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>555</v>
+        <v>517</v>
       </c>
       <c r="K33" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="80">
       <c r="A34" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>443</v>
+        <v>315</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K34" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="80">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="64">
       <c r="A35" s="1" t="s">
-        <v>450</v>
+        <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J35" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K35" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="80">
+      <c r="A36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="K36" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="80">
+      <c r="A37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>841</v>
-      </c>
-      <c r="K35" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="96">
-      <c r="A36" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>916</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="K36" s="10">
-        <v>5</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="64">
-      <c r="A37" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>520</v>
       </c>
       <c r="K37" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="96">
       <c r="A38" s="1" t="s">
-        <v>107</v>
+        <v>912</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>290</v>
+        <v>913</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>406</v>
+        <v>914</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>292</v>
+        <v>915</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>293</v>
+        <v>916</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>733</v>
+        <v>920</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>291</v>
+        <v>917</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>521</v>
+        <v>919</v>
       </c>
       <c r="K38" s="10">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>644</v>
+        <v>918</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="64">
       <c r="A39" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>157</v>
+        <v>500</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>158</v>
+        <v>294</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>160</v>
+        <v>295</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>161</v>
+        <v>732</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K39" s="10">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="80">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="96">
       <c r="A40" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>183</v>
+        <v>406</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>292</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>185</v>
+        <v>733</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K40" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="64">
       <c r="A41" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="K41" s="10">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="96">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="80">
       <c r="A42" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K42" s="10">
         <v>3.9</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="96">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="64">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>443</v>
+        <v>151</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K43" s="10">
         <v>4.2</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="96">
       <c r="A44" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K44" s="10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="112">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="96">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>440</v>
+        <v>177</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>152</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K45" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="128">
+        <v>4.2</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="96">
       <c r="A46" s="1" t="s">
-        <v>451</v>
+        <v>130</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>481</v>
+        <v>187</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>94</v>
+        <v>739</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="K46" s="10">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="112">
       <c r="A47" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>482</v>
+        <v>191</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>114</v>
+        <v>740</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K47" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>653</v>
+      <c r="L47" s="11" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="128">
       <c r="A48" s="1" t="s">
-        <v>150</v>
+        <v>451</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>108</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K48" s="10">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="112">
       <c r="A49" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>163</v>
+        <v>482</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>164</v>
+        <v>108</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>166</v>
+        <v>741</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K49" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="64">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="128">
       <c r="A50" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>443</v>
+        <v>483</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>171</v>
+        <v>742</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K50" s="10">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="80">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="112">
       <c r="A51" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>838</v>
+        <v>743</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K51" s="10">
         <v>4.0999999999999996</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="144">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="64">
       <c r="A52" s="1" t="s">
-        <v>831</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>833</v>
+        <v>168</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>836</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>837</v>
+        <v>169</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>839</v>
+        <v>744</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>834</v>
+        <v>171</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>840</v>
+        <v>534</v>
       </c>
       <c r="K52" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>835</v>
+        <v>656</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="80">
       <c r="A53" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>405</v>
+        <v>146</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>122</v>
+        <v>838</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="K53" s="10">
-        <v>3.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="48">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="144">
       <c r="A54" s="1" t="s">
-        <v>591</v>
+        <v>831</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>592</v>
+        <v>832</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>443</v>
+        <v>833</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>593</v>
+        <v>836</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>594</v>
+        <v>837</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>595</v>
+        <v>460</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>596</v>
+        <v>839</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>834</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>597</v>
+        <v>840</v>
       </c>
       <c r="K54" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>659</v>
+        <v>835</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="80">
       <c r="A55" s="1" t="s">
-        <v>812</v>
+        <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>822</v>
+        <v>119</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>816</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>817</v>
+        <v>120</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>818</v>
+        <v>121</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>815</v>
+        <v>745</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>820</v>
+        <v>558</v>
       </c>
       <c r="K55" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="128">
+        <v>3.5</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="48">
       <c r="A56" s="1" t="s">
-        <v>821</v>
+        <v>591</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>823</v>
+        <v>592</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>826</v>
+        <v>593</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>827</v>
+        <v>594</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>828</v>
+        <v>595</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>830</v>
+        <v>813</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>824</v>
+        <v>596</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J56" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="K56" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="80">
+      <c r="A57" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="K57" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="128">
+      <c r="A58" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J58" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K58" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L56" s="6" t="s">
+      <c r="L58" s="6" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="64">
-      <c r="A57" s="1" t="s">
+    <row r="59" spans="1:12" ht="64">
+      <c r="A59" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="K57" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="80">
-      <c r="A58" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="K58" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="80">
-      <c r="A59" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>958</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>956</v>
+        <v>407</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>957</v>
+        <v>127</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>460</v>
+        <v>128</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>960</v>
+        <v>746</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>963</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>962</v>
+        <v>559</v>
       </c>
       <c r="K59" s="10">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>961</v>
+        <v>660</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="80">
       <c r="A60" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>139</v>
+        <v>963</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K60" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="96">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="80">
       <c r="A61" s="1" t="s">
-        <v>850</v>
+        <v>955</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>895</v>
+        <v>958</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>897</v>
+        <v>956</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>898</v>
+        <v>957</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>899</v>
+        <v>460</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>894</v>
+        <v>959</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>896</v>
+        <v>960</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>226</v>
+        <v>963</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>900</v>
+        <v>962</v>
       </c>
       <c r="K61" s="10">
         <v>4.8</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>901</v>
+        <v>961</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="80">
       <c r="A62" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>258</v>
+        <v>486</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>259</v>
+        <v>409</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>261</v>
+        <v>136</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>262</v>
+        <v>748</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K62" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="48">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="96">
       <c r="A63" s="1" t="s">
-        <v>452</v>
+        <v>850</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>443</v>
+        <v>895</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>254</v>
+        <v>897</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>257</v>
+        <v>898</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>899</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>749</v>
+        <v>894</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>256</v>
+        <v>896</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>535</v>
+        <v>900</v>
       </c>
       <c r="K63" s="10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="64">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="80">
       <c r="A64" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>445</v>
+        <v>258</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>750</v>
+        <v>893</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K64" s="10">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="64">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="48">
       <c r="A65" s="1" t="s">
-        <v>205</v>
+        <v>452</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="K65" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="48">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="64">
       <c r="A66" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="K66" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="48">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="64">
       <c r="A67" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>441</v>
+        <v>268</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="K67" s="10">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="48">
       <c r="A68" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K68" s="10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="48">
       <c r="A69" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>443</v>
+        <v>238</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K69" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="96">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="48">
       <c r="A70" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>442</v>
+        <v>243</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>443</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K70" s="10">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="48">
       <c r="A71" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K71" s="10">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="64">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="96">
       <c r="A72" s="1" t="s">
-        <v>793</v>
+        <v>227</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>800</v>
+        <v>248</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>801</v>
+        <v>249</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>802</v>
+        <v>250</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>797</v>
+        <v>252</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>796</v>
+        <v>756</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>795</v>
+        <v>251</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J72" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="K72" s="10">
+        <v>4</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="48">
+      <c r="A73" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="K73" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="64">
+      <c r="A74" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J74" s="7" t="s">
         <v>799</v>
       </c>
-      <c r="K72" s="10">
+      <c r="K74" s="10">
         <v>4.2</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="L74" s="2" t="s">
         <v>798</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="64">
-      <c r="A73" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="K73" s="10">
-        <v>4</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="80">
-      <c r="A74" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="K74" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="64">
       <c r="A75" s="1" t="s">
-        <v>307</v>
+        <v>229</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>442</v>
+        <v>37</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="K75" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="112">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="80">
       <c r="A76" s="1" t="s">
-        <v>230</v>
+        <v>453</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>440</v>
+        <v>27</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K76" s="10">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="80">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="64">
       <c r="A77" s="1" t="s">
-        <v>231</v>
+        <v>307</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>50</v>
+        <v>492</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="K77" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="64">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="112">
       <c r="A78" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>55</v>
+        <v>487</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K78" s="10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="80">
       <c r="A79" s="1" t="s">
-        <v>283</v>
+        <v>231</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>445</v>
+        <v>50</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="K79" s="10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="112">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="64">
       <c r="A80" s="1" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>445</v>
+        <v>55</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K80" s="10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="48">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="80">
       <c r="A81" s="1" t="s">
-        <v>454</v>
+        <v>283</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>441</v>
+        <v>488</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K81" s="10">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="144">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="112">
       <c r="A82" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>442</v>
+        <v>489</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>469</v>
+        <v>18</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>470</v>
+        <v>765</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K82" s="10">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="64">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="48">
       <c r="A83" s="1" t="s">
-        <v>300</v>
+        <v>454</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>444</v>
+        <v>490</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="K83" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="96">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="144">
       <c r="A84" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="K84" s="10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="64">
       <c r="A85" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>440</v>
+        <v>491</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>474</v>
+        <v>32</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>475</v>
+        <v>768</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K85" s="10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="48">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="96">
       <c r="A86" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>445</v>
+        <v>457</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>24</v>
+        <v>459</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>460</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>25</v>
+        <v>769</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>461</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="K86" s="10">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="80">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="64">
       <c r="A87" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>66</v>
+        <v>471</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>410</v>
+        <v>472</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>42</v>
+        <v>473</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>474</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>25</v>
+        <v>770</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>475</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K87" s="10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="64">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="48">
       <c r="A88" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>442</v>
+        <v>22</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>577</v>
+        <v>544</v>
       </c>
       <c r="K88" s="10">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="48">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="80">
       <c r="A89" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="K89" s="10">
         <v>3.8</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="48">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="64">
       <c r="A90" s="1" t="s">
-        <v>598</v>
+        <v>305</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>599</v>
+        <v>74</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>601</v>
+        <v>436</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>602</v>
+        <v>75</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>603</v>
+        <v>76</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>600</v>
+        <v>773</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="K90" s="10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="32">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="48">
       <c r="A91" s="1" t="s">
-        <v>394</v>
+        <v>306</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>443</v>
+        <v>69</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>12</v>
+        <v>404</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>578</v>
+        <v>545</v>
       </c>
       <c r="K91" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.8</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="64">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="48">
       <c r="A92" s="1" t="s">
-        <v>308</v>
+        <v>598</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>284</v>
+        <v>599</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>285</v>
+        <v>601</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>287</v>
+        <v>602</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>288</v>
+        <v>600</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>12</v>
+        <v>404</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="K92" s="10">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="48">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="32">
       <c r="A93" s="1" t="s">
-        <v>309</v>
+        <v>394</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="D93" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>403</v>
+      <c r="D93" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>401</v>
+        <v>776</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>400</v>
+        <v>12</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="K93" s="10">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="96">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="64">
       <c r="A94" s="1" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>445</v>
+        <v>284</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>418</v>
+        <v>285</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>10</v>
+        <v>286</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>11</v>
+        <v>777</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="K94" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="64">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="48">
       <c r="A95" s="1" t="s">
-        <v>495</v>
+        <v>309</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>460</v>
+        <v>399</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>499</v>
+        <v>401</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K95" s="10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="112">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="96">
       <c r="A96" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>440</v>
+        <v>8</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>463</v>
+        <v>418</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>361</v>
+        <v>9</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>465</v>
+        <v>779</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="K96" s="10">
-        <v>3.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="96">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="64">
       <c r="A97" s="1" t="s">
-        <v>388</v>
+        <v>495</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>13</v>
+        <v>496</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>419</v>
+        <v>497</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>14</v>
+        <v>498</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>16</v>
+        <v>780</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>499</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K97" s="10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="64">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="112">
       <c r="A98" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>47</v>
+        <v>464</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>48</v>
+        <v>781</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>465</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K98" s="10">
-        <v>4.0999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="48">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="96">
       <c r="A99" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>806</v>
+        <v>782</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="K99" s="10"/>
+        <v>549</v>
+      </c>
+      <c r="K99" s="10">
+        <v>4.3</v>
+      </c>
       <c r="L99" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="96">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="64">
       <c r="A100" s="1" t="s">
-        <v>793</v>
+        <v>389</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>803</v>
+        <v>494</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>805</v>
+        <v>420</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>808</v>
+        <v>711</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>811</v>
+        <v>581</v>
       </c>
       <c r="K100" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L100" s="6" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="96">
+      <c r="L100" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="48">
       <c r="A101" s="1" t="s">
-        <v>868</v>
+        <v>390</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>876</v>
+        <v>87</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="K101" s="10"/>
+      <c r="L101" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="96">
+      <c r="A102" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>880</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>883</v>
-      </c>
-      <c r="K101" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="64">
-      <c r="A102" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>443</v>
-      </c>
       <c r="D102" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>369</v>
+        <v>804</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>783</v>
+        <v>807</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>370</v>
+        <v>808</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>358</v>
+        <v>12</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>582</v>
+        <v>811</v>
       </c>
       <c r="K102" s="10">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L102" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="48">
+      <c r="L102" s="6" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="96">
       <c r="A103" s="1" t="s">
-        <v>585</v>
+        <v>868</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>443</v>
+        <v>876</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>588</v>
+        <v>877</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>784</v>
+        <v>882</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>589</v>
+        <v>880</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>590</v>
+        <v>883</v>
       </c>
       <c r="K103" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="96">
+        <v>4.7</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="64">
       <c r="A104" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K104" s="10">
-        <v>4.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="48">
       <c r="A105" s="1" t="s">
-        <v>393</v>
+        <v>585</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>371</v>
+        <v>586</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>424</v>
+        <v>587</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>374</v>
+        <v>588</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>372</v>
+        <v>589</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="K105" s="10">
-        <v>3.1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="48">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="96">
       <c r="A106" s="1" t="s">
-        <v>455</v>
+        <v>392</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="K106" s="10">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="96">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="48">
       <c r="A107" s="1" t="s">
-        <v>456</v>
+        <v>393</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>584</v>
+        <v>550</v>
       </c>
       <c r="K107" s="10">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="48">
       <c r="A108" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K108" s="10">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="48">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="96">
       <c r="A109" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>443</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>383</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="K109" s="10">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="48">
       <c r="A110" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K110" s="10">
-        <v>4.4000000000000004</v>
+        <v>3.9</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="48">
       <c r="A111" s="1" t="s">
-        <v>605</v>
+        <v>477</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>607</v>
+        <v>375</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>608</v>
+        <v>377</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>609</v>
+        <v>376</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>610</v>
+        <v>790</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>358</v>
       </c>
       <c r="J111" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="K111" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="48">
+      <c r="A112" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="K112" s="10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="48">
+      <c r="A113" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J113" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="K111" s="10">
+      <c r="K113" s="10">
         <v>3.4</v>
       </c>
-      <c r="L111" s="2" t="s">
+      <c r="L113" s="2" t="s">
         <v>708</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J110">
-    <sortCondition ref="I2:I110"/>
-    <sortCondition ref="D2:D110"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J112">
+    <sortCondition ref="I2:I112"/>
+    <sortCondition ref="D2:D112"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{888884B7-DD2F-EC40-8B89-A0B40F7B4538}"/>
-    <hyperlink ref="H51" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
-    <hyperlink ref="H41" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
-    <hyperlink ref="H49" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
-    <hyperlink ref="H39" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
-    <hyperlink ref="H50" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
-    <hyperlink ref="H42" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
-    <hyperlink ref="H43" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
-    <hyperlink ref="H44" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
-    <hyperlink ref="H40" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
-    <hyperlink ref="H45" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
+    <hyperlink ref="H53" r:id="rId2" xr:uid="{F1B55455-7154-F540-874B-6E233BA227BC}"/>
+    <hyperlink ref="H43" r:id="rId3" xr:uid="{A92963D2-0211-6845-AA2A-FCCEEFF7851A}"/>
+    <hyperlink ref="H51" r:id="rId4" xr:uid="{9B3FF564-1F19-A34B-A899-A20D7581056D}"/>
+    <hyperlink ref="H41" r:id="rId5" xr:uid="{BB259414-9186-2A48-B039-25F2DB09EED0}"/>
+    <hyperlink ref="H52" r:id="rId6" xr:uid="{2566BBDB-2CAD-5F4E-A8E1-F7A346EB58FF}"/>
+    <hyperlink ref="H44" r:id="rId7" xr:uid="{868C2E93-4BE1-FF4E-8704-CAD0B0B5FB5E}"/>
+    <hyperlink ref="H45" r:id="rId8" xr:uid="{A6FD8CDE-ACEB-FD40-9BF1-3F8DB3F4651E}"/>
+    <hyperlink ref="H46" r:id="rId9" xr:uid="{7C3BD908-1146-7940-B467-385355D0B54D}"/>
+    <hyperlink ref="H42" r:id="rId10" xr:uid="{913A8024-8610-134D-94D0-8676D357AD56}"/>
+    <hyperlink ref="H47" r:id="rId11" xr:uid="{70A1F7DE-B062-E943-8045-EE9A16C8C7AE}"/>
     <hyperlink ref="H8" r:id="rId12" xr:uid="{B61C32CF-65DE-5D45-922F-EF85040EC17D}"/>
     <hyperlink ref="H11" r:id="rId13" xr:uid="{FDA925B5-456C-174D-A520-BF6A25282571}"/>
     <hyperlink ref="H10" r:id="rId14" xr:uid="{D8FAF5B1-45FC-4D4B-9A8A-2BFE23534C33}"/>
@@ -8810,77 +8963,78 @@
     <hyperlink ref="H12" r:id="rId16" xr:uid="{90038BA7-E075-0440-A96D-EA6ACC7FD191}"/>
     <hyperlink ref="H13" r:id="rId17" xr:uid="{5316EB1A-A470-B64F-A2F7-637436A96606}"/>
     <hyperlink ref="H14" r:id="rId18" xr:uid="{6FA5AFA1-22DA-D848-929C-A04ED36DAE9C}"/>
-    <hyperlink ref="H69" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
-    <hyperlink ref="H67" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
-    <hyperlink ref="H68" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
-    <hyperlink ref="H70" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
-    <hyperlink ref="H63" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
-    <hyperlink ref="H62" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
-    <hyperlink ref="H66" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
-    <hyperlink ref="H65" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
-    <hyperlink ref="H71" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
-    <hyperlink ref="H64" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
-    <hyperlink ref="H92" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
-    <hyperlink ref="H38" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
-    <hyperlink ref="H37" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
-    <hyperlink ref="H30" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
-    <hyperlink ref="H32" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
-    <hyperlink ref="H31" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
-    <hyperlink ref="H27" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
-    <hyperlink ref="H33" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
-    <hyperlink ref="H35" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
-    <hyperlink ref="H28" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
-    <hyperlink ref="H29" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
-    <hyperlink ref="H34" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
-    <hyperlink ref="H26" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
-    <hyperlink ref="H110" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
-    <hyperlink ref="H104" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
-    <hyperlink ref="H102" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
-    <hyperlink ref="H105" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
-    <hyperlink ref="H106" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
-    <hyperlink ref="H107" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
-    <hyperlink ref="H108" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
-    <hyperlink ref="H93" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
-    <hyperlink ref="H84" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
-    <hyperlink ref="H96" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
-    <hyperlink ref="H82" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
-    <hyperlink ref="H85" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
-    <hyperlink ref="H95" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
-    <hyperlink ref="H103" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
-    <hyperlink ref="H54" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
-    <hyperlink ref="H90" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
-    <hyperlink ref="H111" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
-    <hyperlink ref="H72" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
-    <hyperlink ref="H100" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
-    <hyperlink ref="L100" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
-    <hyperlink ref="H55" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
-    <hyperlink ref="L55" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
-    <hyperlink ref="H56" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
-    <hyperlink ref="L56" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
-    <hyperlink ref="H52" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
-    <hyperlink ref="H23" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
-    <hyperlink ref="L23" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
-    <hyperlink ref="H24" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
-    <hyperlink ref="L25" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
-    <hyperlink ref="H25" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
-    <hyperlink ref="H22" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
-    <hyperlink ref="L22" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
-    <hyperlink ref="H101" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
-    <hyperlink ref="L101" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
-    <hyperlink ref="H21" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
-    <hyperlink ref="L21" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
-    <hyperlink ref="H61" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
-    <hyperlink ref="H20" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
-    <hyperlink ref="H36" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
-    <hyperlink ref="H19" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
-    <hyperlink ref="L19" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
-    <hyperlink ref="H18" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
-    <hyperlink ref="L18" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
-    <hyperlink ref="H17" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
-    <hyperlink ref="H16" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
-    <hyperlink ref="L16" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
-    <hyperlink ref="H59" r:id="rId88" xr:uid="{E42A52B1-D676-8D44-AA60-7F68949475E8}"/>
-    <hyperlink ref="H15" r:id="rId89" xr:uid="{CE730D97-1D2C-7C46-ACA3-E12040378435}"/>
+    <hyperlink ref="H71" r:id="rId19" xr:uid="{0F56A368-05DC-0046-A036-15A5A9522952}"/>
+    <hyperlink ref="H69" r:id="rId20" xr:uid="{9DC77239-72AD-1A40-93F3-F8C653039533}"/>
+    <hyperlink ref="H70" r:id="rId21" xr:uid="{5D78D208-C834-DC4D-87CE-7718DC1647F2}"/>
+    <hyperlink ref="H72" r:id="rId22" xr:uid="{B69E3BA3-5461-EE40-BA4E-41A5BE1E7BF4}"/>
+    <hyperlink ref="H65" r:id="rId23" xr:uid="{B62A6D1F-5DF0-A643-BD46-EC9EB0884BB7}"/>
+    <hyperlink ref="H64" r:id="rId24" xr:uid="{FC29BA63-1C7C-5644-A653-C892769FAC75}"/>
+    <hyperlink ref="H68" r:id="rId25" xr:uid="{DCC13ED3-9E8E-DA4D-91D1-75A7931C642A}"/>
+    <hyperlink ref="H67" r:id="rId26" xr:uid="{0D9C681C-5B99-484C-BFFE-EF206CDCCCD9}"/>
+    <hyperlink ref="H73" r:id="rId27" xr:uid="{BB4D8478-DB58-4541-B1EB-38CC918B98D4}"/>
+    <hyperlink ref="H66" r:id="rId28" xr:uid="{BC3F325E-FC97-4046-8121-C76DBBF7A70C}"/>
+    <hyperlink ref="H94" r:id="rId29" xr:uid="{6CB5F6A4-6266-8745-8ABF-834A77B5DB82}"/>
+    <hyperlink ref="H40" r:id="rId30" xr:uid="{CFE95743-0EDD-8E40-A8A0-F984882C50FA}"/>
+    <hyperlink ref="H39" r:id="rId31" xr:uid="{1DB044A5-2953-CC4F-8392-5B010494975C}"/>
+    <hyperlink ref="H32" r:id="rId32" xr:uid="{2E2BE611-B19B-864B-81CA-ED12C30C5381}"/>
+    <hyperlink ref="H34" r:id="rId33" xr:uid="{7BE5EE7B-E118-0242-9A9A-1D3F59310915}"/>
+    <hyperlink ref="H33" r:id="rId34" location="51756" xr:uid="{02D186F8-FDBD-EC49-A8A3-FF14990164C8}"/>
+    <hyperlink ref="H29" r:id="rId35" xr:uid="{D4D7764B-4625-6849-A173-ABC063A92FD9}"/>
+    <hyperlink ref="H35" r:id="rId36" xr:uid="{3A4EA812-599C-7544-A5F0-23CA28A2F37F}"/>
+    <hyperlink ref="H37" r:id="rId37" xr:uid="{C00B1E10-5E9E-154D-AB53-5ADB8CCCC7CF}"/>
+    <hyperlink ref="H30" r:id="rId38" xr:uid="{B1D05BCB-7B7E-5C4B-A7C7-46D21228123A}"/>
+    <hyperlink ref="H31" r:id="rId39" xr:uid="{A244D270-7C2F-FC48-AA9E-77923E3F9E9C}"/>
+    <hyperlink ref="H36" r:id="rId40" xr:uid="{F7DB1F5F-687C-9141-9973-65A3BF51552C}"/>
+    <hyperlink ref="H28" r:id="rId41" xr:uid="{F3F64AD5-5A76-7347-A675-056AF03551CD}"/>
+    <hyperlink ref="H112" r:id="rId42" xr:uid="{7B808A16-9C5B-D94C-81E8-46AFD11DAA8B}"/>
+    <hyperlink ref="H106" r:id="rId43" xr:uid="{B760EFB7-EAAF-EA48-87C1-3533C77A9935}"/>
+    <hyperlink ref="H104" r:id="rId44" xr:uid="{968384FB-1A18-4A4F-8CBD-27769ADC4E4A}"/>
+    <hyperlink ref="H107" r:id="rId45" xr:uid="{704D09EA-DD52-5242-B84F-4497D98C6ED4}"/>
+    <hyperlink ref="H108" r:id="rId46" xr:uid="{A9977D40-898D-A047-A597-F8890E973840}"/>
+    <hyperlink ref="H109" r:id="rId47" xr:uid="{4E792F61-7F80-6C4B-9665-B6B417F7696C}"/>
+    <hyperlink ref="H110" r:id="rId48" xr:uid="{9640B243-AB3F-1241-8664-B498E1955BA8}"/>
+    <hyperlink ref="H95" r:id="rId49" xr:uid="{1EEB7EC7-3232-C74A-B8D4-F766FA226DD6}"/>
+    <hyperlink ref="H86" r:id="rId50" xr:uid="{2982BCF7-83FA-DF42-8E77-65A98FEF0D97}"/>
+    <hyperlink ref="H98" r:id="rId51" xr:uid="{0C3EA1BA-1C76-F34B-BAFC-DF3F07FE7E3C}"/>
+    <hyperlink ref="H84" r:id="rId52" xr:uid="{F982A45B-F644-B64B-87EC-0810B78786A5}"/>
+    <hyperlink ref="H87" r:id="rId53" xr:uid="{D2634F17-366F-9740-84F6-0D60A7B20722}"/>
+    <hyperlink ref="H97" r:id="rId54" xr:uid="{4AF62C81-5DA0-9E44-B08F-C265FE6BB5D9}"/>
+    <hyperlink ref="H105" r:id="rId55" xr:uid="{87D48D69-5CB1-5544-A6F0-BE893636CEF2}"/>
+    <hyperlink ref="H56" r:id="rId56" xr:uid="{52C93DA9-64C2-014A-B30A-2B177DD0B7DE}"/>
+    <hyperlink ref="H92" r:id="rId57" xr:uid="{2E2C475F-ED50-6140-A773-84CC4222E0CA}"/>
+    <hyperlink ref="H113" r:id="rId58" xr:uid="{D539F041-4ECB-4B46-AA9A-D6B196D8A578}"/>
+    <hyperlink ref="H74" r:id="rId59" xr:uid="{D03CDF7F-3D47-744D-A3F2-87B440B09025}"/>
+    <hyperlink ref="H102" r:id="rId60" xr:uid="{A5585207-4432-684C-ADE9-C84F0CA5AAD9}"/>
+    <hyperlink ref="L102" r:id="rId61" xr:uid="{3E54F8DD-6635-3C47-BCC2-34908E69A5D1}"/>
+    <hyperlink ref="H57" r:id="rId62" xr:uid="{F8B1CF3D-0CD6-EA4E-A42F-3BF6A0C87CAC}"/>
+    <hyperlink ref="L57" r:id="rId63" display="https://www.google.com.tw/maps/place/22:02%E7%81%AB%E9%8D%8B%E6%9E%97%E5%8F%A3A9%E5%BA%97/@25.0663398,121.3593625,17z/data=!3m2!4b1!5s0x3442a7292586cf11:0x703479ec14144dc9!4m5!3m4!1s0x3442a6d8f37ed567:0xeb5e73cbf3a1886f!8m2!3d25.0663398!4d121.3615512?hl=zh-TW&amp;authuser=0" xr:uid="{CB0D7412-1A12-5349-B3D7-414DF5B43C83}"/>
+    <hyperlink ref="H58" r:id="rId64" xr:uid="{D1CBAEBE-2E3F-0040-9DE2-9A9A3466061E}"/>
+    <hyperlink ref="L58" r:id="rId65" display="https://www.google.com.tw/maps/place/%E5%85%AB%E6%96%B9%E6%82%85%E9%8D%8B%E7%89%A9%E6%9E%97%E5%8F%A3%E4%BB%81%E6%84%9B%E5%BA%97/@25.0757201,121.366146,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a73657bfbe67:0x346d8a5db5ff186a!8m2!3d25.0757201!4d121.36834?hl=zh-TW&amp;authuser=0" xr:uid="{A55B55C3-93B4-4040-AF7B-DCA3062DEBD3}"/>
+    <hyperlink ref="H54" r:id="rId66" xr:uid="{AAD20ECD-8588-E241-B69B-754D4B06881A}"/>
+    <hyperlink ref="H25" r:id="rId67" xr:uid="{9C140042-4CC9-034D-A00A-3D2BD16F97AD}"/>
+    <hyperlink ref="L25" r:id="rId68" xr:uid="{FA7D09AC-D851-AC41-8398-2F23FC809D00}"/>
+    <hyperlink ref="H26" r:id="rId69" xr:uid="{DB973B9E-8E27-AA40-A331-E5E9CEB96B21}"/>
+    <hyperlink ref="L27" r:id="rId70" display="https://www.google.com.tw/maps/place/S%C3%B6t+cafe+Bistronomy+%E6%B5%AE%E5%B3%B6%E5%B1%95%E6%82%85%E5%BA%97/@25.0903959,121.3788836,17z/data=!4m9!1m2!2m1!1z5paw5YyX5biC5bGV5oKF5rWu5bO25ZKW5ZWh6aSo!3m5!1s0x3442a6eb3619c47b:0x47e7cbddc475b699!8m2!3d25.0905085!4d121.3811853!15sCh7mlrDljJfluILlsZXmgoXmta7ls7blkpbllaHppKhaJiIk5pawIOWMl-W4giDlsZUg5oKFIOa1ruWztiDlkpbllaEg6aSokgEKcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNMGIyUXRSRFJCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{F0213A89-61DF-6448-8E39-F59141AE23F6}"/>
+    <hyperlink ref="H27" r:id="rId71" xr:uid="{561C4FC2-300D-2440-B605-44B4569BA6AC}"/>
+    <hyperlink ref="H24" r:id="rId72" xr:uid="{B3CCD5FF-E445-8244-A20C-A965CDDEA901}"/>
+    <hyperlink ref="L24" r:id="rId73" display="https://www.google.com.tw/maps/place/%E7%94%9C%E8%92%94%E5%90%87%E8%88%92%E8%8A%99%E8%95%BE%E5%92%96%E5%95%A1%E5%B0%88%E8%B3%A3/@25.069282,121.3641541,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7b6e5b090b9:0x3660f93869cab755!8m2!3d25.069282!4d121.3663481?hl=zh-TW&amp;authuser=0" xr:uid="{D5DCDB6B-532C-2148-8B67-9B9DD10D57B1}"/>
+    <hyperlink ref="H103" r:id="rId74" xr:uid="{CC1630A2-421D-884D-81E7-32E237B33080}"/>
+    <hyperlink ref="L103" r:id="rId75" xr:uid="{E43EF40F-F508-A443-9A5C-C1B22C6E598E}"/>
+    <hyperlink ref="H23" r:id="rId76" xr:uid="{34F2F552-FE7F-5549-8AE7-C52C1D1D21AB}"/>
+    <hyperlink ref="L23" r:id="rId77" xr:uid="{8DB17DE3-1D91-7041-8C0D-59A1D544BAED}"/>
+    <hyperlink ref="H63" r:id="rId78" xr:uid="{660EB1D5-BFEE-7446-B839-17006FEA123A}"/>
+    <hyperlink ref="H22" r:id="rId79" xr:uid="{EC7EB99D-3CAA-EB4D-A98C-DCEE8436E6E6}"/>
+    <hyperlink ref="H38" r:id="rId80" xr:uid="{179AAF9D-38F8-D145-8DBF-4D4C34EAB439}"/>
+    <hyperlink ref="H21" r:id="rId81" xr:uid="{55B07958-A1B0-8A48-B1D9-032D66A4C249}"/>
+    <hyperlink ref="L21" r:id="rId82" display="https://www.google.ca/maps/place/%E9%A3%9F%E4%B9%8B%E6%9C%89%E6%83%85%EF%BC%9A%E7%BE%8E%E5%91%B3%E7%94%A8%E5%BF%83%E7%B6%93%E7%87%9F/@49.1535212,-123.1354447,14z/data=!4m5!3m4!1s0x3442a72869dba05f:0x147152b8c6ccf57a!8m2!3d25.07158!4d121.3642026?hl=zh-TW&amp;authuser=0" xr:uid="{35E9DBDE-831C-2448-9ABE-20709794D354}"/>
+    <hyperlink ref="H20" r:id="rId83" xr:uid="{AEFAC7F1-E6DF-BF40-B0B2-77658D461D51}"/>
+    <hyperlink ref="L20" r:id="rId84" xr:uid="{5E2FC776-585F-4B42-8BD2-4A9C8963F5E8}"/>
+    <hyperlink ref="H19" r:id="rId85" xr:uid="{0E2A30E6-9E31-3F44-A818-7734F09D0351}"/>
+    <hyperlink ref="H18" r:id="rId86" xr:uid="{8FEFF94C-3121-0B40-B801-49BCE0358794}"/>
+    <hyperlink ref="L18" r:id="rId87" display="https://www.google.ca/maps/place/%E6%98%8E%E6%B0%B4%E7%84%B6%E3%83%BB%E6%A8%82-%E6%9E%97%E5%8F%A3%E6%98%95%E5%A2%83%E5%BA%97/@25.0738036,121.3668081,17z/data=!4m5!3m4!1s0x3442a7e5ecb94375:0xf2a1dbb6301faa45!8m2!3d25.0737609!4d121.3690299?hl=zh-TW&amp;authuser=0" xr:uid="{8D239CF5-EB6C-1442-932F-769079D411E5}"/>
+    <hyperlink ref="H61" r:id="rId88" xr:uid="{E42A52B1-D676-8D44-AA60-7F68949475E8}"/>
+    <hyperlink ref="H17" r:id="rId89" xr:uid="{CE730D97-1D2C-7C46-ACA3-E12040378435}"/>
+    <hyperlink ref="H15" r:id="rId90" xr:uid="{9F579E7C-4194-DF47-BB4C-408DAA470C44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3101-Restaurant.xlsx
+++ b/db/A7XLK-3101-Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592B447D-4FAC-EE46-BC6B-893651BD30D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3992B7C6-AC68-1447-863C-3D0CD1ECB7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-12240" yWindow="-18580" windowWidth="27860" windowHeight="13420" xr2:uid="{1AAFA279-DBCD-DA42-8F0D-FE7868FF2730}"/>
   </bookViews>
@@ -5187,1076 +5187,1076 @@
         <v>631</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="112">
+    <row r="15" spans="1:12" ht="64">
       <c r="A15" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="K15" s="10">
         <v>4.9000000000000004</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="64">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="80">
       <c r="A16" s="1" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>445</v>
+        <v>965</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>990</v>
+        <v>972</v>
       </c>
       <c r="K16" s="10">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="80">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="112">
       <c r="A17" s="1" t="s">
-        <v>964</v>
+        <v>947</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>968</v>
+        <v>930</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>966</v>
+        <v>951</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="K17" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="112">
+        <v>4.3</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="64">
       <c r="A18" s="1" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>800</v>
+        <v>939</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="K18" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>954</v>
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="64">
       <c r="A19" s="1" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>445</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="K19" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="64">
+        <v>5</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="128">
       <c r="A20" s="1" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>445</v>
+        <v>922</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>933</v>
+        <v>403</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>935</v>
+        <v>924</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>926</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="K20" s="10">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="128">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12"